--- a/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4170" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C67DEFA-BB35-4EB6-B932-3884EAFA3343}"/>
+  <xr:revisionPtr revIDLastSave="4175" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4C0134-8ED1-434E-A067-5F4EFABFA36A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="1195">
   <si>
     <t>Type</t>
   </si>
@@ -2222,15 +2222,6 @@
     <t>Drop off the flint zone probe</t>
   </si>
   <si>
-    <t>tool_Hd_xxxxx</t>
-  </si>
-  <si>
-    <t>tool change file</t>
-  </si>
-  <si>
-    <t>Optional - Settings required for each tool</t>
-  </si>
-  <si>
     <t>z_offset</t>
   </si>
   <si>
@@ -2346,12 +2337,6 @@
   </si>
   <si>
     <t>This macro is run when a print has "100%"  completed</t>
-  </si>
-  <si>
-    <t>tool.g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional- Define tool perameters set by the tool_hd_x .g  file </t>
   </si>
   <si>
     <t>Machine Gcode</t>
@@ -3712,6 +3697,12 @@
   </si>
   <si>
     <t>chamber_ramp</t>
+  </si>
+  <si>
+    <t>Ramp up chamber temp</t>
+  </si>
+  <si>
+    <t>To avoid heater faults</t>
   </si>
 </sst>
 </file>
@@ -7799,10 +7790,10 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}" name="Table3" displayName="Table3" ref="A1:C13" totalsRowShown="0">
-  <autoFilter ref="A1:C13" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C13">
-    <sortCondition ref="A1:A13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}" name="Table3" displayName="Table3" ref="A1:C12" totalsRowShown="0">
+  <autoFilter ref="A1:C12" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
+    <sortCondition ref="A1:A12"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="18"/>
@@ -7814,10 +7805,10 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}" name="Table4" displayName="Table4" ref="A16:C33" totalsRowShown="0">
-  <autoFilter ref="A16:C33" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:C33">
-    <sortCondition ref="A16:A33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}" name="Table4" displayName="Table4" ref="A15:C31" totalsRowShown="0">
+  <autoFilter ref="A15:C31" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:C31">
+    <sortCondition ref="A15:A31"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="17"/>
@@ -7829,8 +7820,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}" name="Table5" displayName="Table5" ref="A35:B39" totalsRowShown="0">
-  <autoFilter ref="A35:B39" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}" name="Table5" displayName="Table5" ref="A33:B37" totalsRowShown="0">
+  <autoFilter ref="A33:B37" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{9B5CA5FD-9D48-460B-8000-5A3DECA0A58C}" name="Machine Gcode"/>
     <tableColumn id="3" xr3:uid="{122CB247-7719-4458-B0BE-E37243F62675}" name="Description"/>
@@ -7840,10 +7831,10 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}" name="Table58" displayName="Table58" ref="A44:B54" totalsRowShown="0">
-  <autoFilter ref="A44:B54" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A45:B54">
-    <sortCondition ref="A44:A54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}" name="Table58" displayName="Table58" ref="A42:B52" totalsRowShown="0">
+  <autoFilter ref="A42:B52" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:B52">
+    <sortCondition ref="A42:A52"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{646EABC4-F408-4AD0-8ED9-44B19D7B9F30}" name="Filaments"/>
@@ -15235,7 +15226,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
@@ -15260,7 +15251,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -15366,94 +15363,94 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="147" t="s">
+      <c r="A12" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="B12" s="146" t="s">
+      <c r="B12" t="s">
         <v>721</v>
       </c>
-      <c r="C12" s="148" t="s">
+      <c r="C12" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="25" t="s">
-        <v>723</v>
-      </c>
-      <c r="B13" t="s">
-        <v>724</v>
-      </c>
-      <c r="C13" t="s">
-        <v>725</v>
-      </c>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25"/>
       <c r="B14" s="25"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
+      <c r="A15" s="65" t="s">
+        <v>649</v>
+      </c>
+      <c r="B15" t="s">
+        <v>723</v>
+      </c>
+      <c r="C15" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="65" t="s">
-        <v>649</v>
+      <c r="A16" s="25" t="s">
+        <v>724</v>
       </c>
       <c r="B16" t="s">
+        <v>725</v>
+      </c>
+      <c r="C16" t="s">
         <v>726</v>
-      </c>
-      <c r="C16" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="4" t="s">
         <v>728</v>
-      </c>
-      <c r="C17" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25" t="s">
+        <v>729</v>
+      </c>
+      <c r="C18" t="s">
         <v>730</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25" t="s">
+        <v>731</v>
+      </c>
+      <c r="C19" t="s">
         <v>732</v>
-      </c>
-      <c r="C19" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25" t="s">
+        <v>733</v>
+      </c>
+      <c r="C20" t="s">
         <v>734</v>
-      </c>
-      <c r="C20" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C21" t="s">
         <v>736</v>
-      </c>
-      <c r="C21" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25" t="s">
+        <v>737</v>
+      </c>
+      <c r="C22" t="s">
         <v>738</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" s="134" t="s">
         <v>739</v>
       </c>
     </row>
@@ -15461,10 +15458,10 @@
       <c r="A23" s="25" t="s">
         <v>740</v>
       </c>
+      <c r="B23" t="s">
+        <v>741</v>
+      </c>
       <c r="C23" t="s">
-        <v>741</v>
-      </c>
-      <c r="E23" s="134" t="s">
         <v>742</v>
       </c>
     </row>
@@ -15472,31 +15469,31 @@
       <c r="A24" s="25" t="s">
         <v>743</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>744</v>
-      </c>
-      <c r="C24" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25" t="s">
+        <v>745</v>
+      </c>
+      <c r="C25" t="s">
         <v>746</v>
-      </c>
-      <c r="C25" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25" t="s">
+        <v>747</v>
+      </c>
+      <c r="C26" t="s">
         <v>748</v>
-      </c>
-      <c r="C26" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25" t="s">
+        <v>749</v>
+      </c>
+      <c r="B27" t="s">
         <v>750</v>
       </c>
       <c r="C27" t="s">
@@ -15518,185 +15515,166 @@
       <c r="A29" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>756</v>
-      </c>
-      <c r="C29" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25" t="s">
+        <v>757</v>
+      </c>
+      <c r="C30" t="s">
         <v>758</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="25"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" s="25"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="47" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="25" t="s">
+      <c r="B33" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
         <v>760</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B34" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="147" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
         <v>762</v>
       </c>
-      <c r="C32" s="148" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="25"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="B34" s="25"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="47" t="s">
-        <v>764</v>
-      </c>
       <c r="B35" t="s">
-        <v>361</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B36" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>764</v>
+      </c>
+      <c r="B37" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="B39" t="s">
+        <v>765</v>
+      </c>
+      <c r="D39" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="B40" t="s">
         <v>767</v>
       </c>
-      <c r="B37" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
+      <c r="D40" t="s">
         <v>768</v>
       </c>
-      <c r="B38" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="47" t="s">
         <v>769</v>
       </c>
-      <c r="B39" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="B41" t="s">
+      <c r="B42" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
         <v>770</v>
       </c>
-      <c r="D41" t="s">
+      <c r="B43" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="B42" t="s">
-        <v>772</v>
-      </c>
-      <c r="D42" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="47" t="s">
-        <v>774</v>
-      </c>
       <c r="B44" t="s">
-        <v>361</v>
+        <v>761</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B45" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B46" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B47" t="s">
-        <v>778</v>
+        <v>761</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B48" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B49" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B50" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B51" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B52" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>784</v>
-      </c>
-      <c r="B53" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>785</v>
-      </c>
-      <c r="B54" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -15737,14 +15715,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="A1" s="107" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B1" s="105"/>
       <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="108" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B2" s="105"/>
       <c r="C2" s="105"/>
@@ -15754,80 +15732,80 @@
       <c r="B3" s="128"/>
       <c r="C3" s="128"/>
       <c r="D3" s="110" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="E3" s="110" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="F3" s="110" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="G3" s="110" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="H3" s="110" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="I3" s="110" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="J3" s="133" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="K3" s="110" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="L3" s="112" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="106" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
       <c r="A4" s="126" t="s">
+        <v>788</v>
+      </c>
+      <c r="B4" s="126" t="s">
+        <v>789</v>
+      </c>
+      <c r="C4" s="126" t="s">
+        <v>790</v>
+      </c>
+      <c r="D4" s="126" t="s">
+        <v>791</v>
+      </c>
+      <c r="E4" s="126" t="s">
+        <v>792</v>
+      </c>
+      <c r="F4" s="126" t="s">
         <v>793</v>
       </c>
-      <c r="B4" s="126" t="s">
+      <c r="G4" s="126" t="s">
         <v>794</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="H4" s="126" t="s">
         <v>795</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="I4" s="126" t="s">
         <v>796</v>
       </c>
-      <c r="E4" s="126" t="s">
+      <c r="J4" s="126" t="s">
         <v>797</v>
       </c>
-      <c r="F4" s="126" t="s">
+      <c r="K4" s="126" t="s">
         <v>798</v>
       </c>
-      <c r="G4" s="126" t="s">
+      <c r="L4" s="126" t="s">
         <v>799</v>
-      </c>
-      <c r="H4" s="126" t="s">
-        <v>800</v>
-      </c>
-      <c r="I4" s="126" t="s">
-        <v>801</v>
-      </c>
-      <c r="J4" s="126" t="s">
-        <v>802</v>
-      </c>
-      <c r="K4" s="126" t="s">
-        <v>803</v>
-      </c>
-      <c r="L4" s="126" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A5" s="129" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B5" s="122" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C5" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D5" s="123">
         <v>105</v>
@@ -15859,13 +15837,13 @@
     </row>
     <row r="6" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="129" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B6" s="122" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C6" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D6" s="123">
         <v>105</v>
@@ -15897,13 +15875,13 @@
     </row>
     <row r="7" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="129" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="B7" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C7" s="123" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="D7" s="123">
         <v>90</v>
@@ -15935,10 +15913,10 @@
     </row>
     <row r="8" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="129" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C8" s="123">
         <v>0</v>
@@ -15956,10 +15934,10 @@
         <v>50</v>
       </c>
       <c r="H8" s="123" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="I8" s="124" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="J8" s="123">
         <v>80</v>
@@ -15973,13 +15951,13 @@
     </row>
     <row r="9" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="121" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B9" s="122" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C9" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D9" s="123">
         <v>105</v>
@@ -16011,13 +15989,13 @@
     </row>
     <row r="10" spans="1:12" s="106" customFormat="1" ht="17.25" customHeight="1">
       <c r="A10" s="121" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="B10" s="122" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C10" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D10" s="123">
         <v>60</v>
@@ -16049,13 +16027,13 @@
     </row>
     <row r="11" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B11" s="122" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C11" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D11" s="123">
         <v>60</v>
@@ -16087,13 +16065,13 @@
     </row>
     <row r="12" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="B12" s="122" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C12" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D12" s="123">
         <v>60</v>
@@ -16125,13 +16103,13 @@
     </row>
     <row r="13" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="121" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B13" s="122" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C13" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D13" s="123">
         <v>70</v>
@@ -16163,10 +16141,10 @@
     </row>
     <row r="14" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="121" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B14" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C14" s="123">
         <v>0</v>
@@ -16201,11 +16179,11 @@
     </row>
     <row r="15" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="129" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="B15" s="122"/>
       <c r="C15" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D15" s="123">
         <v>137</v>
@@ -16237,11 +16215,11 @@
     </row>
     <row r="16" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="129" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B16" s="122"/>
       <c r="C16" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D16" s="123">
         <v>126</v>
@@ -16273,13 +16251,13 @@
     </row>
     <row r="17" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A17" s="121" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B17" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C17" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D17" s="123">
         <v>145</v>
@@ -16311,13 +16289,13 @@
     </row>
     <row r="18" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="121" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="B18" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C18" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D18" s="123">
         <v>113</v>
@@ -16349,11 +16327,11 @@
     </row>
     <row r="19" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="121" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="B19" s="122"/>
       <c r="C19" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D19" s="123">
         <v>158</v>
@@ -16385,11 +16363,11 @@
     </row>
     <row r="20" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="121" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B20" s="122"/>
       <c r="C20" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D20" s="123">
         <v>143</v>
@@ -16425,7 +16403,7 @@
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D21" s="123">
         <v>140</v>
@@ -16457,13 +16435,13 @@
     </row>
     <row r="22" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="121" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="B22" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C22" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D22" s="123">
         <v>113</v>
@@ -16495,13 +16473,13 @@
     </row>
     <row r="23" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="129" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="B23" s="122" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C23" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D23" s="123">
         <v>143</v>
@@ -16533,13 +16511,13 @@
     </row>
     <row r="24" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="129" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B24" s="122" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C24" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D24" s="123">
         <v>165</v>
@@ -16571,13 +16549,13 @@
     </row>
     <row r="25" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="121" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="B25" s="122" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C25" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D25" s="123">
         <v>165</v>
@@ -16609,13 +16587,13 @@
     </row>
     <row r="26" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="130" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="B26" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C26" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D26" s="123">
         <v>70</v>
@@ -16647,13 +16625,13 @@
     </row>
     <row r="27" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="129" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="B27" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C27" s="123" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="D27" s="123">
         <v>80</v>
@@ -16685,13 +16663,13 @@
     </row>
     <row r="28" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="129" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B28" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C28" s="123" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="D28" s="123">
         <v>85</v>
@@ -16726,10 +16704,10 @@
         <v>664</v>
       </c>
       <c r="B29" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C29" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D29" s="123">
         <v>90</v>
@@ -16761,10 +16739,10 @@
     </row>
     <row r="30" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="129" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="B30" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C30" s="123">
         <v>0</v>
@@ -16802,7 +16780,7 @@
         <v>663</v>
       </c>
       <c r="B31" s="122" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C31" s="123">
         <v>0</v>
@@ -16837,10 +16815,10 @@
     </row>
     <row r="32" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="129" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B32" s="122" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C32" s="123">
         <v>0</v>
@@ -16875,10 +16853,10 @@
     </row>
     <row r="33" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="129" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B33" s="122" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C33" s="123">
         <v>0</v>
@@ -16913,11 +16891,11 @@
     </row>
     <row r="34" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="129" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="B34" s="122"/>
       <c r="C34" s="123" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D34" s="123">
         <v>170</v>
@@ -16932,10 +16910,10 @@
         <v>100</v>
       </c>
       <c r="H34" s="123" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="I34" s="124" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="J34" s="123">
         <v>158</v>
@@ -16949,11 +16927,11 @@
     </row>
     <row r="35" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="129" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B35" s="122"/>
       <c r="C35" s="123" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="D35" s="123">
         <v>80</v>
@@ -16985,10 +16963,10 @@
     </row>
     <row r="36" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="121" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B36" s="122" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C36" s="123">
         <v>0</v>
@@ -17023,7 +17001,7 @@
     </row>
     <row r="37" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="121" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="B37" s="122"/>
       <c r="C37" s="123">
@@ -17074,7 +17052,7 @@
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
       <c r="A39" s="109" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B39" s="229"/>
       <c r="C39" s="229"/>
@@ -17091,7 +17069,7 @@
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="109" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B41" s="270"/>
       <c r="C41" s="270"/>
@@ -17107,7 +17085,7 @@
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
       <c r="A42" s="229" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B42" s="105"/>
       <c r="C42" s="105"/>
@@ -17116,7 +17094,7 @@
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
       <c r="A43" s="229" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="B43" s="105"/>
       <c r="C43" s="105"/>
@@ -17125,7 +17103,7 @@
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
       <c r="A44" s="229" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B44" s="105"/>
       <c r="C44" s="105"/>
@@ -17133,7 +17111,7 @@
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
       <c r="A45" s="229" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B45" s="105"/>
       <c r="C45" s="105"/>
@@ -17141,7 +17119,7 @@
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
       <c r="A46" s="229" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B46" s="105"/>
       <c r="C46" s="105"/>
@@ -17151,7 +17129,7 @@
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="117" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B47" s="117"/>
       <c r="C47" s="117"/>
@@ -17177,7 +17155,7 @@
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
       <c r="A49" s="131" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="E49" s="120"/>
       <c r="F49" s="120"/>
@@ -17191,7 +17169,7 @@
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
       <c r="A50" s="131" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="E50" s="120"/>
       <c r="F50" s="120"/>
@@ -24428,7 +24406,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="102" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -24436,32 +24414,32 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="103" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="104" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="102" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="102" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="102" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="102" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -24469,17 +24447,17 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="103" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="104" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="102" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -24487,37 +24465,37 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="103" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="102" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="102" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="102" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="102" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="102" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="102" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -24525,22 +24503,22 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="103" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="102" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="102" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="102" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -24569,39 +24547,39 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="277" t="s">
+        <v>868</v>
+      </c>
+      <c r="B1" s="278" t="s">
+        <v>869</v>
+      </c>
+      <c r="C1" s="278" t="s">
+        <v>870</v>
+      </c>
+      <c r="D1" s="278" t="s">
+        <v>871</v>
+      </c>
+      <c r="E1" s="278" t="s">
+        <v>872</v>
+      </c>
+      <c r="F1" s="278" t="s">
         <v>873</v>
       </c>
-      <c r="B1" s="278" t="s">
+      <c r="G1" s="279" t="s">
         <v>874</v>
       </c>
-      <c r="C1" s="278" t="s">
+      <c r="H1" s="274" t="s">
         <v>875</v>
       </c>
-      <c r="D1" s="278" t="s">
-        <v>876</v>
-      </c>
-      <c r="E1" s="278" t="s">
-        <v>877</v>
-      </c>
-      <c r="F1" s="278" t="s">
-        <v>878</v>
-      </c>
-      <c r="G1" s="279" t="s">
-        <v>879</v>
-      </c>
-      <c r="H1" s="274" t="s">
-        <v>880</v>
-      </c>
       <c r="J1" s="272" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="K1" s="272" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="277" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B2" s="278">
         <v>1</v>
@@ -24619,56 +24597,56 @@
         <v>1</v>
       </c>
       <c r="G2" s="279" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="H2" s="274">
         <v>2</v>
       </c>
       <c r="J2" s="280" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="K2" s="272" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="L2" s="272" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="277" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="B3" s="278" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C3" s="278" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D3" s="281" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="E3" s="281" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="F3" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="H3" s="274" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="J3" s="280" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="K3" s="272" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="L3" s="272" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="277" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="B4" s="278">
         <v>450</v>
@@ -24677,7 +24655,7 @@
         <v>450</v>
       </c>
       <c r="D4" s="278" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="E4" s="278">
         <v>285</v>
@@ -24689,33 +24667,33 @@
         <v>300</v>
       </c>
       <c r="H4" s="274" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="J4" s="280" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="K4" s="272" t="s">
         <v>667</v>
       </c>
       <c r="L4" s="272" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="277" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="B5" s="278" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="C5" s="278" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="D5" s="278">
         <v>150</v>
       </c>
       <c r="E5" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F5" s="278">
         <v>157</v>
@@ -24724,21 +24702,21 @@
         <v>120</v>
       </c>
       <c r="H5" s="274" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="J5" s="280" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="K5" s="272" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="L5" s="272" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
       <c r="A6" s="277" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B6" s="278">
         <v>80</v>
@@ -24747,22 +24725,22 @@
         <v>100</v>
       </c>
       <c r="D6" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E6" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F6" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="G6" s="279">
         <v>60</v>
       </c>
       <c r="H6" s="274" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="J6" s="280" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="K6" s="272" t="s">
         <v>561</v>
@@ -24770,583 +24748,583 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="277" t="s">
+        <v>891</v>
+      </c>
+      <c r="B7" s="278" t="s">
+        <v>892</v>
+      </c>
+      <c r="C7" s="278" t="s">
+        <v>893</v>
+      </c>
+      <c r="D7" s="278" t="s">
+        <v>894</v>
+      </c>
+      <c r="E7" s="278" t="s">
+        <v>895</v>
+      </c>
+      <c r="F7" s="278" t="s">
         <v>896</v>
       </c>
-      <c r="B7" s="278" t="s">
+      <c r="G7" s="279" t="s">
         <v>897</v>
       </c>
-      <c r="C7" s="278" t="s">
+      <c r="H7" s="274" t="s">
         <v>898</v>
       </c>
-      <c r="D7" s="278" t="s">
-        <v>899</v>
-      </c>
-      <c r="E7" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="F7" s="278" t="s">
-        <v>901</v>
-      </c>
-      <c r="G7" s="279" t="s">
-        <v>902</v>
-      </c>
-      <c r="H7" s="274" t="s">
-        <v>903</v>
-      </c>
       <c r="J7" s="280" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="K7" s="272" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="L7" s="272" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="277" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B8" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="C8" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="D8" s="278" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="E8" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="F8" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="G8" s="279" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="H8" s="274" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="J8" s="280" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="K8" s="272" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="L8" s="272" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="277" t="s">
+        <v>903</v>
+      </c>
+      <c r="B9" s="278" t="s">
+        <v>904</v>
+      </c>
+      <c r="C9" s="278" t="s">
+        <v>904</v>
+      </c>
+      <c r="D9" s="278" t="s">
+        <v>905</v>
+      </c>
+      <c r="E9" s="278" t="s">
+        <v>906</v>
+      </c>
+      <c r="F9" s="278" t="s">
+        <v>907</v>
+      </c>
+      <c r="H9" s="274" t="s">
         <v>908</v>
       </c>
-      <c r="B9" s="278" t="s">
-        <v>909</v>
-      </c>
-      <c r="C9" s="278" t="s">
-        <v>909</v>
-      </c>
-      <c r="D9" s="278" t="s">
-        <v>910</v>
-      </c>
-      <c r="E9" s="278" t="s">
-        <v>911</v>
-      </c>
-      <c r="F9" s="278" t="s">
-        <v>912</v>
-      </c>
-      <c r="H9" s="274" t="s">
-        <v>913</v>
-      </c>
       <c r="J9" s="280" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="K9" s="272" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="L9" s="272" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1">
       <c r="A10" s="277" t="s">
+        <v>909</v>
+      </c>
+      <c r="B10" s="282" t="s">
+        <v>910</v>
+      </c>
+      <c r="C10" s="282" t="s">
+        <v>911</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>912</v>
+      </c>
+      <c r="E10" s="282" t="s">
+        <v>913</v>
+      </c>
+      <c r="F10" s="278" t="s">
         <v>914</v>
       </c>
-      <c r="B10" s="282" t="s">
+      <c r="G10" s="275" t="s">
         <v>915</v>
       </c>
-      <c r="C10" s="282" t="s">
+      <c r="H10" s="274" t="s">
         <v>916</v>
       </c>
-      <c r="D10" s="282" t="s">
-        <v>917</v>
-      </c>
-      <c r="E10" s="282" t="s">
-        <v>918</v>
-      </c>
-      <c r="F10" s="278" t="s">
-        <v>919</v>
-      </c>
-      <c r="G10" s="275" t="s">
-        <v>920</v>
-      </c>
-      <c r="H10" s="274" t="s">
-        <v>921</v>
-      </c>
       <c r="J10" s="280" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="K10" s="272" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="277" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B11" s="278" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="C11" s="278" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="D11" s="278" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="E11" s="278" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="F11" s="278" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="G11" s="279" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="H11" s="274" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="J11" s="280" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="K11" s="272" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="L11" s="272" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="283" t="s">
+        <v>922</v>
+      </c>
+      <c r="B12" s="282" t="s">
+        <v>923</v>
+      </c>
+      <c r="C12" s="282" t="s">
+        <v>924</v>
+      </c>
+      <c r="D12" s="284" t="s">
+        <v>925</v>
+      </c>
+      <c r="E12" s="282" t="s">
+        <v>926</v>
+      </c>
+      <c r="F12" s="284" t="s">
         <v>927</v>
       </c>
-      <c r="B12" s="282" t="s">
+      <c r="H12" s="274" t="s">
         <v>928</v>
       </c>
-      <c r="C12" s="282" t="s">
-        <v>929</v>
-      </c>
-      <c r="D12" s="284" t="s">
-        <v>930</v>
-      </c>
-      <c r="E12" s="282" t="s">
-        <v>931</v>
-      </c>
-      <c r="F12" s="284" t="s">
-        <v>932</v>
-      </c>
-      <c r="H12" s="274" t="s">
-        <v>933</v>
-      </c>
       <c r="J12" s="280" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="K12" s="272" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="L12" s="272" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="277" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B13" s="278" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="C13" s="278" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="D13" s="278">
         <v>120</v>
       </c>
       <c r="E13" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F13" s="278" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="G13" s="279" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="H13" s="274" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="J13" s="280" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="K13" s="272" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="L13" s="272" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="277" t="s">
+        <v>933</v>
+      </c>
+      <c r="B14" s="278" t="s">
+        <v>934</v>
+      </c>
+      <c r="C14" s="278" t="s">
+        <v>934</v>
+      </c>
+      <c r="D14" s="278" t="s">
+        <v>935</v>
+      </c>
+      <c r="E14" s="278" t="s">
+        <v>936</v>
+      </c>
+      <c r="F14" s="278" t="s">
+        <v>937</v>
+      </c>
+      <c r="G14" s="279" t="s">
         <v>938</v>
       </c>
-      <c r="B14" s="278" t="s">
+      <c r="H14" s="274" t="s">
         <v>939</v>
       </c>
-      <c r="C14" s="278" t="s">
-        <v>939</v>
-      </c>
-      <c r="D14" s="278" t="s">
-        <v>940</v>
-      </c>
-      <c r="E14" s="278" t="s">
-        <v>941</v>
-      </c>
-      <c r="F14" s="278" t="s">
-        <v>942</v>
-      </c>
-      <c r="G14" s="279" t="s">
-        <v>943</v>
-      </c>
-      <c r="H14" s="274" t="s">
-        <v>944</v>
-      </c>
       <c r="J14" s="280" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="K14" s="272" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="L14" s="272" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="273" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B15" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="C15" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="H15" s="274" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="J15" s="280" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="K15" s="272" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="L15" s="272" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="277" t="s">
+        <v>941</v>
+      </c>
+      <c r="B16" s="278" t="s">
+        <v>942</v>
+      </c>
+      <c r="C16" s="278" t="s">
+        <v>943</v>
+      </c>
+      <c r="D16" s="278" t="s">
+        <v>944</v>
+      </c>
+      <c r="E16" s="278" t="s">
+        <v>945</v>
+      </c>
+      <c r="F16" s="278" t="s">
+        <v>945</v>
+      </c>
+      <c r="H16" s="274" t="s">
         <v>946</v>
       </c>
-      <c r="B16" s="278" t="s">
-        <v>947</v>
-      </c>
-      <c r="C16" s="278" t="s">
-        <v>948</v>
-      </c>
-      <c r="D16" s="278" t="s">
-        <v>949</v>
-      </c>
-      <c r="E16" s="278" t="s">
-        <v>950</v>
-      </c>
-      <c r="F16" s="278" t="s">
-        <v>950</v>
-      </c>
-      <c r="H16" s="274" t="s">
-        <v>951</v>
-      </c>
       <c r="J16" s="280" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="K16" s="272" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="L16" s="272" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" s="277" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B17" s="278" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C17" s="278" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D17" s="278" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="E17" s="278" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="F17" s="278" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="H17" s="274" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="J17" s="280" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="K17" s="272" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="277" t="s">
+        <v>951</v>
+      </c>
+      <c r="B18" s="278" t="s">
+        <v>952</v>
+      </c>
+      <c r="C18" s="278" t="s">
+        <v>953</v>
+      </c>
+      <c r="D18" s="278" t="s">
+        <v>954</v>
+      </c>
+      <c r="E18" s="278" t="s">
+        <v>955</v>
+      </c>
+      <c r="F18" s="278" t="s">
         <v>956</v>
       </c>
-      <c r="B18" s="278" t="s">
+      <c r="H18" s="274" t="s">
         <v>957</v>
       </c>
-      <c r="C18" s="278" t="s">
-        <v>958</v>
-      </c>
-      <c r="D18" s="278" t="s">
-        <v>959</v>
-      </c>
-      <c r="E18" s="278" t="s">
-        <v>960</v>
-      </c>
-      <c r="F18" s="278" t="s">
-        <v>961</v>
-      </c>
-      <c r="H18" s="274" t="s">
-        <v>962</v>
-      </c>
       <c r="J18" s="280" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="K18" s="272" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="L18" s="272" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="277" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="B19" s="278" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="C19" s="278" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="D19" s="278" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="E19" s="278" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="F19" s="278" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="G19" s="279" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="H19" s="279" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="J19" s="280" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="K19" s="272" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="L19" s="272" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="273" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B20" s="274" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="C20" s="274" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="G20" s="279" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="H20" s="274" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="J20" s="280" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="K20" s="272" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="L20" s="272" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1">
       <c r="A21" s="277" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B21" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C21" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="D21" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="E21" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G21" s="276" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="H21" s="274" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="J21" s="280" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="K21" s="272" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="277" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="B22" s="278" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="C22" s="278" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="D22" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="E22" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="F22" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G22" s="279" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="H22" s="274" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="J22" s="280" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="K22" s="272" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="L22" s="272" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="277" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="B23" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C23" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="D23" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="E23" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="F23" s="278" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G23" s="279" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="H23" s="274" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="J23" s="280" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="K23" s="272" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="L23" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="277" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="B24" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C24" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="D24" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E24" s="278" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="H24" s="274" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="J24" s="280" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="K24" s="272" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="L24" s="272" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="277" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B25" s="278">
         <v>0.05</v>
@@ -25355,10 +25333,10 @@
         <v>0.05</v>
       </c>
       <c r="D25" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E25" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="G25" s="279">
         <v>0.05</v>
@@ -25367,274 +25345,274 @@
         <v>0.04</v>
       </c>
       <c r="J25" s="280" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="K25" s="272" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="L25" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="277" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B26" s="278" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C26" s="278" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="D26" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E26" s="278" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G26" s="279" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="H26" s="274" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="J26" s="280" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="K26" s="272" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="L26" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="277" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="B27" s="278" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C27" s="278" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="D27" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E27" s="278" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="H27" s="278" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="J27" s="280" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="K27" s="272" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="L27" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="277" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="B28" s="278" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="C28" s="278" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="D28" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E28" s="278" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="G28" s="278" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="H28" s="274" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="J28" s="280" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="K28" s="272" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="L28" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1">
       <c r="A29" s="277" t="s">
+        <v>993</v>
+      </c>
+      <c r="B29" s="278" t="s">
+        <v>994</v>
+      </c>
+      <c r="C29" s="278" t="s">
+        <v>995</v>
+      </c>
+      <c r="D29" s="278" t="s">
+        <v>996</v>
+      </c>
+      <c r="E29" s="278" t="s">
+        <v>994</v>
+      </c>
+      <c r="G29" s="279" t="s">
+        <v>997</v>
+      </c>
+      <c r="H29" s="274" t="s">
         <v>998</v>
       </c>
-      <c r="B29" s="278" t="s">
-        <v>999</v>
-      </c>
-      <c r="C29" s="278" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D29" s="278" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E29" s="278" t="s">
-        <v>999</v>
-      </c>
-      <c r="G29" s="279" t="s">
-        <v>1002</v>
-      </c>
-      <c r="H29" s="274" t="s">
-        <v>1003</v>
-      </c>
       <c r="J29" s="280" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="K29" s="272" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="277" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B30" s="278" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="C30" s="278" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="D30" s="278" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="E30" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="G30" s="279" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="H30" s="274" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="J30" s="280" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="K30" s="272" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="L30" s="272" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="277" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="B31" s="278" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="C31" s="278" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="D31" s="278" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="E31" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="G31" s="279" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="H31" s="278" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="J31" s="280" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="K31" s="272" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="L31" s="272" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="277" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="B32" s="278" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C32" s="278" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="D32" s="278" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="E32" s="278" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="G32" s="279" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="H32" s="274" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="J32" s="280" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="K32" s="272" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="L32" s="272" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="277" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B33" s="278" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C33" s="278" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D33" s="278" t="s">
+        <v>996</v>
+      </c>
+      <c r="E33" s="278" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G33" s="279" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H33" s="274" t="s">
         <v>1015</v>
       </c>
-      <c r="B33" s="278" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C33" s="278" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D33" s="278" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E33" s="278" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G33" s="279" t="s">
-        <v>1019</v>
-      </c>
-      <c r="H33" s="274" t="s">
-        <v>1020</v>
-      </c>
       <c r="J33" s="280" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="K33" s="272" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="L33" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="277" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B34" s="278" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C34" s="278" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="D34" s="278">
         <v>1000</v>
@@ -25652,18 +25630,18 @@
         <v>9800</v>
       </c>
       <c r="J34" s="280" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="K34" s="272" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="L34" s="272" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1">
       <c r="A35" s="277" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B35" s="278">
         <v>1.75</v>
@@ -25687,158 +25665,158 @@
         <v>1.75</v>
       </c>
       <c r="K35" s="272" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="K36" s="272" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="L36" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="K37" s="272" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="L37" s="272" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="K38" s="272" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="K39" s="272" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="L39" s="272" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="K40" s="272" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="L40" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="K41" s="272" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="L41" s="272" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="K42" s="272" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L42" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="K43" s="272" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="L43" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="K44" s="272" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="K45" s="272" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="L45" s="272" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="K46" s="272" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="L46" s="272" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="K47" s="272" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="L47" s="272" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="K48" s="272" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="L48" s="272" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="49" spans="11:12">
       <c r="K49" s="272" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="L49" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="50" spans="11:12">
       <c r="K50" s="272" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="L50" s="272" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="51" spans="11:12">
       <c r="K51" s="272" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="L51" s="272" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="52" spans="11:12">
       <c r="K52" s="272" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="53" spans="11:12">
       <c r="K53" s="272" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="L53" s="272" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="54" spans="11:12">
       <c r="K54" s="272" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="L54" s="272" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="55" spans="11:12">
       <c r="K55" s="272" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="L55" s="272" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -25863,46 +25841,46 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="5" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B1" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="C1" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D1" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B2" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C2" s="137" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="B4" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="C4" t="s">
         <v>357</v>
@@ -25910,29 +25888,29 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="B5" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="C5" s="149" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B6" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -25957,7 +25935,7 @@
         <v>360</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>361</v>
@@ -25966,12 +25944,12 @@
         <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="139" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B2" s="139"/>
       <c r="C2" s="139"/>
@@ -25980,81 +25958,81 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="E6" s="99" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="C7" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1"/>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C15" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -26062,7 +26040,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -26070,71 +26048,71 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="136" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="E19" s="99" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="140" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="E23" s="99" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="140" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="B30" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="C30" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="D30" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="E30" s="80" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75">
       <c r="A31" s="138" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
     </row>
   </sheetData>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4175" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4C0134-8ED1-434E-A067-5F4EFABFA36A}"/>
+  <xr:revisionPtr revIDLastSave="4188" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1030B065-5EAF-4F68-8B39-3331C561EF00}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="36000" yWindow="75" windowWidth="21600" windowHeight="11295" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="1194">
   <si>
     <t>Type</t>
   </si>
@@ -2084,9 +2084,6 @@
     <t>Infill Type</t>
   </si>
   <si>
-    <t>Grid or Gyroid</t>
-  </si>
-  <si>
     <t>V2 Drybox</t>
   </si>
   <si>
@@ -2115,9 +2112,6 @@
   </si>
   <si>
     <t>V2 Z System</t>
-  </si>
-  <si>
-    <t>V2 LRS-240 Buddy_1x.stl</t>
   </si>
   <si>
     <t>added missing</t>
@@ -3192,12 +3186,6 @@
     <t>options</t>
   </si>
   <si>
-    <t>Test new Chamber Heater &amp; Fan</t>
-  </si>
-  <si>
-    <t>Roy</t>
-  </si>
-  <si>
     <t>WIP</t>
   </si>
   <si>
@@ -3207,21 +3195,12 @@
     <t>R/M</t>
   </si>
   <si>
-    <t>make a basic config which boards ?</t>
-  </si>
-  <si>
     <t>M/R</t>
   </si>
   <si>
     <t>workout a way to get esp32 programmed easierly</t>
   </si>
   <si>
-    <t>Chris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3rd may Mark/chris  / writing instructions /sort global vars out </t>
-  </si>
-  <si>
     <t>Update all BOMs</t>
   </si>
   <si>
@@ -3703,6 +3682,24 @@
   </si>
   <si>
     <t>To avoid heater faults</t>
+  </si>
+  <si>
+    <t>V2 LRS-360 Buddy_1x.stl</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Find a functional fan for the 750w PTC heater</t>
+  </si>
+  <si>
+    <t>make a basic config files</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>redesign the brush to reach nozzle on the volcano</t>
   </si>
 </sst>
 </file>
@@ -3710,13 +3707,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="7">
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="169" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
-    <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+    <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
   </numFmts>
   <fonts count="74">
     <font>
@@ -4523,7 +4520,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
@@ -4645,9 +4642,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4658,7 +4655,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4769,10 +4766,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4803,7 +4800,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4822,7 +4819,7 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyAlignment="1">
@@ -4836,11 +4833,11 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4855,7 +4852,7 @@
     <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4876,10 +4873,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4888,10 +4885,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4909,7 +4906,7 @@
     <xf numFmtId="3" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4991,7 +4988,7 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="41" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5088,18 +5085,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5136,6 +5122,20 @@
     <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5586,170 +5586,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -6613,7 +6449,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6638,7 +6474,7 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6724,6 +6560,170 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <border>
@@ -7726,64 +7726,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J148" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J148" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J148" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J148">
     <sortCondition ref="A1:A148"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="96"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="95"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="93"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="92">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="79"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="78">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="91" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="89" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="77" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="75" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D51" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D51" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="23" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D51" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D51">
     <sortCondition ref="B1:B51"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="34" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="22" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="21" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:H92" totalsRowCount="1" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:H92" totalsRowCount="1" headerRowDxfId="101">
   <autoFilter ref="A1:H91" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="98" totalsRowDxfId="97"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
-    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="23" dataCellStyle="Normal 7">
+    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="96"/>
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="93" totalsRowDxfId="92" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7882,121 +7882,121 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86" tableBorderDxfId="85" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72" tableBorderDxfId="71" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Cut length" dataDxfId="82" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="BOM Quantity" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Cut length" dataDxfId="68" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="BOM Quantity" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="66" tableBorderDxfId="65" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="61" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D26" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D26" totalsRowShown="0" headerRowDxfId="60" tableBorderDxfId="59" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D26" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D26">
     <sortCondition ref="B1:B26"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="71" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="58" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="57" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="56" totalsRowDxfId="55" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B29:D39" totalsRowShown="0" headerRowDxfId="68" tableBorderDxfId="67" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B29:D39" totalsRowShown="0" headerRowDxfId="54" tableBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B29:D39" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B30:D39">
     <sortCondition ref="B29:B39"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="52" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="51" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="50" totalsRowDxfId="49" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D45" totalsRowShown="0" headerRowDxfId="62" tableBorderDxfId="61" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D45" totalsRowShown="0" headerRowDxfId="48" tableBorderDxfId="47" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D45" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D45">
     <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="44" totalsRowDxfId="43" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D74" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D74" totalsRowShown="0" headerRowDxfId="42" tableBorderDxfId="41" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D74" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D74">
     <sortCondition ref="B1:B74"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="38" totalsRowDxfId="37" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D44" totalsRowShown="0" headerRowDxfId="50" tableBorderDxfId="49" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D44" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="35" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="48" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="32" totalsRowDxfId="31" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D18" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D18" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D18" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D18">
     <sortCondition ref="B1:B18"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="28" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="27" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13308,7 +13308,7 @@
         <v>3.64</v>
       </c>
       <c r="H8" s="83"/>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="47" t="s">
         <v>665</v>
       </c>
     </row>
@@ -13529,8 +13529,8 @@
       <c r="J16" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>674</v>
+      <c r="K16" s="281" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -13556,7 +13556,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>571</v>
@@ -13577,7 +13577,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>572</v>
@@ -13598,7 +13598,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>573</v>
@@ -13619,7 +13619,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>574</v>
@@ -13640,7 +13640,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>575</v>
@@ -13661,7 +13661,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>576</v>
@@ -13682,7 +13682,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>577</v>
@@ -13703,7 +13703,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>578</v>
@@ -13724,7 +13724,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>580</v>
@@ -13745,7 +13745,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>591</v>
@@ -13766,7 +13766,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>592</v>
@@ -13787,7 +13787,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>593</v>
@@ -13808,7 +13808,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>594</v>
@@ -13829,7 +13829,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>595</v>
@@ -13850,7 +13850,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B32" s="24" t="s">
         <v>596</v>
@@ -13871,7 +13871,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>597</v>
@@ -13892,7 +13892,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>509</v>
@@ -13913,7 +13913,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>511</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B36" s="24" t="s">
         <v>514</v>
@@ -13955,7 +13955,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B37" s="24" t="s">
         <v>515</v>
@@ -13976,7 +13976,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B38" s="82" t="s">
         <v>516</v>
@@ -13997,7 +13997,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B39" s="24" t="s">
         <v>517</v>
@@ -14018,7 +14018,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B40" s="24" t="s">
         <v>518</v>
@@ -14039,7 +14039,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B41" s="24" t="s">
         <v>519</v>
@@ -14060,7 +14060,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B42" s="24" t="s">
         <v>520</v>
@@ -14081,7 +14081,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B43" s="24" t="s">
         <v>521</v>
@@ -14102,7 +14102,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B44" s="24" t="s">
         <v>522</v>
@@ -14123,7 +14123,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B45" s="24" t="s">
         <v>523</v>
@@ -14144,7 +14144,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B46" s="24" t="s">
         <v>524</v>
@@ -14165,7 +14165,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B47" s="24" t="s">
         <v>525</v>
@@ -14186,7 +14186,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B48" s="24" t="s">
         <v>526</v>
@@ -14207,7 +14207,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B49" s="24" t="s">
         <v>527</v>
@@ -14228,7 +14228,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B50" s="24" t="s">
         <v>528</v>
@@ -14249,7 +14249,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B51" s="24" t="s">
         <v>529</v>
@@ -14270,7 +14270,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="135" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B52" s="24" t="s">
         <v>530</v>
@@ -14291,7 +14291,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="135" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B53" s="24" t="s">
         <v>531</v>
@@ -14312,7 +14312,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B54" s="24" t="s">
         <v>549</v>
@@ -14333,7 +14333,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>551</v>
@@ -14354,7 +14354,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>552</v>
@@ -14375,7 +14375,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B57" s="24" t="s">
         <v>553</v>
@@ -14396,7 +14396,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B58" s="24" t="s">
         <v>554</v>
@@ -14417,7 +14417,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>389</v>
@@ -14442,7 +14442,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>391</v>
@@ -14463,7 +14463,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>393</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>394</v>
@@ -14509,7 +14509,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>602</v>
@@ -14530,7 +14530,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B64" s="28" t="s">
         <v>603</v>
@@ -14551,7 +14551,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B65" s="24" t="s">
         <v>604</v>
@@ -14572,10 +14572,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B66" s="24" t="s">
         <v>679</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>680</v>
       </c>
       <c r="D66" s="91"/>
       <c r="E66" s="24">
@@ -14593,7 +14593,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B67" s="82" t="s">
         <v>443</v>
@@ -14614,7 +14614,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B68" s="52" t="s">
         <v>445</v>
@@ -14637,7 +14637,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B69" s="52" t="s">
         <v>446</v>
@@ -14660,7 +14660,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B70" s="52" t="s">
         <v>447</v>
@@ -14683,7 +14683,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B71" s="52" t="s">
         <v>448</v>
@@ -14704,7 +14704,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B72" s="52" t="s">
         <v>449</v>
@@ -14725,7 +14725,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B73" s="52" t="s">
         <v>452</v>
@@ -14753,7 +14753,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B74" s="24" t="s">
         <v>451</v>
@@ -14781,7 +14781,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B75" s="52" t="s">
         <v>450</v>
@@ -14806,10 +14806,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B76" s="24" t="s">
         <v>682</v>
-      </c>
-      <c r="B76" s="24" t="s">
-        <v>683</v>
       </c>
       <c r="C76">
         <v>7.45</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B77" s="24" t="s">
         <v>474</v>
@@ -14855,7 +14855,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B78" s="24" t="s">
         <v>476</v>
@@ -14876,7 +14876,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B79" s="24" t="s">
         <v>477</v>
@@ -14897,7 +14897,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B80" s="24" t="s">
         <v>478</v>
@@ -14918,7 +14918,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B81" s="24" t="s">
         <v>479</v>
@@ -14939,7 +14939,7 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B82" s="24" t="s">
         <v>480</v>
@@ -14960,7 +14960,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B83" s="24" t="s">
         <v>481</v>
@@ -14981,7 +14981,7 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B84" s="24" t="s">
         <v>482</v>
@@ -15002,7 +15002,7 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B85" s="24" t="s">
         <v>483</v>
@@ -15023,7 +15023,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B86" s="24" t="s">
         <v>484</v>
@@ -15044,7 +15044,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B87" s="24" t="s">
         <v>485</v>
@@ -15065,7 +15065,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B88" s="24" t="s">
         <v>486</v>
@@ -15086,7 +15086,7 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B89" s="24" t="s">
         <v>487</v>
@@ -15107,7 +15107,7 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B90" s="24" t="s">
         <v>488</v>
@@ -15128,7 +15128,7 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B91" s="24" t="s">
         <v>489</v>
@@ -15169,10 +15169,10 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="265" t="s">
-        <v>677</v>
-      </c>
-      <c r="B93" t="s">
-        <v>685</v>
+        <v>676</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>1188</v>
       </c>
       <c r="D93">
         <v>46</v>
@@ -15181,15 +15181,15 @@
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="135" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B94" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D94">
         <v>20</v>
@@ -15198,18 +15198,18 @@
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="135" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="I95" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -15237,140 +15237,140 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C1" t="s">
         <v>361</v>
       </c>
       <c r="E1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="41" t="s">
+        <v>690</v>
+      </c>
+      <c r="B3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>692</v>
-      </c>
-      <c r="B3" t="s">
-        <v>693</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="25" t="s">
+        <v>693</v>
+      </c>
+      <c r="B4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>695</v>
-      </c>
-      <c r="B4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="B5" t="s">
+        <v>697</v>
+      </c>
+      <c r="C5" t="s">
         <v>698</v>
-      </c>
-      <c r="B5" t="s">
-        <v>699</v>
-      </c>
-      <c r="C5" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="12" customHeight="1">
       <c r="A6" s="147" t="s">
+        <v>699</v>
+      </c>
+      <c r="B6" s="146" t="s">
+        <v>700</v>
+      </c>
+      <c r="C6" s="148" t="s">
         <v>701</v>
       </c>
-      <c r="B6" s="146" t="s">
+      <c r="E6" t="s">
         <v>702</v>
-      </c>
-      <c r="C6" s="148" t="s">
-        <v>703</v>
-      </c>
-      <c r="E6" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25" t="s">
+        <v>703</v>
+      </c>
+      <c r="B7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>705</v>
-      </c>
-      <c r="B7" t="s">
-        <v>706</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25" t="s">
+        <v>706</v>
+      </c>
+      <c r="B8" t="s">
+        <v>707</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="B8" t="s">
-        <v>709</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="100" t="s">
+        <v>709</v>
+      </c>
+      <c r="B9" t="s">
+        <v>710</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="B9" t="s">
-        <v>712</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25" t="s">
+        <v>712</v>
+      </c>
+      <c r="B10" t="s">
+        <v>713</v>
+      </c>
+      <c r="C10" t="s">
         <v>714</v>
-      </c>
-      <c r="B10" t="s">
-        <v>715</v>
-      </c>
-      <c r="C10" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="B11" t="s">
+        <v>716</v>
+      </c>
+      <c r="C11" t="s">
         <v>717</v>
-      </c>
-      <c r="B11" t="s">
-        <v>718</v>
-      </c>
-      <c r="C11" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25" t="s">
+        <v>718</v>
+      </c>
+      <c r="B12" t="s">
+        <v>719</v>
+      </c>
+      <c r="C12" t="s">
         <v>720</v>
-      </c>
-      <c r="B12" t="s">
-        <v>721</v>
-      </c>
-      <c r="C12" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -15386,7 +15386,7 @@
         <v>649</v>
       </c>
       <c r="B15" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C15" t="s">
         <v>361</v>
@@ -15394,137 +15394,137 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25" t="s">
+        <v>722</v>
+      </c>
+      <c r="B16" t="s">
+        <v>723</v>
+      </c>
+      <c r="C16" t="s">
         <v>724</v>
-      </c>
-      <c r="B16" t="s">
-        <v>725</v>
-      </c>
-      <c r="C16" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C18" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C19" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C20" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C21" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="C22" t="s">
+        <v>736</v>
+      </c>
+      <c r="E22" s="134" t="s">
         <v>737</v>
-      </c>
-      <c r="C22" t="s">
-        <v>738</v>
-      </c>
-      <c r="E22" s="134" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="B23" t="s">
+        <v>739</v>
+      </c>
+      <c r="C23" t="s">
         <v>740</v>
-      </c>
-      <c r="B23" t="s">
-        <v>741</v>
-      </c>
-      <c r="C23" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C24" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C25" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C26" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25" t="s">
+        <v>747</v>
+      </c>
+      <c r="B27" t="s">
+        <v>748</v>
+      </c>
+      <c r="C27" t="s">
         <v>749</v>
-      </c>
-      <c r="B27" t="s">
-        <v>750</v>
-      </c>
-      <c r="C27" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="B28" t="s">
+        <v>751</v>
+      </c>
+      <c r="C28" t="s">
         <v>752</v>
-      </c>
-      <c r="B28" t="s">
-        <v>753</v>
-      </c>
-      <c r="C28" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C29" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C30" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -15535,7 +15535,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="47" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B33" t="s">
         <v>361</v>
@@ -15543,55 +15543,55 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B34" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B36" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B37" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="B39" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="B40" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D40" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="47" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B42" t="s">
         <v>361</v>
@@ -15599,82 +15599,82 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B43" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B44" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B45" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B46" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B47" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B48" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B49" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B50" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B51" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B52" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -15715,14 +15715,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="A1" s="107" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B1" s="105"/>
       <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="108" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B2" s="105"/>
       <c r="C2" s="105"/>
@@ -15732,80 +15732,80 @@
       <c r="B3" s="128"/>
       <c r="C3" s="128"/>
       <c r="D3" s="110" t="s">
+        <v>781</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>781</v>
+      </c>
+      <c r="F3" s="110" t="s">
+        <v>781</v>
+      </c>
+      <c r="G3" s="110" t="s">
+        <v>781</v>
+      </c>
+      <c r="H3" s="110" t="s">
+        <v>781</v>
+      </c>
+      <c r="I3" s="110" t="s">
+        <v>782</v>
+      </c>
+      <c r="J3" s="133" t="s">
         <v>783</v>
       </c>
-      <c r="E3" s="110" t="s">
-        <v>783</v>
-      </c>
-      <c r="F3" s="110" t="s">
-        <v>783</v>
-      </c>
-      <c r="G3" s="110" t="s">
-        <v>783</v>
-      </c>
-      <c r="H3" s="110" t="s">
-        <v>783</v>
-      </c>
-      <c r="I3" s="110" t="s">
+      <c r="K3" s="110" t="s">
         <v>784</v>
       </c>
-      <c r="J3" s="133" t="s">
+      <c r="L3" s="112" t="s">
         <v>785</v>
-      </c>
-      <c r="K3" s="110" t="s">
-        <v>786</v>
-      </c>
-      <c r="L3" s="112" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="106" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
       <c r="A4" s="126" t="s">
+        <v>786</v>
+      </c>
+      <c r="B4" s="126" t="s">
+        <v>787</v>
+      </c>
+      <c r="C4" s="126" t="s">
         <v>788</v>
       </c>
-      <c r="B4" s="126" t="s">
+      <c r="D4" s="126" t="s">
         <v>789</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="E4" s="126" t="s">
         <v>790</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="F4" s="126" t="s">
         <v>791</v>
       </c>
-      <c r="E4" s="126" t="s">
+      <c r="G4" s="126" t="s">
         <v>792</v>
       </c>
-      <c r="F4" s="126" t="s">
+      <c r="H4" s="126" t="s">
         <v>793</v>
       </c>
-      <c r="G4" s="126" t="s">
+      <c r="I4" s="126" t="s">
         <v>794</v>
       </c>
-      <c r="H4" s="126" t="s">
+      <c r="J4" s="126" t="s">
         <v>795</v>
       </c>
-      <c r="I4" s="126" t="s">
+      <c r="K4" s="126" t="s">
         <v>796</v>
       </c>
-      <c r="J4" s="126" t="s">
+      <c r="L4" s="126" t="s">
         <v>797</v>
-      </c>
-      <c r="K4" s="126" t="s">
-        <v>798</v>
-      </c>
-      <c r="L4" s="126" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A5" s="129" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B5" s="122" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C5" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D5" s="123">
         <v>105</v>
@@ -15837,13 +15837,13 @@
     </row>
     <row r="6" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="129" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B6" s="122" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C6" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D6" s="123">
         <v>105</v>
@@ -15875,13 +15875,13 @@
     </row>
     <row r="7" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="129" t="s">
+        <v>801</v>
+      </c>
+      <c r="B7" s="122" t="s">
+        <v>802</v>
+      </c>
+      <c r="C7" s="123" t="s">
         <v>803</v>
-      </c>
-      <c r="B7" s="122" t="s">
-        <v>804</v>
-      </c>
-      <c r="C7" s="123" t="s">
-        <v>805</v>
       </c>
       <c r="D7" s="123">
         <v>90</v>
@@ -15913,10 +15913,10 @@
     </row>
     <row r="8" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="129" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C8" s="123">
         <v>0</v>
@@ -15934,10 +15934,10 @@
         <v>50</v>
       </c>
       <c r="H8" s="123" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="I8" s="124" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="J8" s="123">
         <v>80</v>
@@ -15951,13 +15951,13 @@
     </row>
     <row r="9" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="121" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B9" s="122" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C9" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D9" s="123">
         <v>105</v>
@@ -15989,13 +15989,13 @@
     </row>
     <row r="10" spans="1:12" s="106" customFormat="1" ht="17.25" customHeight="1">
       <c r="A10" s="121" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B10" s="122" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C10" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D10" s="123">
         <v>60</v>
@@ -16027,13 +16027,13 @@
     </row>
     <row r="11" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B11" s="122" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C11" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D11" s="123">
         <v>60</v>
@@ -16065,13 +16065,13 @@
     </row>
     <row r="12" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B12" s="122" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C12" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D12" s="123">
         <v>60</v>
@@ -16103,13 +16103,13 @@
     </row>
     <row r="13" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="121" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B13" s="122" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C13" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D13" s="123">
         <v>70</v>
@@ -16141,10 +16141,10 @@
     </row>
     <row r="14" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="121" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B14" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C14" s="123">
         <v>0</v>
@@ -16179,11 +16179,11 @@
     </row>
     <row r="15" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="129" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B15" s="122"/>
       <c r="C15" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D15" s="123">
         <v>137</v>
@@ -16215,11 +16215,11 @@
     </row>
     <row r="16" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="129" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B16" s="122"/>
       <c r="C16" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D16" s="123">
         <v>126</v>
@@ -16251,13 +16251,13 @@
     </row>
     <row r="17" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A17" s="121" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B17" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C17" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D17" s="123">
         <v>145</v>
@@ -16289,13 +16289,13 @@
     </row>
     <row r="18" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="121" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B18" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C18" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D18" s="123">
         <v>113</v>
@@ -16327,11 +16327,11 @@
     </row>
     <row r="19" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="121" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B19" s="122"/>
       <c r="C19" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D19" s="123">
         <v>158</v>
@@ -16363,11 +16363,11 @@
     </row>
     <row r="20" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="121" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B20" s="122"/>
       <c r="C20" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D20" s="123">
         <v>143</v>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="B21" s="122"/>
       <c r="C21" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D21" s="123">
         <v>140</v>
@@ -16435,13 +16435,13 @@
     </row>
     <row r="22" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="121" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B22" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C22" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D22" s="123">
         <v>113</v>
@@ -16473,13 +16473,13 @@
     </row>
     <row r="23" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="129" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B23" s="122" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C23" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D23" s="123">
         <v>143</v>
@@ -16511,13 +16511,13 @@
     </row>
     <row r="24" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="129" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B24" s="122" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C24" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D24" s="123">
         <v>165</v>
@@ -16549,13 +16549,13 @@
     </row>
     <row r="25" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="121" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B25" s="122" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C25" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D25" s="123">
         <v>165</v>
@@ -16587,13 +16587,13 @@
     </row>
     <row r="26" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="130" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B26" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C26" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D26" s="123">
         <v>70</v>
@@ -16625,13 +16625,13 @@
     </row>
     <row r="27" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="129" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B27" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C27" s="123" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D27" s="123">
         <v>80</v>
@@ -16663,13 +16663,13 @@
     </row>
     <row r="28" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="129" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B28" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C28" s="123" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D28" s="123">
         <v>85</v>
@@ -16704,10 +16704,10 @@
         <v>664</v>
       </c>
       <c r="B29" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C29" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D29" s="123">
         <v>90</v>
@@ -16739,10 +16739,10 @@
     </row>
     <row r="30" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="129" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B30" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C30" s="123">
         <v>0</v>
@@ -16780,7 +16780,7 @@
         <v>663</v>
       </c>
       <c r="B31" s="122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C31" s="123">
         <v>0</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="32" spans="1:12" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="129" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B32" s="122" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C32" s="123">
         <v>0</v>
@@ -16853,10 +16853,10 @@
     </row>
     <row r="33" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="129" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B33" s="122" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C33" s="123">
         <v>0</v>
@@ -16891,11 +16891,11 @@
     </row>
     <row r="34" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="129" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B34" s="122"/>
       <c r="C34" s="123" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D34" s="123">
         <v>170</v>
@@ -16910,10 +16910,10 @@
         <v>100</v>
       </c>
       <c r="H34" s="123" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="I34" s="124" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="J34" s="123">
         <v>158</v>
@@ -16927,11 +16927,11 @@
     </row>
     <row r="35" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="129" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B35" s="122"/>
       <c r="C35" s="123" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D35" s="123">
         <v>80</v>
@@ -16963,10 +16963,10 @@
     </row>
     <row r="36" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="121" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B36" s="122" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C36" s="123">
         <v>0</v>
@@ -17001,7 +17001,7 @@
     </row>
     <row r="37" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="121" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B37" s="122"/>
       <c r="C37" s="123">
@@ -17037,22 +17037,22 @@
     </row>
     <row r="38" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="111"/>
-      <c r="B38" s="268"/>
-      <c r="C38" s="268"/>
-      <c r="D38" s="269"/>
-      <c r="E38" s="269"/>
-      <c r="F38" s="269"/>
-      <c r="G38" s="269"/>
-      <c r="H38" s="269"/>
-      <c r="I38" s="269"/>
-      <c r="J38" s="269"/>
+      <c r="B38" s="282"/>
+      <c r="C38" s="282"/>
+      <c r="D38" s="283"/>
+      <c r="E38" s="283"/>
+      <c r="F38" s="283"/>
+      <c r="G38" s="283"/>
+      <c r="H38" s="283"/>
+      <c r="I38" s="283"/>
+      <c r="J38" s="283"/>
       <c r="K38" s="113"/>
       <c r="L38" s="113"/>
       <c r="M38" s="114"/>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
       <c r="A39" s="109" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B39" s="229"/>
       <c r="C39" s="229"/>
@@ -17069,23 +17069,23 @@
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="109" t="s">
-        <v>838</v>
-      </c>
-      <c r="B41" s="270"/>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
-      <c r="E41" s="271"/>
-      <c r="F41" s="271"/>
-      <c r="G41" s="271"/>
-      <c r="H41" s="271"/>
-      <c r="I41" s="271"/>
-      <c r="J41" s="271"/>
-      <c r="K41" s="271"/>
+        <v>836</v>
+      </c>
+      <c r="B41" s="284"/>
+      <c r="C41" s="284"/>
+      <c r="D41" s="285"/>
+      <c r="E41" s="285"/>
+      <c r="F41" s="285"/>
+      <c r="G41" s="285"/>
+      <c r="H41" s="285"/>
+      <c r="I41" s="285"/>
+      <c r="J41" s="285"/>
+      <c r="K41" s="285"/>
       <c r="M41" s="116"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
       <c r="A42" s="229" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B42" s="105"/>
       <c r="C42" s="105"/>
@@ -17094,7 +17094,7 @@
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
       <c r="A43" s="229" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B43" s="105"/>
       <c r="C43" s="105"/>
@@ -17103,7 +17103,7 @@
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
       <c r="A44" s="229" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B44" s="105"/>
       <c r="C44" s="105"/>
@@ -17111,7 +17111,7 @@
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
       <c r="A45" s="229" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B45" s="105"/>
       <c r="C45" s="105"/>
@@ -17119,7 +17119,7 @@
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
       <c r="A46" s="229" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B46" s="105"/>
       <c r="C46" s="105"/>
@@ -17129,7 +17129,7 @@
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="117" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B47" s="117"/>
       <c r="C47" s="117"/>
@@ -17155,7 +17155,7 @@
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
       <c r="A49" s="131" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E49" s="120"/>
       <c r="F49" s="120"/>
@@ -17169,7 +17169,7 @@
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
       <c r="A50" s="131" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E50" s="120"/>
       <c r="F50" s="120"/>
@@ -24406,7 +24406,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="102" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -24414,32 +24414,32 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="103" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="104" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="102" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="102" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="102" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="102" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -24447,17 +24447,17 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="103" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="104" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="102" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -24465,37 +24465,37 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="103" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="102" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="102" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="102" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="102" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="102" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="102" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -24503,22 +24503,22 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="103" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="102" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="102" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="102" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -24531,1292 +24531,1292 @@
   <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28" style="277" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" style="278" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43" style="278" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" style="278" customWidth="1"/>
-    <col min="5" max="5" width="34.85546875" style="278" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5703125" style="278" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.140625" style="279" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.85546875" style="274" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="272"/>
-    <col min="10" max="10" width="102.28515625" style="272" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.7109375" style="272" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="272"/>
+    <col min="1" max="1" width="28" style="273" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" style="274" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" style="274" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="274" customWidth="1"/>
+    <col min="5" max="5" width="34.85546875" style="274" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" style="274" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.140625" style="275" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.85546875" style="270" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="268"/>
+    <col min="10" max="10" width="102.28515625" style="268" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.7109375" style="268" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="268"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="277" t="s">
+      <c r="A1" s="273" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1" s="274" t="s">
+        <v>867</v>
+      </c>
+      <c r="C1" s="274" t="s">
         <v>868</v>
       </c>
-      <c r="B1" s="278" t="s">
+      <c r="D1" s="274" t="s">
         <v>869</v>
       </c>
-      <c r="C1" s="278" t="s">
+      <c r="E1" s="274" t="s">
         <v>870</v>
       </c>
-      <c r="D1" s="278" t="s">
+      <c r="F1" s="274" t="s">
         <v>871</v>
       </c>
-      <c r="E1" s="278" t="s">
+      <c r="G1" s="275" t="s">
         <v>872</v>
       </c>
-      <c r="F1" s="278" t="s">
+      <c r="H1" s="270" t="s">
         <v>873</v>
       </c>
-      <c r="G1" s="279" t="s">
+      <c r="J1" s="268" t="s">
+        <v>1066</v>
+      </c>
+      <c r="K1" s="268" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="273" t="s">
         <v>874</v>
       </c>
-      <c r="H1" s="274" t="s">
+      <c r="B2" s="274">
+        <v>1</v>
+      </c>
+      <c r="C2" s="274">
+        <v>1</v>
+      </c>
+      <c r="D2" s="274">
+        <v>1</v>
+      </c>
+      <c r="E2" s="274">
+        <v>1</v>
+      </c>
+      <c r="F2" s="274">
+        <v>1</v>
+      </c>
+      <c r="G2" s="275" t="s">
         <v>875</v>
       </c>
-      <c r="J1" s="272" t="s">
+      <c r="H2" s="270">
+        <v>2</v>
+      </c>
+      <c r="J2" s="276" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K2" s="268" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L2" s="268" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="273" t="s">
+        <v>876</v>
+      </c>
+      <c r="B3" s="274" t="s">
+        <v>877</v>
+      </c>
+      <c r="C3" s="274" t="s">
+        <v>878</v>
+      </c>
+      <c r="D3" s="277" t="s">
+        <v>877</v>
+      </c>
+      <c r="E3" s="277" t="s">
+        <v>877</v>
+      </c>
+      <c r="F3" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="H3" s="270" t="s">
+        <v>877</v>
+      </c>
+      <c r="J3" s="276" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K3" s="268" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L3" s="268" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="273" t="s">
+        <v>880</v>
+      </c>
+      <c r="B4" s="274">
+        <v>450</v>
+      </c>
+      <c r="C4" s="274">
+        <v>450</v>
+      </c>
+      <c r="D4" s="274" t="s">
+        <v>881</v>
+      </c>
+      <c r="E4" s="274">
+        <v>285</v>
+      </c>
+      <c r="F4" s="274">
+        <v>285</v>
+      </c>
+      <c r="G4" s="275">
+        <v>300</v>
+      </c>
+      <c r="H4" s="270" t="s">
+        <v>882</v>
+      </c>
+      <c r="J4" s="276" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K4" s="268" t="s">
+        <v>667</v>
+      </c>
+      <c r="L4" s="268" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="273" t="s">
+        <v>883</v>
+      </c>
+      <c r="B5" s="274" t="s">
+        <v>884</v>
+      </c>
+      <c r="C5" s="274" t="s">
+        <v>885</v>
+      </c>
+      <c r="D5" s="274">
+        <v>150</v>
+      </c>
+      <c r="E5" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="F5" s="274">
+        <v>157</v>
+      </c>
+      <c r="G5" s="275">
+        <v>120</v>
+      </c>
+      <c r="H5" s="270" t="s">
+        <v>886</v>
+      </c>
+      <c r="J5" s="276" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K5" s="268" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L5" s="268" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1">
+      <c r="A6" s="273" t="s">
+        <v>887</v>
+      </c>
+      <c r="B6" s="274">
+        <v>80</v>
+      </c>
+      <c r="C6" s="274">
+        <v>100</v>
+      </c>
+      <c r="D6" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="E6" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="F6" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="G6" s="275">
+        <v>60</v>
+      </c>
+      <c r="H6" s="270" t="s">
+        <v>888</v>
+      </c>
+      <c r="J6" s="276" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K6" s="268" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="273" t="s">
+        <v>889</v>
+      </c>
+      <c r="B7" s="274" t="s">
+        <v>890</v>
+      </c>
+      <c r="C7" s="274" t="s">
+        <v>891</v>
+      </c>
+      <c r="D7" s="274" t="s">
+        <v>892</v>
+      </c>
+      <c r="E7" s="274" t="s">
+        <v>893</v>
+      </c>
+      <c r="F7" s="274" t="s">
+        <v>894</v>
+      </c>
+      <c r="G7" s="275" t="s">
+        <v>895</v>
+      </c>
+      <c r="H7" s="270" t="s">
+        <v>896</v>
+      </c>
+      <c r="J7" s="276" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K7" s="268" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L7" s="268" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="273" t="s">
+        <v>897</v>
+      </c>
+      <c r="B8" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="C8" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="D8" s="274" t="s">
+        <v>805</v>
+      </c>
+      <c r="E8" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="F8" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="G8" s="275" t="s">
+        <v>899</v>
+      </c>
+      <c r="H8" s="270" t="s">
+        <v>900</v>
+      </c>
+      <c r="J8" s="276" t="s">
         <v>1073</v>
       </c>
-      <c r="K1" s="272" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="277" t="s">
-        <v>876</v>
-      </c>
-      <c r="B2" s="278">
-        <v>1</v>
-      </c>
-      <c r="C2" s="278">
-        <v>1</v>
-      </c>
-      <c r="D2" s="278">
-        <v>1</v>
-      </c>
-      <c r="E2" s="278">
-        <v>1</v>
-      </c>
-      <c r="F2" s="278">
-        <v>1</v>
-      </c>
-      <c r="G2" s="279" t="s">
-        <v>877</v>
-      </c>
-      <c r="H2" s="274">
-        <v>2</v>
-      </c>
-      <c r="J2" s="280" t="s">
+      <c r="K8" s="268" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L8" s="268" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="273" t="s">
+        <v>901</v>
+      </c>
+      <c r="B9" s="274" t="s">
+        <v>902</v>
+      </c>
+      <c r="C9" s="274" t="s">
+        <v>902</v>
+      </c>
+      <c r="D9" s="274" t="s">
+        <v>903</v>
+      </c>
+      <c r="E9" s="274" t="s">
+        <v>904</v>
+      </c>
+      <c r="F9" s="274" t="s">
+        <v>905</v>
+      </c>
+      <c r="H9" s="270" t="s">
+        <v>906</v>
+      </c>
+      <c r="J9" s="276" t="s">
         <v>1074</v>
       </c>
-      <c r="K2" s="272" t="s">
-        <v>1107</v>
-      </c>
-      <c r="L2" s="272" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="277" t="s">
-        <v>878</v>
-      </c>
-      <c r="B3" s="278" t="s">
+      <c r="K9" s="268" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L9" s="268" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1">
+      <c r="A10" s="273" t="s">
+        <v>907</v>
+      </c>
+      <c r="B10" s="278" t="s">
+        <v>908</v>
+      </c>
+      <c r="C10" s="278" t="s">
+        <v>909</v>
+      </c>
+      <c r="D10" s="278" t="s">
+        <v>910</v>
+      </c>
+      <c r="E10" s="278" t="s">
+        <v>911</v>
+      </c>
+      <c r="F10" s="274" t="s">
+        <v>912</v>
+      </c>
+      <c r="G10" s="271" t="s">
+        <v>913</v>
+      </c>
+      <c r="H10" s="270" t="s">
+        <v>914</v>
+      </c>
+      <c r="J10" s="276" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K10" s="268" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="273" t="s">
+        <v>915</v>
+      </c>
+      <c r="B11" s="274" t="s">
+        <v>916</v>
+      </c>
+      <c r="C11" s="274" t="s">
+        <v>916</v>
+      </c>
+      <c r="D11" s="274" t="s">
+        <v>917</v>
+      </c>
+      <c r="E11" s="274" t="s">
+        <v>918</v>
+      </c>
+      <c r="F11" s="274" t="s">
+        <v>919</v>
+      </c>
+      <c r="G11" s="275" t="s">
+        <v>899</v>
+      </c>
+      <c r="H11" s="270" t="s">
+        <v>916</v>
+      </c>
+      <c r="J11" s="276" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K11" s="268" t="s">
+        <v>997</v>
+      </c>
+      <c r="L11" s="268" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="279" t="s">
+        <v>920</v>
+      </c>
+      <c r="B12" s="278" t="s">
+        <v>921</v>
+      </c>
+      <c r="C12" s="278" t="s">
+        <v>922</v>
+      </c>
+      <c r="D12" s="280" t="s">
+        <v>923</v>
+      </c>
+      <c r="E12" s="278" t="s">
+        <v>924</v>
+      </c>
+      <c r="F12" s="280" t="s">
+        <v>925</v>
+      </c>
+      <c r="H12" s="270" t="s">
+        <v>926</v>
+      </c>
+      <c r="J12" s="276" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K12" s="268" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L12" s="268" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="273" t="s">
+        <v>927</v>
+      </c>
+      <c r="B13" s="274" t="s">
+        <v>928</v>
+      </c>
+      <c r="C13" s="274" t="s">
+        <v>928</v>
+      </c>
+      <c r="D13" s="274">
+        <v>120</v>
+      </c>
+      <c r="E13" s="274" t="s">
         <v>879</v>
       </c>
-      <c r="C3" s="278" t="s">
-        <v>880</v>
-      </c>
-      <c r="D3" s="281" t="s">
+      <c r="F13" s="274" t="s">
+        <v>929</v>
+      </c>
+      <c r="G13" s="275" t="s">
+        <v>930</v>
+      </c>
+      <c r="H13" s="270" t="s">
+        <v>928</v>
+      </c>
+      <c r="J13" s="276" t="s">
+        <v>1078</v>
+      </c>
+      <c r="K13" s="268" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L13" s="268" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="273" t="s">
+        <v>931</v>
+      </c>
+      <c r="B14" s="274" t="s">
+        <v>932</v>
+      </c>
+      <c r="C14" s="274" t="s">
+        <v>932</v>
+      </c>
+      <c r="D14" s="274" t="s">
+        <v>933</v>
+      </c>
+      <c r="E14" s="274" t="s">
+        <v>934</v>
+      </c>
+      <c r="F14" s="274" t="s">
+        <v>935</v>
+      </c>
+      <c r="G14" s="275" t="s">
+        <v>936</v>
+      </c>
+      <c r="H14" s="270" t="s">
+        <v>937</v>
+      </c>
+      <c r="J14" s="276" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K14" s="268" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L14" s="268" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="269" t="s">
+        <v>938</v>
+      </c>
+      <c r="B15" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="C15" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="H15" s="270" t="s">
+        <v>898</v>
+      </c>
+      <c r="J15" s="276" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K15" s="268" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L15" s="268" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="273" t="s">
+        <v>939</v>
+      </c>
+      <c r="B16" s="274" t="s">
+        <v>940</v>
+      </c>
+      <c r="C16" s="274" t="s">
+        <v>941</v>
+      </c>
+      <c r="D16" s="274" t="s">
+        <v>942</v>
+      </c>
+      <c r="E16" s="274" t="s">
+        <v>943</v>
+      </c>
+      <c r="F16" s="274" t="s">
+        <v>943</v>
+      </c>
+      <c r="H16" s="270" t="s">
+        <v>944</v>
+      </c>
+      <c r="J16" s="276" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K16" s="268" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L16" s="268" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1">
+      <c r="A17" s="273" t="s">
+        <v>945</v>
+      </c>
+      <c r="B17" s="274" t="s">
+        <v>946</v>
+      </c>
+      <c r="C17" s="274" t="s">
+        <v>947</v>
+      </c>
+      <c r="D17" s="274" t="s">
+        <v>948</v>
+      </c>
+      <c r="E17" s="274" t="s">
+        <v>943</v>
+      </c>
+      <c r="F17" s="274" t="s">
+        <v>943</v>
+      </c>
+      <c r="H17" s="270" t="s">
+        <v>946</v>
+      </c>
+      <c r="J17" s="276" t="s">
+        <v>1082</v>
+      </c>
+      <c r="K17" s="268" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="273" t="s">
+        <v>949</v>
+      </c>
+      <c r="B18" s="274" t="s">
+        <v>950</v>
+      </c>
+      <c r="C18" s="274" t="s">
+        <v>951</v>
+      </c>
+      <c r="D18" s="274" t="s">
+        <v>952</v>
+      </c>
+      <c r="E18" s="274" t="s">
+        <v>953</v>
+      </c>
+      <c r="F18" s="274" t="s">
+        <v>954</v>
+      </c>
+      <c r="H18" s="270" t="s">
+        <v>955</v>
+      </c>
+      <c r="J18" s="276" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K18" s="268" t="s">
+        <v>1125</v>
+      </c>
+      <c r="L18" s="268" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="273" t="s">
+        <v>956</v>
+      </c>
+      <c r="B19" s="274" t="s">
+        <v>957</v>
+      </c>
+      <c r="C19" s="274" t="s">
+        <v>957</v>
+      </c>
+      <c r="D19" s="274" t="s">
+        <v>958</v>
+      </c>
+      <c r="E19" s="274" t="s">
+        <v>959</v>
+      </c>
+      <c r="F19" s="274" t="s">
+        <v>960</v>
+      </c>
+      <c r="G19" s="275" t="s">
+        <v>958</v>
+      </c>
+      <c r="H19" s="275" t="s">
+        <v>958</v>
+      </c>
+      <c r="J19" s="276" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K19" s="268" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L19" s="268" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="269" t="s">
+        <v>961</v>
+      </c>
+      <c r="B20" s="270" t="s">
+        <v>962</v>
+      </c>
+      <c r="C20" s="270" t="s">
+        <v>963</v>
+      </c>
+      <c r="G20" s="275" t="s">
+        <v>964</v>
+      </c>
+      <c r="H20" s="270" t="s">
+        <v>965</v>
+      </c>
+      <c r="J20" s="276" t="s">
+        <v>1085</v>
+      </c>
+      <c r="K20" s="268" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L20" s="268" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1">
+      <c r="A21" s="273" t="s">
+        <v>966</v>
+      </c>
+      <c r="B21" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="C21" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="D21" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="E21" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="G21" s="272" t="s">
+        <v>969</v>
+      </c>
+      <c r="H21" s="270" t="s">
+        <v>970</v>
+      </c>
+      <c r="J21" s="276" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K21" s="268" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="273" t="s">
+        <v>971</v>
+      </c>
+      <c r="B22" s="274" t="s">
+        <v>972</v>
+      </c>
+      <c r="C22" s="274" t="s">
+        <v>973</v>
+      </c>
+      <c r="D22" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="E22" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="F22" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="G22" s="275" t="s">
+        <v>974</v>
+      </c>
+      <c r="H22" s="270" t="s">
+        <v>975</v>
+      </c>
+      <c r="J22" s="276" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K22" s="268" t="s">
+        <v>1132</v>
+      </c>
+      <c r="L22" s="268" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="273" t="s">
+        <v>976</v>
+      </c>
+      <c r="B23" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="C23" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="D23" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="E23" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="F23" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="G23" s="275" t="s">
+        <v>977</v>
+      </c>
+      <c r="H23" s="270" t="s">
+        <v>967</v>
+      </c>
+      <c r="J23" s="276" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K23" s="268" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L23" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="273" t="s">
+        <v>978</v>
+      </c>
+      <c r="B24" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="C24" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="D24" s="274" t="s">
         <v>879</v>
       </c>
-      <c r="E3" s="281" t="s">
+      <c r="E24" s="274" t="s">
+        <v>898</v>
+      </c>
+      <c r="H24" s="270" t="s">
+        <v>967</v>
+      </c>
+      <c r="J24" s="276" t="s">
+        <v>1089</v>
+      </c>
+      <c r="K24" s="268" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L24" s="268" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="273" t="s">
+        <v>979</v>
+      </c>
+      <c r="B25" s="274">
+        <v>0.05</v>
+      </c>
+      <c r="C25" s="274">
+        <v>0.05</v>
+      </c>
+      <c r="D25" s="274" t="s">
         <v>879</v>
       </c>
-      <c r="F3" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="H3" s="274" t="s">
+      <c r="E25" s="274" t="s">
         <v>879</v>
       </c>
-      <c r="J3" s="280" t="s">
-        <v>1075</v>
-      </c>
-      <c r="K3" s="272" t="s">
-        <v>1109</v>
-      </c>
-      <c r="L3" s="272" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="277" t="s">
-        <v>882</v>
-      </c>
-      <c r="B4" s="278">
-        <v>450</v>
-      </c>
-      <c r="C4" s="278">
-        <v>450</v>
-      </c>
-      <c r="D4" s="278" t="s">
-        <v>883</v>
-      </c>
-      <c r="E4" s="278">
-        <v>285</v>
-      </c>
-      <c r="F4" s="278">
-        <v>285</v>
-      </c>
-      <c r="G4" s="279">
-        <v>300</v>
-      </c>
-      <c r="H4" s="274" t="s">
-        <v>884</v>
-      </c>
-      <c r="J4" s="280" t="s">
-        <v>1076</v>
-      </c>
-      <c r="K4" s="272" t="s">
-        <v>667</v>
-      </c>
-      <c r="L4" s="272" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="277" t="s">
-        <v>885</v>
-      </c>
-      <c r="B5" s="278" t="s">
-        <v>886</v>
-      </c>
-      <c r="C5" s="278" t="s">
-        <v>887</v>
-      </c>
-      <c r="D5" s="278">
-        <v>150</v>
-      </c>
-      <c r="E5" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="F5" s="278">
-        <v>157</v>
-      </c>
-      <c r="G5" s="279">
-        <v>120</v>
-      </c>
-      <c r="H5" s="274" t="s">
-        <v>888</v>
-      </c>
-      <c r="J5" s="280" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K5" s="272" t="s">
-        <v>1112</v>
-      </c>
-      <c r="L5" s="272" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="277" t="s">
-        <v>889</v>
-      </c>
-      <c r="B6" s="278">
-        <v>80</v>
-      </c>
-      <c r="C6" s="278">
-        <v>100</v>
-      </c>
-      <c r="D6" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="E6" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="F6" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="G6" s="279">
-        <v>60</v>
-      </c>
-      <c r="H6" s="274" t="s">
-        <v>890</v>
-      </c>
-      <c r="J6" s="280" t="s">
-        <v>1078</v>
-      </c>
-      <c r="K6" s="272" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="277" t="s">
-        <v>891</v>
-      </c>
-      <c r="B7" s="278" t="s">
-        <v>892</v>
-      </c>
-      <c r="C7" s="278" t="s">
-        <v>893</v>
-      </c>
-      <c r="D7" s="278" t="s">
-        <v>894</v>
-      </c>
-      <c r="E7" s="278" t="s">
-        <v>895</v>
-      </c>
-      <c r="F7" s="278" t="s">
-        <v>896</v>
-      </c>
-      <c r="G7" s="279" t="s">
-        <v>897</v>
-      </c>
-      <c r="H7" s="274" t="s">
+      <c r="G25" s="275">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="270">
+        <v>0.04</v>
+      </c>
+      <c r="J25" s="276" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K25" s="268" t="s">
+        <v>1138</v>
+      </c>
+      <c r="L25" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="273" t="s">
+        <v>980</v>
+      </c>
+      <c r="B26" s="274" t="s">
+        <v>967</v>
+      </c>
+      <c r="C26" s="274" t="s">
+        <v>981</v>
+      </c>
+      <c r="D26" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="E26" s="274" t="s">
+        <v>982</v>
+      </c>
+      <c r="G26" s="275" t="s">
+        <v>983</v>
+      </c>
+      <c r="H26" s="270" t="s">
         <v>898</v>
       </c>
-      <c r="J7" s="280" t="s">
-        <v>1079</v>
-      </c>
-      <c r="K7" s="272" t="s">
-        <v>1114</v>
-      </c>
-      <c r="L7" s="272" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="277" t="s">
-        <v>899</v>
-      </c>
-      <c r="B8" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="C8" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="D8" s="278" t="s">
-        <v>807</v>
-      </c>
-      <c r="E8" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="F8" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="G8" s="279" t="s">
-        <v>901</v>
-      </c>
-      <c r="H8" s="274" t="s">
-        <v>902</v>
-      </c>
-      <c r="J8" s="280" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K8" s="272" t="s">
-        <v>1116</v>
-      </c>
-      <c r="L8" s="272" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="277" t="s">
-        <v>903</v>
-      </c>
-      <c r="B9" s="278" t="s">
-        <v>904</v>
-      </c>
-      <c r="C9" s="278" t="s">
-        <v>904</v>
-      </c>
-      <c r="D9" s="278" t="s">
-        <v>905</v>
-      </c>
-      <c r="E9" s="278" t="s">
-        <v>906</v>
-      </c>
-      <c r="F9" s="278" t="s">
-        <v>907</v>
-      </c>
-      <c r="H9" s="274" t="s">
-        <v>908</v>
-      </c>
-      <c r="J9" s="280" t="s">
-        <v>1081</v>
-      </c>
-      <c r="K9" s="272" t="s">
-        <v>1118</v>
-      </c>
-      <c r="L9" s="272" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1">
-      <c r="A10" s="277" t="s">
-        <v>909</v>
-      </c>
-      <c r="B10" s="282" t="s">
-        <v>910</v>
-      </c>
-      <c r="C10" s="282" t="s">
-        <v>911</v>
-      </c>
-      <c r="D10" s="282" t="s">
-        <v>912</v>
-      </c>
-      <c r="E10" s="282" t="s">
-        <v>913</v>
-      </c>
-      <c r="F10" s="278" t="s">
-        <v>914</v>
-      </c>
-      <c r="G10" s="275" t="s">
-        <v>915</v>
-      </c>
-      <c r="H10" s="274" t="s">
-        <v>916</v>
-      </c>
-      <c r="J10" s="280" t="s">
-        <v>1082</v>
-      </c>
-      <c r="K10" s="272" t="s">
+      <c r="J26" s="276" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K26" s="268" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L26" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="273" t="s">
+        <v>984</v>
+      </c>
+      <c r="B27" s="274" t="s">
+        <v>985</v>
+      </c>
+      <c r="C27" s="274" t="s">
+        <v>985</v>
+      </c>
+      <c r="D27" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="E27" s="274" t="s">
+        <v>986</v>
+      </c>
+      <c r="H27" s="274" t="s">
+        <v>985</v>
+      </c>
+      <c r="J27" s="276" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K27" s="268" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L27" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="273" t="s">
+        <v>987</v>
+      </c>
+      <c r="B28" s="274" t="s">
+        <v>988</v>
+      </c>
+      <c r="C28" s="274" t="s">
+        <v>988</v>
+      </c>
+      <c r="D28" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="E28" s="274" t="s">
+        <v>989</v>
+      </c>
+      <c r="G28" s="274" t="s">
+        <v>990</v>
+      </c>
+      <c r="H28" s="270" t="s">
+        <v>988</v>
+      </c>
+      <c r="J28" s="276" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K28" s="268" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L28" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1">
+      <c r="A29" s="273" t="s">
+        <v>991</v>
+      </c>
+      <c r="B29" s="274" t="s">
+        <v>992</v>
+      </c>
+      <c r="C29" s="274" t="s">
+        <v>993</v>
+      </c>
+      <c r="D29" s="274" t="s">
+        <v>994</v>
+      </c>
+      <c r="E29" s="274" t="s">
+        <v>992</v>
+      </c>
+      <c r="G29" s="275" t="s">
+        <v>995</v>
+      </c>
+      <c r="H29" s="270" t="s">
+        <v>996</v>
+      </c>
+      <c r="J29" s="276" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K29" s="268" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="273" t="s">
+        <v>997</v>
+      </c>
+      <c r="B30" s="274" t="s">
+        <v>998</v>
+      </c>
+      <c r="C30" s="274" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="277" t="s">
-        <v>917</v>
-      </c>
-      <c r="B11" s="278" t="s">
-        <v>918</v>
-      </c>
-      <c r="C11" s="278" t="s">
-        <v>918</v>
-      </c>
-      <c r="D11" s="278" t="s">
-        <v>919</v>
-      </c>
-      <c r="E11" s="278" t="s">
-        <v>920</v>
-      </c>
-      <c r="F11" s="278" t="s">
-        <v>921</v>
-      </c>
-      <c r="G11" s="279" t="s">
-        <v>901</v>
-      </c>
-      <c r="H11" s="274" t="s">
-        <v>918</v>
-      </c>
-      <c r="J11" s="280" t="s">
-        <v>1083</v>
-      </c>
-      <c r="K11" s="272" t="s">
-        <v>999</v>
-      </c>
-      <c r="L11" s="272" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="283" t="s">
-        <v>922</v>
-      </c>
-      <c r="B12" s="282" t="s">
-        <v>923</v>
-      </c>
-      <c r="C12" s="282" t="s">
-        <v>924</v>
-      </c>
-      <c r="D12" s="284" t="s">
-        <v>925</v>
-      </c>
-      <c r="E12" s="282" t="s">
-        <v>926</v>
-      </c>
-      <c r="F12" s="284" t="s">
-        <v>927</v>
-      </c>
-      <c r="H12" s="274" t="s">
-        <v>928</v>
-      </c>
-      <c r="J12" s="280" t="s">
-        <v>1084</v>
-      </c>
-      <c r="K12" s="272" t="s">
-        <v>1121</v>
-      </c>
-      <c r="L12" s="272" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="277" t="s">
-        <v>929</v>
-      </c>
-      <c r="B13" s="278" t="s">
-        <v>930</v>
-      </c>
-      <c r="C13" s="278" t="s">
-        <v>930</v>
-      </c>
-      <c r="D13" s="278">
-        <v>120</v>
-      </c>
-      <c r="E13" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="F13" s="278" t="s">
-        <v>931</v>
-      </c>
-      <c r="G13" s="279" t="s">
-        <v>932</v>
-      </c>
-      <c r="H13" s="274" t="s">
-        <v>930</v>
-      </c>
-      <c r="J13" s="280" t="s">
-        <v>1085</v>
-      </c>
-      <c r="K13" s="272" t="s">
-        <v>1123</v>
-      </c>
-      <c r="L13" s="272" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="277" t="s">
-        <v>933</v>
-      </c>
-      <c r="B14" s="278" t="s">
-        <v>934</v>
-      </c>
-      <c r="C14" s="278" t="s">
-        <v>934</v>
-      </c>
-      <c r="D14" s="278" t="s">
-        <v>935</v>
-      </c>
-      <c r="E14" s="278" t="s">
-        <v>936</v>
-      </c>
-      <c r="F14" s="278" t="s">
-        <v>937</v>
-      </c>
-      <c r="G14" s="279" t="s">
-        <v>938</v>
-      </c>
-      <c r="H14" s="274" t="s">
-        <v>939</v>
-      </c>
-      <c r="J14" s="280" t="s">
-        <v>1086</v>
-      </c>
-      <c r="K14" s="272" t="s">
-        <v>1125</v>
-      </c>
-      <c r="L14" s="272" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="273" t="s">
-        <v>940</v>
-      </c>
-      <c r="B15" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="C15" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="H15" s="274" t="s">
-        <v>900</v>
-      </c>
-      <c r="J15" s="280" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K15" s="272" t="s">
-        <v>1127</v>
-      </c>
-      <c r="L15" s="272" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="277" t="s">
-        <v>941</v>
-      </c>
-      <c r="B16" s="278" t="s">
-        <v>942</v>
-      </c>
-      <c r="C16" s="278" t="s">
-        <v>943</v>
-      </c>
-      <c r="D16" s="278" t="s">
-        <v>944</v>
-      </c>
-      <c r="E16" s="278" t="s">
-        <v>945</v>
-      </c>
-      <c r="F16" s="278" t="s">
-        <v>945</v>
-      </c>
-      <c r="H16" s="274" t="s">
-        <v>946</v>
-      </c>
-      <c r="J16" s="280" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K16" s="272" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L16" s="272" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1">
-      <c r="A17" s="277" t="s">
-        <v>947</v>
-      </c>
-      <c r="B17" s="278" t="s">
-        <v>948</v>
-      </c>
-      <c r="C17" s="278" t="s">
-        <v>949</v>
-      </c>
-      <c r="D17" s="278" t="s">
-        <v>950</v>
-      </c>
-      <c r="E17" s="278" t="s">
-        <v>945</v>
-      </c>
-      <c r="F17" s="278" t="s">
-        <v>945</v>
-      </c>
-      <c r="H17" s="274" t="s">
-        <v>948</v>
-      </c>
-      <c r="J17" s="280" t="s">
-        <v>1089</v>
-      </c>
-      <c r="K17" s="272" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="277" t="s">
-        <v>951</v>
-      </c>
-      <c r="B18" s="278" t="s">
-        <v>952</v>
-      </c>
-      <c r="C18" s="278" t="s">
-        <v>953</v>
-      </c>
-      <c r="D18" s="278" t="s">
-        <v>954</v>
-      </c>
-      <c r="E18" s="278" t="s">
-        <v>955</v>
-      </c>
-      <c r="F18" s="278" t="s">
-        <v>956</v>
-      </c>
-      <c r="H18" s="274" t="s">
-        <v>957</v>
-      </c>
-      <c r="J18" s="280" t="s">
-        <v>1090</v>
-      </c>
-      <c r="K18" s="272" t="s">
-        <v>1132</v>
-      </c>
-      <c r="L18" s="272" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="277" t="s">
-        <v>958</v>
-      </c>
-      <c r="B19" s="278" t="s">
-        <v>959</v>
-      </c>
-      <c r="C19" s="278" t="s">
-        <v>959</v>
-      </c>
-      <c r="D19" s="278" t="s">
-        <v>960</v>
-      </c>
-      <c r="E19" s="278" t="s">
-        <v>961</v>
-      </c>
-      <c r="F19" s="278" t="s">
-        <v>962</v>
-      </c>
-      <c r="G19" s="279" t="s">
-        <v>960</v>
-      </c>
-      <c r="H19" s="279" t="s">
-        <v>960</v>
-      </c>
-      <c r="J19" s="280" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K19" s="272" t="s">
-        <v>1134</v>
-      </c>
-      <c r="L19" s="272" t="s">
+      <c r="D30" s="274" t="s">
+        <v>994</v>
+      </c>
+      <c r="E30" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="G30" s="275" t="s">
+        <v>977</v>
+      </c>
+      <c r="H30" s="270" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J30" s="276" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K30" s="268" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L30" s="268" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="273" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B31" s="274" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C31" s="274" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D31" s="274" t="s">
+        <v>994</v>
+      </c>
+      <c r="E31" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="G31" s="275" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H31" s="274" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J31" s="276" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K31" s="268" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L31" s="268" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="273" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B32" s="274" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C32" s="274" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D32" s="274" t="s">
+        <v>994</v>
+      </c>
+      <c r="E32" s="274" t="s">
+        <v>879</v>
+      </c>
+      <c r="G32" s="275" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H32" s="270" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J32" s="276" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K32" s="268" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L32" s="268" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="273" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B33" s="274" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C33" s="274" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D33" s="274" t="s">
+        <v>994</v>
+      </c>
+      <c r="E33" s="274" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G33" s="275" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H33" s="270" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J33" s="276" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K33" s="268" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L33" s="268" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="273" t="s">
-        <v>963</v>
-      </c>
-      <c r="B20" s="274" t="s">
-        <v>964</v>
-      </c>
-      <c r="C20" s="274" t="s">
-        <v>965</v>
-      </c>
-      <c r="G20" s="279" t="s">
-        <v>966</v>
-      </c>
-      <c r="H20" s="274" t="s">
-        <v>967</v>
-      </c>
-      <c r="J20" s="280" t="s">
-        <v>1092</v>
-      </c>
-      <c r="K20" s="272" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L20" s="272" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1">
-      <c r="A21" s="277" t="s">
-        <v>968</v>
-      </c>
-      <c r="B21" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="C21" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="D21" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="E21" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="G21" s="276" t="s">
-        <v>971</v>
-      </c>
-      <c r="H21" s="274" t="s">
-        <v>972</v>
-      </c>
-      <c r="J21" s="280" t="s">
-        <v>1093</v>
-      </c>
-      <c r="K21" s="272" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="277" t="s">
-        <v>973</v>
-      </c>
-      <c r="B22" s="278" t="s">
-        <v>974</v>
-      </c>
-      <c r="C22" s="278" t="s">
-        <v>975</v>
-      </c>
-      <c r="D22" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="E22" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="F22" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="G22" s="279" t="s">
-        <v>976</v>
-      </c>
-      <c r="H22" s="274" t="s">
-        <v>977</v>
-      </c>
-      <c r="J22" s="280" t="s">
-        <v>1094</v>
-      </c>
-      <c r="K22" s="272" t="s">
-        <v>1139</v>
-      </c>
-      <c r="L22" s="272" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="277" t="s">
-        <v>978</v>
-      </c>
-      <c r="B23" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="C23" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="D23" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="E23" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="F23" s="278" t="s">
-        <v>970</v>
-      </c>
-      <c r="G23" s="279" t="s">
-        <v>979</v>
-      </c>
-      <c r="H23" s="274" t="s">
-        <v>969</v>
-      </c>
-      <c r="J23" s="280" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K23" s="272" t="s">
-        <v>1141</v>
-      </c>
-      <c r="L23" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="277" t="s">
-        <v>980</v>
-      </c>
-      <c r="B24" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="C24" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="D24" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="E24" s="278" t="s">
-        <v>900</v>
-      </c>
-      <c r="H24" s="274" t="s">
-        <v>969</v>
-      </c>
-      <c r="J24" s="280" t="s">
-        <v>1096</v>
-      </c>
-      <c r="K24" s="272" t="s">
-        <v>1143</v>
-      </c>
-      <c r="L24" s="272" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="277" t="s">
-        <v>981</v>
-      </c>
-      <c r="B25" s="278">
-        <v>0.05</v>
-      </c>
-      <c r="C25" s="278">
-        <v>0.05</v>
-      </c>
-      <c r="D25" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="E25" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="G25" s="279">
-        <v>0.05</v>
-      </c>
-      <c r="H25" s="274">
-        <v>0.04</v>
-      </c>
-      <c r="J25" s="280" t="s">
-        <v>1097</v>
-      </c>
-      <c r="K25" s="272" t="s">
-        <v>1145</v>
-      </c>
-      <c r="L25" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="277" t="s">
-        <v>982</v>
-      </c>
-      <c r="B26" s="278" t="s">
-        <v>969</v>
-      </c>
-      <c r="C26" s="278" t="s">
-        <v>983</v>
-      </c>
-      <c r="D26" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="E26" s="278" t="s">
-        <v>984</v>
-      </c>
-      <c r="G26" s="279" t="s">
-        <v>985</v>
-      </c>
-      <c r="H26" s="274" t="s">
-        <v>900</v>
-      </c>
-      <c r="J26" s="280" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K26" s="272" t="s">
-        <v>1146</v>
-      </c>
-      <c r="L26" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="277" t="s">
-        <v>986</v>
-      </c>
-      <c r="B27" s="278" t="s">
-        <v>987</v>
-      </c>
-      <c r="C27" s="278" t="s">
-        <v>987</v>
-      </c>
-      <c r="D27" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="E27" s="278" t="s">
-        <v>988</v>
-      </c>
-      <c r="H27" s="278" t="s">
-        <v>987</v>
-      </c>
-      <c r="J27" s="280" t="s">
+    <row r="34" spans="1:12">
+      <c r="A34" s="273" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B34" s="274" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C34" s="274" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D34" s="274">
+        <v>1000</v>
+      </c>
+      <c r="E34" s="274">
+        <v>1200</v>
+      </c>
+      <c r="F34" s="274">
+        <v>1700</v>
+      </c>
+      <c r="G34" s="275">
+        <v>10305</v>
+      </c>
+      <c r="H34" s="270">
+        <v>9800</v>
+      </c>
+      <c r="J34" s="276" t="s">
         <v>1099</v>
       </c>
-      <c r="K27" s="272" t="s">
-        <v>1147</v>
-      </c>
-      <c r="L27" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="277" t="s">
-        <v>989</v>
-      </c>
-      <c r="B28" s="278" t="s">
-        <v>990</v>
-      </c>
-      <c r="C28" s="278" t="s">
-        <v>990</v>
-      </c>
-      <c r="D28" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="E28" s="278" t="s">
-        <v>991</v>
-      </c>
-      <c r="G28" s="278" t="s">
-        <v>992</v>
-      </c>
-      <c r="H28" s="274" t="s">
-        <v>990</v>
-      </c>
-      <c r="J28" s="280" t="s">
-        <v>1100</v>
-      </c>
-      <c r="K28" s="272" t="s">
-        <v>1148</v>
-      </c>
-      <c r="L28" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1">
-      <c r="A29" s="277" t="s">
-        <v>993</v>
-      </c>
-      <c r="B29" s="278" t="s">
-        <v>994</v>
-      </c>
-      <c r="C29" s="278" t="s">
-        <v>995</v>
-      </c>
-      <c r="D29" s="278" t="s">
-        <v>996</v>
-      </c>
-      <c r="E29" s="278" t="s">
-        <v>994</v>
-      </c>
-      <c r="G29" s="279" t="s">
-        <v>997</v>
-      </c>
-      <c r="H29" s="274" t="s">
-        <v>998</v>
-      </c>
-      <c r="J29" s="280" t="s">
-        <v>1101</v>
-      </c>
-      <c r="K29" s="272" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="277" t="s">
-        <v>999</v>
-      </c>
-      <c r="B30" s="278" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C30" s="278" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D30" s="278" t="s">
-        <v>996</v>
-      </c>
-      <c r="E30" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="G30" s="279" t="s">
-        <v>979</v>
-      </c>
-      <c r="H30" s="274" t="s">
-        <v>1002</v>
-      </c>
-      <c r="J30" s="280" t="s">
-        <v>1102</v>
-      </c>
-      <c r="K30" s="272" t="s">
+      <c r="K34" s="268" t="s">
         <v>1150</v>
       </c>
-      <c r="L30" s="272" t="s">
+      <c r="L34" s="268" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="277" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B31" s="278" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C31" s="278" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D31" s="278" t="s">
-        <v>996</v>
-      </c>
-      <c r="E31" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="G31" s="279" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H31" s="278" t="s">
-        <v>1004</v>
-      </c>
-      <c r="J31" s="280" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K31" s="272" t="s">
+    <row r="35" spans="1:12" ht="15" customHeight="1">
+      <c r="A35" s="273" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B35" s="274">
+        <v>1.75</v>
+      </c>
+      <c r="C35" s="274">
+        <v>1.75</v>
+      </c>
+      <c r="D35" s="274">
+        <v>1.75</v>
+      </c>
+      <c r="E35" s="274">
+        <v>1.75</v>
+      </c>
+      <c r="F35" s="274">
+        <v>1.75</v>
+      </c>
+      <c r="G35" s="275">
+        <v>2.85</v>
+      </c>
+      <c r="H35" s="270">
+        <v>1.75</v>
+      </c>
+      <c r="K35" s="268" t="s">
         <v>1152</v>
       </c>
-      <c r="L31" s="272" t="s">
+    </row>
+    <row r="36" spans="1:12">
+      <c r="K36" s="268" t="s">
         <v>1153</v>
       </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="277" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B32" s="278" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C32" s="278" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D32" s="278" t="s">
-        <v>996</v>
-      </c>
-      <c r="E32" s="278" t="s">
-        <v>881</v>
-      </c>
-      <c r="G32" s="279" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H32" s="274" t="s">
-        <v>1009</v>
-      </c>
-      <c r="J32" s="280" t="s">
-        <v>1104</v>
-      </c>
-      <c r="K32" s="272" t="s">
+      <c r="L36" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="K37" s="268" t="s">
         <v>1154</v>
       </c>
-      <c r="L32" s="272" t="s">
+      <c r="L37" s="268" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="277" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B33" s="278" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C33" s="278" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D33" s="278" t="s">
-        <v>996</v>
-      </c>
-      <c r="E33" s="278" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G33" s="279" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H33" s="274" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J33" s="280" t="s">
-        <v>1105</v>
-      </c>
-      <c r="K33" s="272" t="s">
+    <row r="38" spans="1:12">
+      <c r="K38" s="268" t="s">
         <v>1156</v>
       </c>
-      <c r="L33" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="277" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B34" s="278" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C34" s="278" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D34" s="278">
-        <v>1000</v>
-      </c>
-      <c r="E34" s="278">
-        <v>1200</v>
-      </c>
-      <c r="F34" s="278">
-        <v>1700</v>
-      </c>
-      <c r="G34" s="279">
-        <v>10305</v>
-      </c>
-      <c r="H34" s="274">
-        <v>9800</v>
-      </c>
-      <c r="J34" s="280" t="s">
-        <v>1106</v>
-      </c>
-      <c r="K34" s="272" t="s">
+    </row>
+    <row r="39" spans="1:12">
+      <c r="K39" s="268" t="s">
         <v>1157</v>
       </c>
-      <c r="L34" s="272" t="s">
+      <c r="L39" s="268" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1">
-      <c r="A35" s="277" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B35" s="278">
-        <v>1.75</v>
-      </c>
-      <c r="C35" s="278">
-        <v>1.75</v>
-      </c>
-      <c r="D35" s="278">
-        <v>1.75</v>
-      </c>
-      <c r="E35" s="278">
-        <v>1.75</v>
-      </c>
-      <c r="F35" s="278">
-        <v>1.75</v>
-      </c>
-      <c r="G35" s="279">
-        <v>2.85</v>
-      </c>
-      <c r="H35" s="274">
-        <v>1.75</v>
-      </c>
-      <c r="K35" s="272" t="s">
+    <row r="40" spans="1:12">
+      <c r="K40" s="268" t="s">
         <v>1159</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="K36" s="272" t="s">
+      <c r="L40" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="K41" s="268" t="s">
         <v>1160</v>
       </c>
-      <c r="L36" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="K37" s="272" t="s">
+      <c r="L41" s="268" t="s">
         <v>1161</v>
       </c>
-      <c r="L37" s="272" t="s">
+    </row>
+    <row r="42" spans="1:12">
+      <c r="K42" s="268" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="K38" s="272" t="s">
+      <c r="L42" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="K43" s="268" t="s">
         <v>1163</v>
       </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="K39" s="272" t="s">
+      <c r="L43" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="K44" s="268" t="s">
         <v>1164</v>
       </c>
-      <c r="L39" s="272" t="s">
+    </row>
+    <row r="45" spans="1:12">
+      <c r="K45" s="268" t="s">
         <v>1165</v>
       </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="K40" s="272" t="s">
+      <c r="L45" s="268" t="s">
         <v>1166</v>
       </c>
-      <c r="L40" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="K41" s="272" t="s">
+    </row>
+    <row r="46" spans="1:12">
+      <c r="K46" s="268" t="s">
         <v>1167</v>
       </c>
-      <c r="L41" s="272" t="s">
+      <c r="L46" s="268" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
-      <c r="K42" s="272" t="s">
+    <row r="47" spans="1:12">
+      <c r="K47" s="268" t="s">
         <v>1169</v>
       </c>
-      <c r="L42" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="K43" s="272" t="s">
+      <c r="L47" s="268" t="s">
         <v>1170</v>
       </c>
-      <c r="L43" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="K44" s="272" t="s">
+    </row>
+    <row r="48" spans="1:12">
+      <c r="K48" s="268" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="K45" s="272" t="s">
+      <c r="L48" s="268" t="s">
         <v>1172</v>
       </c>
-      <c r="L45" s="272" t="s">
+    </row>
+    <row r="49" spans="11:12">
+      <c r="K49" s="268" t="s">
         <v>1173</v>
       </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="K46" s="272" t="s">
+      <c r="L49" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="50" spans="11:12">
+      <c r="K50" s="268" t="s">
         <v>1174</v>
       </c>
-      <c r="L46" s="272" t="s">
+      <c r="L50" s="268" t="s">
         <v>1175</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
-      <c r="K47" s="272" t="s">
+    <row r="51" spans="11:12">
+      <c r="K51" s="268" t="s">
         <v>1176</v>
       </c>
-      <c r="L47" s="272" t="s">
+      <c r="L51" s="268" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="52" spans="11:12">
+      <c r="K52" s="268" t="s">
         <v>1177</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
-      <c r="K48" s="272" t="s">
+    <row r="53" spans="11:12">
+      <c r="K53" s="268" t="s">
         <v>1178</v>
       </c>
-      <c r="L48" s="272" t="s">
+      <c r="L53" s="268" t="s">
         <v>1179</v>
       </c>
     </row>
-    <row r="49" spans="11:12">
-      <c r="K49" s="272" t="s">
+    <row r="54" spans="11:12">
+      <c r="K54" s="268" t="s">
         <v>1180</v>
       </c>
-      <c r="L49" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="50" spans="11:12">
-      <c r="K50" s="272" t="s">
+      <c r="L54" s="268" t="s">
         <v>1181</v>
       </c>
-      <c r="L50" s="272" t="s">
+    </row>
+    <row r="55" spans="11:12">
+      <c r="K55" s="268" t="s">
         <v>1182</v>
       </c>
-    </row>
-    <row r="51" spans="11:12">
-      <c r="K51" s="272" t="s">
+      <c r="L55" s="268" t="s">
         <v>1183</v>
-      </c>
-      <c r="L51" s="272" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="52" spans="11:12">
-      <c r="K52" s="272" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="53" spans="11:12">
-      <c r="K53" s="272" t="s">
-        <v>1185</v>
-      </c>
-      <c r="L53" s="272" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="54" spans="11:12">
-      <c r="K54" s="272" t="s">
-        <v>1187</v>
-      </c>
-      <c r="L54" s="272" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="55" spans="11:12">
-      <c r="K55" s="272" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L55" s="272" t="s">
-        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -25830,7 +25830,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
@@ -25841,46 +25841,46 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C1" t="s">
         <v>1020</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1021</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>1024</v>
+        <v>1190</v>
       </c>
       <c r="B2" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="C2" s="137" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>1029</v>
+        <v>1191</v>
       </c>
       <c r="B4" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C4" t="s">
         <v>357</v>
@@ -25888,29 +25888,37 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B5" t="s">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="C5" s="149" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="B6" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1036</v>
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -25935,7 +25943,7 @@
         <v>360</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>361</v>
@@ -25944,12 +25952,12 @@
         <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="139" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="B2" s="139"/>
       <c r="C2" s="139"/>
@@ -25958,81 +25966,81 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="E6" s="99" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="C7" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1"/>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="C15" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -26040,7 +26048,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -26048,71 +26056,71 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="136" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="E19" s="99" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="140" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="E23" s="99" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="140" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="B30" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="C30" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="D30" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="E30" s="80" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75">
       <c r="A31" s="138" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4188" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1030B065-5EAF-4F68-8B39-3331C561EF00}"/>
+  <xr:revisionPtr revIDLastSave="4193" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F927425-297A-4389-928A-E99CF9897A67}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="36000" yWindow="75" windowWidth="21600" windowHeight="11295" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1196">
   <si>
     <t>Type</t>
   </si>
@@ -3700,6 +3700,12 @@
   </si>
   <si>
     <t>redesign the brush to reach nozzle on the volcano</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>redesign the AB motor cover so it can be locked</t>
   </si>
 </sst>
 </file>
@@ -4520,7 +4526,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
@@ -5136,6 +5142,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5586,6 +5593,170 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -6560,170 +6731,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <border>
@@ -7726,64 +7733,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J148" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J148" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J148" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J148">
     <sortCondition ref="A1:A148"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="82"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="79"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="78">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="96"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="95"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="93"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="92">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="77" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="75" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="91" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="90"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="89" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D51" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="23" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D51" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D51" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D51">
     <sortCondition ref="B1:B51"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="22" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="21" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="34" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:H92" totalsRowCount="1" headerRowDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:H92" totalsRowCount="1" headerRowDxfId="32">
   <autoFilter ref="A1:H91" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="100" totalsRowDxfId="99"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="29" totalsRowDxfId="28"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
-    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="96"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="93" totalsRowDxfId="92" dataCellStyle="Normal 7">
+    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="23" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7882,121 +7889,121 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72" tableBorderDxfId="71" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86" tableBorderDxfId="85" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Cut length" dataDxfId="68" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="BOM Quantity" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Cut length" dataDxfId="82" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="BOM Quantity" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="66" tableBorderDxfId="65" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="61" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D26" totalsRowShown="0" headerRowDxfId="60" tableBorderDxfId="59" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D26" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D26" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D26">
     <sortCondition ref="B1:B26"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="58" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="57" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="56" totalsRowDxfId="55" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="71" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B29:D39" totalsRowShown="0" headerRowDxfId="54" tableBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B29:D39" totalsRowShown="0" headerRowDxfId="68" tableBorderDxfId="67" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B29:D39" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B30:D39">
     <sortCondition ref="B29:B39"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="52" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="51" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="50" totalsRowDxfId="49" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D45" totalsRowShown="0" headerRowDxfId="48" tableBorderDxfId="47" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D45" totalsRowShown="0" headerRowDxfId="62" tableBorderDxfId="61" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D45" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D45">
     <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="44" totalsRowDxfId="43" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D74" totalsRowShown="0" headerRowDxfId="42" tableBorderDxfId="41" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D74" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D74" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D74">
     <sortCondition ref="B1:B74"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="38" totalsRowDxfId="37" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D44" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="35" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D44" totalsRowShown="0" headerRowDxfId="50" tableBorderDxfId="49" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="32" totalsRowDxfId="31" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="48" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D18" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D18" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D18" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D18">
     <sortCondition ref="B1:B18"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="28" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="27" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -25830,7 +25837,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
@@ -25919,6 +25926,22 @@
       </c>
       <c r="B9" t="s">
         <v>1029</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="286" t="s">
+        <v>1194</v>
       </c>
     </row>
   </sheetData>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4199" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6ABB91B-3233-431A-B8FD-7B18247611C9}"/>
+  <xr:revisionPtr revIDLastSave="4204" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C87BD04-987D-4233-A1EE-7DB819147CE4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1196">
   <si>
     <t>Type</t>
   </si>
@@ -3594,9 +3594,6 @@
     <t>redesign the AB motor cover so it can be fastened</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Quantity M</t>
   </si>
   <si>
@@ -3606,7 +3603,7 @@
     <t>Tools</t>
   </si>
   <si>
-    <t>Drill bits mm  6,5,4,3,4.2,1.3mm</t>
+    <t>Drill bits mm  6,5,4,3,4.2,1.5mm</t>
   </si>
   <si>
     <t xml:space="preserve">Taps M3,M6 </t>
@@ -3703,6 +3700,12 @@
   </si>
   <si>
     <t>to stick silicon heater  to aluminium bed</t>
+  </si>
+  <si>
+    <t>add a cpap fan fan</t>
+  </si>
+  <si>
+    <t>add a temp sensor to the cpap</t>
   </si>
 </sst>
 </file>
@@ -4516,7 +4519,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
@@ -5030,14 +5033,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="12" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="12"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5119,17 +5114,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="12" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -5137,6 +5124,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="12" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="12"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5457,13 +5456,6 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -5503,6 +5495,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5589,16 +5588,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5618,10 +5621,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5753,9 +5752,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5772,6 +5768,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5830,9 +5829,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5849,6 +5845,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5907,9 +5906,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5926,6 +5922,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5984,9 +5983,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6003,6 +5999,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6061,9 +6060,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6080,6 +6076,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6138,9 +6137,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6157,6 +6153,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6231,9 +6230,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6250,6 +6246,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6308,9 +6307,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6327,6 +6323,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6686,13 +6685,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -6717,6 +6709,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -7727,7 +7726,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J148" totalsRowShown="0" headerRowDxfId="101" dataDxfId="100" headerRowBorderDxfId="98" tableBorderDxfId="99" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J148" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J148" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J148">
     <sortCondition ref="A1:A148"/>
@@ -7759,7 +7758,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="33" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="34" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7772,19 +7771,19 @@
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="30" totalsRowDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="28" totalsRowDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="29" totalsRowDxfId="28"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
     <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="26" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="24" dataCellStyle="Normal 7">
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="23" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="22">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7846,7 +7845,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
   <autoFilter ref="A4:L37" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7907,7 +7906,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="75" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7922,7 +7921,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="71" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="69" totalsRowDxfId="70" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7937,7 +7936,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="63" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7952,7 +7951,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="57" totalsRowDxfId="58" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7967,7 +7966,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="51" totalsRowDxfId="52" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7982,7 +7981,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="48" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="45" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7997,7 +7996,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="39" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8225,31 +8224,31 @@
       <c r="A1" s="191" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="245" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="245" t="s">
+      <c r="B1" s="241" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="245" t="s">
+      <c r="D1" s="241" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="245" t="s">
+      <c r="E1" s="241" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="245" t="s">
+      <c r="F1" s="241" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="246" t="s">
+      <c r="G1" s="242" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="247" t="s">
+      <c r="H1" s="243" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="248" t="s">
+      <c r="I1" s="244" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="248" t="s">
+      <c r="J1" s="244" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8350,7 +8349,7 @@
       <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="249" t="s">
+      <c r="B5" s="245" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="159">
@@ -8381,7 +8380,7 @@
       <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="250" t="s">
+      <c r="B6" s="246" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="160">
@@ -8412,7 +8411,7 @@
       <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="250" t="s">
+      <c r="B7" s="246" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="160">
@@ -8443,7 +8442,7 @@
       <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="251" t="s">
+      <c r="B8" s="247" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="161">
@@ -8474,7 +8473,7 @@
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="249" t="s">
+      <c r="B9" s="245" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="161">
@@ -8493,7 +8492,7 @@
       <c r="G9" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="252" t="s">
+      <c r="H9" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="204">
@@ -8524,7 +8523,7 @@
       <c r="G10" s="150" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="252" t="s">
+      <c r="H10" s="248" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="204">
@@ -8598,10 +8597,10 @@
       <c r="A13" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="253" t="s">
+      <c r="B13" s="249" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="254">
+      <c r="C13" s="250">
         <v>1</v>
       </c>
       <c r="D13" s="156">
@@ -8617,7 +8616,7 @@
       <c r="G13" s="150" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="255" t="s">
+      <c r="H13" s="251" t="s">
         <v>42</v>
       </c>
       <c r="I13" s="204">
@@ -8629,7 +8628,7 @@
       <c r="A14" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="250" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="9">
@@ -8638,7 +8637,7 @@
       <c r="D14" s="156">
         <v>1</v>
       </c>
-      <c r="E14" s="254">
+      <c r="E14" s="250">
         <v>2.3199999999999998</v>
       </c>
       <c r="F14" s="157">
@@ -8648,7 +8647,7 @@
       <c r="G14" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="255" t="s">
+      <c r="H14" s="251" t="s">
         <v>45</v>
       </c>
       <c r="I14" s="204">
@@ -8660,7 +8659,7 @@
       <c r="A15" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="250" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="9">
@@ -8669,7 +8668,7 @@
       <c r="D15" s="156">
         <v>1</v>
       </c>
-      <c r="E15" s="256">
+      <c r="E15" s="252">
         <v>4.82</v>
       </c>
       <c r="F15" s="157">
@@ -8679,7 +8678,7 @@
       <c r="G15" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="257" t="s">
+      <c r="H15" s="253" t="s">
         <v>45</v>
       </c>
       <c r="I15" s="204">
@@ -8710,7 +8709,7 @@
       <c r="G16" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="257" t="s">
+      <c r="H16" s="253" t="s">
         <v>45</v>
       </c>
       <c r="I16" s="205">
@@ -8731,7 +8730,7 @@
       <c r="D17" s="156">
         <v>1</v>
       </c>
-      <c r="E17" s="256">
+      <c r="E17" s="252">
         <v>10</v>
       </c>
       <c r="F17" s="157">
@@ -8741,7 +8740,7 @@
       <c r="G17" s="150" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="257" t="s">
+      <c r="H17" s="253" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="204">
@@ -8753,10 +8752,10 @@
       <c r="A18" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="258" t="s">
+      <c r="B18" s="254" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="258">
+      <c r="C18" s="254">
         <v>1</v>
       </c>
       <c r="D18" s="156">
@@ -8772,7 +8771,7 @@
       <c r="G18" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="252" t="s">
+      <c r="H18" s="248" t="s">
         <v>45</v>
       </c>
       <c r="I18" s="204">
@@ -8787,7 +8786,7 @@
       <c r="B19" s="165" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="258">
+      <c r="C19" s="254">
         <v>1</v>
       </c>
       <c r="D19" s="156">
@@ -8803,7 +8802,7 @@
       <c r="G19" s="150" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="252" t="s">
+      <c r="H19" s="248" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="204">
@@ -8834,7 +8833,7 @@
       <c r="G20" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="252" t="s">
+      <c r="H20" s="248" t="s">
         <v>45</v>
       </c>
       <c r="I20" s="205"/>
@@ -8844,7 +8843,7 @@
       <c r="A21" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="250" t="s">
+      <c r="B21" s="246" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="43">
@@ -8863,7 +8862,7 @@
       <c r="G21" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="259" t="s">
+      <c r="H21" s="255" t="s">
         <v>60</v>
       </c>
       <c r="I21" s="205"/>
@@ -8873,7 +8872,7 @@
       <c r="A22" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="258" t="s">
+      <c r="B22" s="254" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="43">
@@ -8892,7 +8891,7 @@
       <c r="G22" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="252" t="s">
+      <c r="H22" s="248" t="s">
         <v>63</v>
       </c>
       <c r="I22" s="204">
@@ -8904,7 +8903,7 @@
       <c r="A23" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="249" t="s">
+      <c r="B23" s="245" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="155">
@@ -8923,7 +8922,7 @@
       <c r="G23" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="H23" s="252" t="s">
+      <c r="H23" s="248" t="s">
         <v>66</v>
       </c>
       <c r="I23" s="204">
@@ -9000,13 +8999,13 @@
       <c r="B26" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="254">
+      <c r="C26" s="250">
         <v>1</v>
       </c>
       <c r="D26" s="156">
         <v>1</v>
       </c>
-      <c r="E26" s="256">
+      <c r="E26" s="252">
         <v>16</v>
       </c>
       <c r="F26" s="157">
@@ -9124,7 +9123,7 @@
       <c r="B30" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="260">
+      <c r="C30" s="256">
         <v>2</v>
       </c>
       <c r="D30" s="156">
@@ -9152,10 +9151,10 @@
       <c r="A31" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="253" t="s">
+      <c r="B31" s="249" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="260">
+      <c r="C31" s="256">
         <v>5</v>
       </c>
       <c r="D31" s="156">
@@ -9186,7 +9185,7 @@
       <c r="B32" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="260">
+      <c r="C32" s="256">
         <v>2</v>
       </c>
       <c r="D32" s="156">
@@ -9248,7 +9247,7 @@
       <c r="B34" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="260">
+      <c r="C34" s="256">
         <v>2</v>
       </c>
       <c r="D34" s="156">
@@ -9307,7 +9306,7 @@
       <c r="A36" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="254" t="s">
+      <c r="B36" s="250" t="s">
         <v>94</v>
       </c>
       <c r="C36" s="9">
@@ -9341,7 +9340,7 @@
       <c r="B37" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="260">
+      <c r="C37" s="256">
         <v>2</v>
       </c>
       <c r="D37" s="156">
@@ -9372,7 +9371,7 @@
       <c r="B38" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="260">
+      <c r="C38" s="256">
         <v>5</v>
       </c>
       <c r="D38" s="156">
@@ -9400,10 +9399,10 @@
       <c r="A39" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="254" t="s">
+      <c r="B39" s="250" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="260">
+      <c r="C39" s="256">
         <v>5</v>
       </c>
       <c r="D39" s="156">
@@ -9431,10 +9430,10 @@
       <c r="A40" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="250" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="260">
+      <c r="C40" s="256">
         <v>5</v>
       </c>
       <c r="D40" s="156">
@@ -9493,7 +9492,7 @@
       <c r="A42" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="253" t="s">
+      <c r="B42" s="249" t="s">
         <v>105</v>
       </c>
       <c r="C42" s="9">
@@ -9636,7 +9635,7 @@
       <c r="G46" s="150" t="s">
         <v>112</v>
       </c>
-      <c r="H46" s="252" t="s">
+      <c r="H46" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="204">
@@ -9667,7 +9666,7 @@
       <c r="G47" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="H47" s="252" t="s">
+      <c r="H47" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="204">
@@ -9698,7 +9697,7 @@
       <c r="G48" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="H48" s="252" t="s">
+      <c r="H48" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="205">
@@ -9721,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="224"/>
-      <c r="H49" s="286"/>
+      <c r="H49" s="279"/>
       <c r="I49" s="225"/>
       <c r="J49" s="226"/>
     </row>
@@ -9729,7 +9728,7 @@
       <c r="A50" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="251" t="s">
+      <c r="B50" s="247" t="s">
         <v>119</v>
       </c>
       <c r="C50" s="161">
@@ -9748,7 +9747,7 @@
       <c r="G50" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="H50" s="252" t="s">
+      <c r="H50" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I50" s="204">
@@ -9779,7 +9778,7 @@
       <c r="G51" s="150" t="s">
         <v>121</v>
       </c>
-      <c r="H51" s="255" t="s">
+      <c r="H51" s="251" t="s">
         <v>30</v>
       </c>
       <c r="I51" s="204">
@@ -9791,7 +9790,7 @@
       <c r="A52" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B52" s="251" t="s">
+      <c r="B52" s="247" t="s">
         <v>122</v>
       </c>
       <c r="C52" s="43">
@@ -9810,7 +9809,7 @@
       <c r="G52" s="150" t="s">
         <v>123</v>
       </c>
-      <c r="H52" s="252" t="s">
+      <c r="H52" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="204">
@@ -9946,7 +9945,7 @@
       <c r="A57" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B57" s="250" t="s">
+      <c r="B57" s="246" t="s">
         <v>133</v>
       </c>
       <c r="C57" s="160">
@@ -9977,7 +9976,7 @@
       <c r="A58" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="250" t="s">
+      <c r="B58" s="246" t="s">
         <v>136</v>
       </c>
       <c r="C58" s="160">
@@ -10008,16 +10007,16 @@
       <c r="A59" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="254" t="s">
+      <c r="B59" s="250" t="s">
         <v>138</v>
       </c>
-      <c r="C59" s="254">
+      <c r="C59" s="250">
         <v>1</v>
       </c>
       <c r="D59" s="156">
         <v>1</v>
       </c>
-      <c r="E59" s="256">
+      <c r="E59" s="252">
         <v>33.700000000000003</v>
       </c>
       <c r="F59" s="157">
@@ -10058,7 +10057,7 @@
       <c r="G60" s="150" t="s">
         <v>141</v>
       </c>
-      <c r="H60" s="252" t="s">
+      <c r="H60" s="248" t="s">
         <v>142</v>
       </c>
       <c r="I60" s="204">
@@ -10089,7 +10088,7 @@
       <c r="G61" s="150" t="s">
         <v>144</v>
       </c>
-      <c r="H61" s="261" t="s">
+      <c r="H61" s="257" t="s">
         <v>145</v>
       </c>
       <c r="I61" s="204">
@@ -10120,7 +10119,7 @@
       <c r="G62" s="150" t="s">
         <v>147</v>
       </c>
-      <c r="H62" s="252" t="s">
+      <c r="H62" s="248" t="s">
         <v>148</v>
       </c>
       <c r="I62" s="204">
@@ -10132,10 +10131,10 @@
       <c r="A63" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B63" s="254" t="s">
+      <c r="B63" s="250" t="s">
         <v>149</v>
       </c>
-      <c r="C63" s="254">
+      <c r="C63" s="250">
         <v>1</v>
       </c>
       <c r="D63" s="156">
@@ -10151,7 +10150,7 @@
       <c r="G63" s="150" t="s">
         <v>150</v>
       </c>
-      <c r="H63" s="255" t="s">
+      <c r="H63" s="251" t="s">
         <v>151</v>
       </c>
       <c r="I63" s="204">
@@ -10163,7 +10162,7 @@
       <c r="A64" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="250" t="s">
+      <c r="B64" s="246" t="s">
         <v>152</v>
       </c>
       <c r="C64" s="43">
@@ -10182,7 +10181,7 @@
       <c r="G64" s="150" t="s">
         <v>153</v>
       </c>
-      <c r="H64" s="255" t="s">
+      <c r="H64" s="251" t="s">
         <v>154</v>
       </c>
       <c r="I64" s="204">
@@ -10194,7 +10193,7 @@
       <c r="A65" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B65" s="250" t="s">
+      <c r="B65" s="246" t="s">
         <v>155</v>
       </c>
       <c r="C65" s="43">
@@ -10213,7 +10212,7 @@
       <c r="G65" s="150" t="s">
         <v>156</v>
       </c>
-      <c r="H65" s="255" t="s">
+      <c r="H65" s="251" t="s">
         <v>154</v>
       </c>
       <c r="I65" s="205">
@@ -10225,7 +10224,7 @@
       <c r="A66" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="250" t="s">
+      <c r="B66" s="246" t="s">
         <v>157</v>
       </c>
       <c r="C66" s="43">
@@ -10244,7 +10243,7 @@
       <c r="G66" s="150" t="s">
         <v>158</v>
       </c>
-      <c r="H66" s="255" t="s">
+      <c r="H66" s="251" t="s">
         <v>154</v>
       </c>
       <c r="I66" s="205">
@@ -10256,7 +10255,7 @@
       <c r="A67" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="254" t="s">
+      <c r="B67" s="250" t="s">
         <v>159</v>
       </c>
       <c r="C67" s="9">
@@ -10275,7 +10274,7 @@
       <c r="G67" s="150" t="s">
         <v>160</v>
       </c>
-      <c r="H67" s="255" t="s">
+      <c r="H67" s="251" t="s">
         <v>154</v>
       </c>
       <c r="I67" s="204">
@@ -10339,7 +10338,7 @@
       <c r="G69" s="150" t="s">
         <v>166</v>
       </c>
-      <c r="H69" s="252" t="s">
+      <c r="H69" s="248" t="s">
         <v>167</v>
       </c>
       <c r="I69" s="204">
@@ -10370,7 +10369,7 @@
       <c r="G70" s="150" t="s">
         <v>169</v>
       </c>
-      <c r="H70" s="252" t="s">
+      <c r="H70" s="248" t="s">
         <v>167</v>
       </c>
       <c r="I70" s="204">
@@ -10811,7 +10810,7 @@
       <c r="A84" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="249" t="s">
+      <c r="B84" s="245" t="s">
         <v>195</v>
       </c>
       <c r="C84" s="141">
@@ -10844,7 +10843,7 @@
       <c r="A85" s="141" t="s">
         <v>161</v>
       </c>
-      <c r="B85" s="258" t="s">
+      <c r="B85" s="254" t="s">
         <v>197</v>
       </c>
       <c r="C85" s="141">
@@ -10877,7 +10876,7 @@
       <c r="A86" s="141" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="249" t="s">
+      <c r="B86" s="245" t="s">
         <v>199</v>
       </c>
       <c r="C86" s="141">
@@ -11141,7 +11140,7 @@
       <c r="A94" s="141" t="s">
         <v>161</v>
       </c>
-      <c r="B94" s="250" t="s">
+      <c r="B94" s="246" t="s">
         <v>215</v>
       </c>
       <c r="C94" s="160">
@@ -11174,7 +11173,7 @@
       <c r="A95" s="141" t="s">
         <v>161</v>
       </c>
-      <c r="B95" s="250" t="s">
+      <c r="B95" s="246" t="s">
         <v>217</v>
       </c>
       <c r="C95" s="160">
@@ -11207,7 +11206,7 @@
       <c r="A96" s="141" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="250" t="s">
+      <c r="B96" s="246" t="s">
         <v>219</v>
       </c>
       <c r="C96" s="160">
@@ -11306,7 +11305,7 @@
       <c r="A99" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B99" s="254" t="s">
+      <c r="B99" s="250" t="s">
         <v>226</v>
       </c>
       <c r="C99" s="155">
@@ -11391,7 +11390,7 @@
       <c r="G101" s="151" t="s">
         <v>231</v>
       </c>
-      <c r="H101" s="252" t="s">
+      <c r="H101" s="248" t="s">
         <v>225</v>
       </c>
       <c r="I101" s="204">
@@ -11457,7 +11456,7 @@
       <c r="G103" s="151" t="s">
         <v>236</v>
       </c>
-      <c r="H103" s="252" t="s">
+      <c r="H103" s="248" t="s">
         <v>237</v>
       </c>
       <c r="I103" s="204">
@@ -11488,7 +11487,7 @@
       <c r="G104" s="151" t="s">
         <v>239</v>
       </c>
-      <c r="H104" s="252" t="s">
+      <c r="H104" s="248" t="s">
         <v>237</v>
       </c>
       <c r="I104" s="204"/>
@@ -11548,7 +11547,7 @@
       <c r="G106" s="151" t="s">
         <v>243</v>
       </c>
-      <c r="H106" s="252" t="s">
+      <c r="H106" s="248" t="s">
         <v>237</v>
       </c>
       <c r="I106" s="204">
@@ -11579,7 +11578,7 @@
       <c r="G107" s="151" t="s">
         <v>245</v>
       </c>
-      <c r="H107" s="252" t="s">
+      <c r="H107" s="248" t="s">
         <v>237</v>
       </c>
       <c r="I107" s="204">
@@ -11610,7 +11609,7 @@
       <c r="G108" s="152" t="s">
         <v>248</v>
       </c>
-      <c r="H108" s="252" t="s">
+      <c r="H108" s="248" t="s">
         <v>249</v>
       </c>
       <c r="I108" s="204"/>
@@ -11639,7 +11638,7 @@
       <c r="G109" s="152" t="s">
         <v>251</v>
       </c>
-      <c r="H109" s="252" t="s">
+      <c r="H109" s="248" t="s">
         <v>252</v>
       </c>
       <c r="I109" s="204">
@@ -11701,7 +11700,7 @@
       <c r="G111" s="151" t="s">
         <v>257</v>
       </c>
-      <c r="H111" s="252" t="s">
+      <c r="H111" s="248" t="s">
         <v>225</v>
       </c>
       <c r="I111" s="204">
@@ -11732,7 +11731,7 @@
       <c r="G112" s="150" t="s">
         <v>260</v>
       </c>
-      <c r="H112" s="252" t="s">
+      <c r="H112" s="248" t="s">
         <v>261</v>
       </c>
       <c r="I112" s="204">
@@ -11806,7 +11805,7 @@
       <c r="A115" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B115" s="253" t="s">
+      <c r="B115" s="249" t="s">
         <v>268</v>
       </c>
       <c r="C115" s="180">
@@ -11825,7 +11824,7 @@
       <c r="G115" s="152" t="s">
         <v>269</v>
       </c>
-      <c r="H115" s="252" t="s">
+      <c r="H115" s="248" t="s">
         <v>270</v>
       </c>
       <c r="I115" s="204">
@@ -11837,7 +11836,7 @@
       <c r="A116" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="253" t="s">
+      <c r="B116" s="249" t="s">
         <v>271</v>
       </c>
       <c r="C116" s="180">
@@ -11856,7 +11855,7 @@
       <c r="G116" s="152" t="s">
         <v>272</v>
       </c>
-      <c r="H116" s="252" t="s">
+      <c r="H116" s="248" t="s">
         <v>273</v>
       </c>
       <c r="I116" s="204">
@@ -11887,7 +11886,7 @@
       <c r="G117" s="150" t="s">
         <v>275</v>
       </c>
-      <c r="H117" s="252" t="s">
+      <c r="H117" s="248" t="s">
         <v>276</v>
       </c>
       <c r="I117" s="204">
@@ -11899,7 +11898,7 @@
       <c r="A118" s="141" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="253" t="s">
+      <c r="B118" s="249" t="s">
         <v>277</v>
       </c>
       <c r="C118" s="180">
@@ -11918,7 +11917,7 @@
       <c r="G118" s="150" t="s">
         <v>278</v>
       </c>
-      <c r="H118" s="252" t="s">
+      <c r="H118" s="248" t="s">
         <v>276</v>
       </c>
       <c r="I118" s="204">
@@ -11930,7 +11929,7 @@
       <c r="A119" s="141" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="251" t="s">
+      <c r="B119" s="247" t="s">
         <v>279</v>
       </c>
       <c r="C119" s="181">
@@ -11949,7 +11948,7 @@
       <c r="G119" s="152" t="s">
         <v>280</v>
       </c>
-      <c r="H119" s="252" t="s">
+      <c r="H119" s="248" t="s">
         <v>281</v>
       </c>
       <c r="I119" s="204">
@@ -11961,7 +11960,7 @@
       <c r="A120" s="141" t="s">
         <v>282</v>
       </c>
-      <c r="B120" s="262" t="s">
+      <c r="B120" s="258" t="s">
         <v>283</v>
       </c>
       <c r="C120" s="182">
@@ -11980,7 +11979,7 @@
       <c r="G120" s="152" t="s">
         <v>284</v>
       </c>
-      <c r="H120" s="255" t="s">
+      <c r="H120" s="251" t="s">
         <v>285</v>
       </c>
       <c r="I120" s="204">
@@ -11992,7 +11991,7 @@
       <c r="A121" s="141" t="s">
         <v>282</v>
       </c>
-      <c r="B121" s="250" t="s">
+      <c r="B121" s="246" t="s">
         <v>286</v>
       </c>
       <c r="C121" s="160">
@@ -12011,7 +12010,7 @@
       <c r="G121" s="152" t="s">
         <v>287</v>
       </c>
-      <c r="H121" s="255" t="s">
+      <c r="H121" s="251" t="s">
         <v>285</v>
       </c>
       <c r="I121" s="204">
@@ -12042,7 +12041,7 @@
       <c r="G122" s="150" t="s">
         <v>289</v>
       </c>
-      <c r="H122" s="255" t="s">
+      <c r="H122" s="251" t="s">
         <v>285</v>
       </c>
       <c r="I122" s="204">
@@ -12073,7 +12072,7 @@
       <c r="G123" s="152" t="s">
         <v>291</v>
       </c>
-      <c r="H123" s="252" t="s">
+      <c r="H123" s="248" t="s">
         <v>292</v>
       </c>
       <c r="I123" s="204">
@@ -12104,7 +12103,7 @@
       <c r="G124" s="152" t="s">
         <v>294</v>
       </c>
-      <c r="H124" s="252" t="s">
+      <c r="H124" s="248" t="s">
         <v>295</v>
       </c>
       <c r="I124" s="204">
@@ -12135,7 +12134,7 @@
       <c r="G125" s="152" t="s">
         <v>297</v>
       </c>
-      <c r="H125" s="252" t="s">
+      <c r="H125" s="248" t="s">
         <v>295</v>
       </c>
       <c r="I125" s="204">
@@ -12166,7 +12165,7 @@
       <c r="G126" s="152" t="s">
         <v>299</v>
       </c>
-      <c r="H126" s="252" t="s">
+      <c r="H126" s="248" t="s">
         <v>295</v>
       </c>
       <c r="I126" s="204">
@@ -12197,7 +12196,7 @@
       <c r="G127" s="152" t="s">
         <v>301</v>
       </c>
-      <c r="H127" s="252" t="s">
+      <c r="H127" s="248" t="s">
         <v>295</v>
       </c>
       <c r="I127" s="204">
@@ -12228,7 +12227,7 @@
       <c r="G128" s="152" t="s">
         <v>303</v>
       </c>
-      <c r="H128" s="252" t="s">
+      <c r="H128" s="248" t="s">
         <v>295</v>
       </c>
       <c r="I128" s="204">
@@ -12259,7 +12258,7 @@
       <c r="G129" s="152" t="s">
         <v>305</v>
       </c>
-      <c r="H129" s="252" t="s">
+      <c r="H129" s="248" t="s">
         <v>295</v>
       </c>
       <c r="I129" s="204">
@@ -12290,7 +12289,7 @@
       <c r="G130" s="152" t="s">
         <v>307</v>
       </c>
-      <c r="H130" s="252" t="s">
+      <c r="H130" s="248" t="s">
         <v>308</v>
       </c>
       <c r="I130" s="204">
@@ -12321,7 +12320,7 @@
       <c r="G131" s="153" t="s">
         <v>310</v>
       </c>
-      <c r="H131" s="252" t="s">
+      <c r="H131" s="248" t="s">
         <v>311</v>
       </c>
       <c r="I131" s="204">
@@ -12352,7 +12351,7 @@
       <c r="G132" s="152" t="s">
         <v>313</v>
       </c>
-      <c r="H132" s="252" t="s">
+      <c r="H132" s="248" t="s">
         <v>314</v>
       </c>
       <c r="I132" s="204">
@@ -12395,7 +12394,7 @@
       <c r="A134" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B134" s="250" t="s">
+      <c r="B134" s="246" t="s">
         <v>319</v>
       </c>
       <c r="C134" s="155">
@@ -12414,7 +12413,7 @@
       <c r="G134" s="152" t="s">
         <v>320</v>
       </c>
-      <c r="H134" s="252" t="s">
+      <c r="H134" s="248" t="s">
         <v>321</v>
       </c>
       <c r="I134" s="204">
@@ -12426,7 +12425,7 @@
       <c r="A135" s="141" t="s">
         <v>315</v>
       </c>
-      <c r="B135" s="250" t="s">
+      <c r="B135" s="246" t="s">
         <v>322</v>
       </c>
       <c r="C135" s="155">
@@ -12445,7 +12444,7 @@
       <c r="G135" s="152" t="s">
         <v>323</v>
       </c>
-      <c r="H135" s="252" t="s">
+      <c r="H135" s="248" t="s">
         <v>321</v>
       </c>
       <c r="I135" s="204">
@@ -12457,7 +12456,7 @@
       <c r="A136" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B136" s="250" t="s">
+      <c r="B136" s="246" t="s">
         <v>324</v>
       </c>
       <c r="C136" s="155">
@@ -12476,7 +12475,7 @@
       <c r="G136" s="152" t="s">
         <v>325</v>
       </c>
-      <c r="H136" s="252" t="s">
+      <c r="H136" s="248" t="s">
         <v>321</v>
       </c>
       <c r="I136" s="204">
@@ -12488,7 +12487,7 @@
       <c r="A137" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B137" s="250" t="s">
+      <c r="B137" s="246" t="s">
         <v>326</v>
       </c>
       <c r="C137" s="155">
@@ -12507,7 +12506,7 @@
       <c r="G137" s="152" t="s">
         <v>327</v>
       </c>
-      <c r="H137" s="252" t="s">
+      <c r="H137" s="248" t="s">
         <v>321</v>
       </c>
       <c r="I137" s="204">
@@ -12538,7 +12537,7 @@
       <c r="G138" s="152" t="s">
         <v>329</v>
       </c>
-      <c r="H138" s="252" t="s">
+      <c r="H138" s="248" t="s">
         <v>330</v>
       </c>
       <c r="I138" s="204">
@@ -12581,7 +12580,7 @@
       <c r="A140" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B140" s="251" t="s">
+      <c r="B140" s="247" t="s">
         <v>336</v>
       </c>
       <c r="C140" s="161">
@@ -12600,7 +12599,7 @@
       <c r="G140" s="152" t="s">
         <v>337</v>
       </c>
-      <c r="H140" s="252" t="s">
+      <c r="H140" s="248" t="s">
         <v>338</v>
       </c>
       <c r="I140" s="204">
@@ -12612,7 +12611,7 @@
       <c r="A141" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B141" s="251" t="s">
+      <c r="B141" s="247" t="s">
         <v>339</v>
       </c>
       <c r="C141" s="43">
@@ -12631,7 +12630,7 @@
       <c r="G141" s="152" t="s">
         <v>340</v>
       </c>
-      <c r="H141" s="252" t="s">
+      <c r="H141" s="248" t="s">
         <v>341</v>
       </c>
       <c r="I141" s="205">
@@ -12693,7 +12692,7 @@
       <c r="G143" s="152" t="s">
         <v>346</v>
       </c>
-      <c r="H143" s="252" t="s">
+      <c r="H143" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I143" s="204">
@@ -12724,7 +12723,7 @@
       <c r="G144" s="152" t="s">
         <v>348</v>
       </c>
-      <c r="H144" s="252" t="s">
+      <c r="H144" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I144" s="204">
@@ -12755,7 +12754,7 @@
       <c r="G145" s="152" t="s">
         <v>350</v>
       </c>
-      <c r="H145" s="252" t="s">
+      <c r="H145" s="248" t="s">
         <v>30</v>
       </c>
       <c r="I145" s="204">
@@ -12817,7 +12816,7 @@
       <c r="G147" s="152" t="s">
         <v>354</v>
       </c>
-      <c r="H147" s="252" t="s">
+      <c r="H147" s="248" t="s">
         <v>355</v>
       </c>
       <c r="I147" s="204">
@@ -12875,13 +12874,13 @@
     </row>
     <row r="150" spans="1:10">
       <c r="F150" s="8"/>
-      <c r="J150" s="263"/>
+      <c r="J150" s="259"/>
     </row>
     <row r="151" spans="1:10">
-      <c r="J151" s="263"/>
+      <c r="J151" s="259"/>
     </row>
     <row r="152" spans="1:10">
-      <c r="J152" s="263"/>
+      <c r="J152" s="259"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15169,7 +15168,7 @@
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="287" t="s">
+      <c r="A93" s="280" t="s">
         <v>677</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -15718,33 +15717,15 @@
       <c r="A1" s="107" t="s">
         <v>784</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="108" t="s">
         <v>785</v>
       </c>
-      <c r="B2" s="242"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:12" s="106" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="127"/>
@@ -16907,7 +16888,6 @@
       <c r="L33" s="123">
         <v>2050</v>
       </c>
-      <c r="M33" s="241"/>
     </row>
     <row r="34" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="129" t="s">
@@ -16944,7 +16924,6 @@
       <c r="L34" s="123">
         <v>2100</v>
       </c>
-      <c r="M34" s="241"/>
     </row>
     <row r="35" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="129" t="s">
@@ -16981,7 +16960,6 @@
       <c r="L35" s="123">
         <v>100</v>
       </c>
-      <c r="M35" s="241"/>
     </row>
     <row r="36" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="121" t="s">
@@ -17020,7 +16998,6 @@
       <c r="L36" s="123">
         <v>3000</v>
       </c>
-      <c r="M36" s="241"/>
     </row>
     <row r="37" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="121" t="s">
@@ -17057,7 +17034,6 @@
       <c r="L37" s="123">
         <v>2200</v>
       </c>
-      <c r="M37" s="241"/>
     </row>
     <row r="38" spans="1:13" s="106" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="111"/>
@@ -17078,29 +17054,15 @@
       <c r="A39" s="109" t="s">
         <v>840</v>
       </c>
-      <c r="B39" s="244"/>
-      <c r="C39" s="244"/>
-      <c r="D39" s="242"/>
-      <c r="E39" s="242"/>
-      <c r="F39" s="242"/>
-      <c r="G39" s="242"/>
-      <c r="H39" s="242"/>
-      <c r="I39" s="242"/>
-      <c r="J39" s="242"/>
+      <c r="B39" s="278"/>
+      <c r="C39" s="278"/>
       <c r="K39" s="115"/>
       <c r="L39" s="115"/>
       <c r="M39" s="116"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B40" s="244"/>
-      <c r="C40" s="244"/>
-      <c r="D40" s="242"/>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="242"/>
-      <c r="H40" s="242"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
+      <c r="B40" s="278"/>
+      <c r="C40" s="278"/>
       <c r="K40" s="115"/>
       <c r="L40" s="115"/>
       <c r="M40" s="116"/>
@@ -17119,92 +17081,50 @@
       <c r="I41" s="285"/>
       <c r="J41" s="285"/>
       <c r="K41" s="285"/>
-      <c r="L41" s="242"/>
       <c r="M41" s="116"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="244" t="s">
+      <c r="A42" s="278" t="s">
         <v>842</v>
       </c>
-      <c r="B42" s="242"/>
-      <c r="C42" s="242"/>
-      <c r="D42" s="242"/>
-      <c r="E42" s="242"/>
-      <c r="F42" s="242"/>
-      <c r="G42" s="242"/>
-      <c r="H42" s="242"/>
-      <c r="I42" s="242"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
       <c r="J42" s="115"/>
-      <c r="K42" s="242"/>
-      <c r="L42" s="242"/>
       <c r="M42" s="116"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="244" t="s">
+      <c r="A43" s="278" t="s">
         <v>843</v>
       </c>
-      <c r="B43" s="242"/>
-      <c r="C43" s="242"/>
-      <c r="D43" s="242"/>
-      <c r="E43" s="242"/>
-      <c r="F43" s="242"/>
-      <c r="G43" s="242"/>
-      <c r="H43" s="242"/>
-      <c r="I43" s="242"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
       <c r="J43" s="115"/>
-      <c r="K43" s="242"/>
-      <c r="L43" s="242"/>
       <c r="M43" s="116"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="244" t="s">
+      <c r="A44" s="278" t="s">
         <v>844</v>
       </c>
-      <c r="B44" s="242"/>
-      <c r="C44" s="242"/>
-      <c r="D44" s="242"/>
-      <c r="E44" s="242"/>
-      <c r="F44" s="242"/>
-      <c r="G44" s="242"/>
-      <c r="H44" s="242"/>
-      <c r="I44" s="242"/>
-      <c r="J44" s="242"/>
-      <c r="K44" s="242"/>
-      <c r="L44" s="242"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
       <c r="M44" s="116"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="244" t="s">
+      <c r="A45" s="278" t="s">
         <v>845</v>
       </c>
-      <c r="B45" s="242"/>
-      <c r="C45" s="242"/>
-      <c r="D45" s="242"/>
-      <c r="E45" s="242"/>
-      <c r="F45" s="242"/>
-      <c r="G45" s="242"/>
-      <c r="H45" s="242"/>
-      <c r="I45" s="242"/>
-      <c r="J45" s="242"/>
-      <c r="K45" s="242"/>
-      <c r="L45" s="242"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
       <c r="M45" s="116"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="244" t="s">
+      <c r="A46" s="278" t="s">
         <v>846</v>
       </c>
-      <c r="B46" s="242"/>
-      <c r="C46" s="242"/>
-      <c r="D46" s="242"/>
-      <c r="E46" s="242"/>
-      <c r="F46" s="242"/>
-      <c r="G46" s="242"/>
-      <c r="H46" s="242"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
       <c r="I46" s="115"/>
       <c r="J46" s="115"/>
-      <c r="K46" s="242"/>
-      <c r="L46" s="242"/>
       <c r="M46" s="116"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
@@ -17216,16 +17136,13 @@
       <c r="D47" s="117"/>
       <c r="E47" s="118"/>
       <c r="F47" s="118"/>
-      <c r="G47" s="281"/>
+      <c r="G47" s="277"/>
       <c r="H47" s="117"/>
       <c r="I47" s="117"/>
       <c r="J47" s="117"/>
-      <c r="K47" s="242"/>
-      <c r="L47" s="242"/>
       <c r="M47" s="116"/>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D48" s="242"/>
       <c r="E48" s="120"/>
       <c r="F48" s="120"/>
       <c r="G48" s="120"/>
@@ -17240,7 +17157,6 @@
       <c r="A49" s="131" t="s">
         <v>848</v>
       </c>
-      <c r="D49" s="242"/>
       <c r="E49" s="120"/>
       <c r="F49" s="120"/>
       <c r="G49" s="120"/>
@@ -17255,7 +17171,6 @@
       <c r="A50" s="131" t="s">
         <v>849</v>
       </c>
-      <c r="D50" s="242"/>
       <c r="E50" s="120"/>
       <c r="F50" s="120"/>
       <c r="G50" s="120"/>
@@ -17267,8 +17182,7 @@
       <c r="M50" s="116"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="288"/>
-      <c r="D51" s="242"/>
+      <c r="A51" s="281"/>
       <c r="E51" s="120"/>
       <c r="F51" s="120"/>
       <c r="G51" s="120"/>
@@ -17281,7 +17195,6 @@
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
       <c r="A52" s="132"/>
-      <c r="D52" s="242"/>
       <c r="E52" s="120"/>
       <c r="F52" s="120"/>
       <c r="G52" s="120"/>
@@ -17293,7 +17206,6 @@
       <c r="M52" s="116"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D53" s="242"/>
       <c r="E53" s="120"/>
       <c r="F53" s="120"/>
       <c r="G53" s="120"/>
@@ -17305,7 +17217,6 @@
       <c r="M53" s="116"/>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D54" s="242"/>
       <c r="E54" s="120"/>
       <c r="F54" s="120"/>
       <c r="G54" s="120"/>
@@ -17317,7 +17228,6 @@
       <c r="M54" s="116"/>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D55" s="242"/>
       <c r="E55" s="120"/>
       <c r="F55" s="120"/>
       <c r="G55" s="120"/>
@@ -17329,7 +17239,6 @@
       <c r="M55" s="116"/>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D56" s="242"/>
       <c r="E56" s="120"/>
       <c r="F56" s="120"/>
       <c r="G56" s="120"/>
@@ -17341,7 +17250,6 @@
       <c r="M56" s="116"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D57" s="242"/>
       <c r="E57" s="120"/>
       <c r="F57" s="120"/>
       <c r="G57" s="120"/>
@@ -17353,7 +17261,6 @@
       <c r="M57" s="116"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D58" s="242"/>
       <c r="E58" s="120"/>
       <c r="F58" s="120"/>
       <c r="G58" s="120"/>
@@ -17365,7 +17272,6 @@
       <c r="M58" s="116"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D59" s="242"/>
       <c r="E59" s="120"/>
       <c r="F59" s="120"/>
       <c r="G59" s="120"/>
@@ -17377,7 +17283,6 @@
       <c r="M59" s="116"/>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D60" s="242"/>
       <c r="E60" s="120"/>
       <c r="F60" s="120"/>
       <c r="G60" s="120"/>
@@ -17389,7 +17294,6 @@
       <c r="M60" s="116"/>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D61" s="242"/>
       <c r="E61" s="120"/>
       <c r="F61" s="120"/>
       <c r="G61" s="120"/>
@@ -17401,7 +17305,6 @@
       <c r="M61" s="116"/>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D62" s="242"/>
       <c r="E62" s="120"/>
       <c r="F62" s="120"/>
       <c r="G62" s="120"/>
@@ -17413,7 +17316,6 @@
       <c r="M62" s="116"/>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D63" s="242"/>
       <c r="E63" s="120"/>
       <c r="F63" s="120"/>
       <c r="G63" s="120"/>
@@ -17425,7 +17327,6 @@
       <c r="M63" s="116"/>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D64" s="242"/>
       <c r="E64" s="120"/>
       <c r="F64" s="120"/>
       <c r="G64" s="120"/>
@@ -25929,7 +25830,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
@@ -26021,8 +25922,19 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="243" t="s">
-        <v>1158</v>
+      <c r="A9" s="286" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1147</v>
       </c>
     </row>
   </sheetData>
@@ -26047,7 +25959,7 @@
         <v>360</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>361</v>
@@ -26056,12 +25968,12 @@
         <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="139" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B2" s="139"/>
       <c r="C2" s="139"/>
@@ -26070,81 +25982,81 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>1165</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" s="99" t="s">
         <v>1166</v>
-      </c>
-      <c r="E6" s="99" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C7" t="s">
         <v>1168</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1"/>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>1174</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C15" t="s">
         <v>1176</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -26152,7 +26064,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -26160,71 +26072,71 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="136" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E19" s="99" t="s">
         <v>1180</v>
-      </c>
-      <c r="E19" s="99" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="140" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>1183</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="99" t="s">
         <v>1185</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="E23" s="99" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="140" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B30" t="s">
         <v>1188</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>1189</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>1190</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="80" t="s">
         <v>1191</v>
-      </c>
-      <c r="E30" s="80" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75">
       <c r="A31" s="138" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
         <v>1193</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -26262,13 +26174,13 @@
       <c r="B1" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="260" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="260" t="s">
         <v>362</v>
       </c>
-      <c r="E1" s="264" t="s">
+      <c r="E1" s="260" t="s">
         <v>363</v>
       </c>
       <c r="F1" s="54"/>
@@ -26283,7 +26195,7 @@
       <c r="C2" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D2" s="265">
+      <c r="D2" s="261">
         <v>420</v>
       </c>
       <c r="E2" s="1">
@@ -26292,10 +26204,10 @@
       <c r="F2" s="55" t="s">
         <v>367</v>
       </c>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="262"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="34" t="s">
@@ -26307,19 +26219,19 @@
       <c r="C3" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D3" s="265">
+      <c r="D3" s="261">
         <v>368</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="267" t="s">
+      <c r="F3" s="263" t="s">
         <v>370</v>
       </c>
-      <c r="G3" s="266"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="262"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="34" t="s">
@@ -26331,19 +26243,19 @@
       <c r="C4" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="265">
+      <c r="D4" s="261">
         <v>172</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="267" t="s">
+      <c r="F4" s="263" t="s">
         <v>373</v>
       </c>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="34" t="s">
@@ -26355,19 +26267,19 @@
       <c r="C5" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D5" s="265">
+      <c r="D5" s="261">
         <v>420</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="267" t="s">
+      <c r="F5" s="263" t="s">
         <v>377</v>
       </c>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="18"/>
@@ -26377,17 +26289,17 @@
       <c r="C6" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D6" s="265">
+      <c r="D6" s="261">
         <v>480</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="56"/>
-      <c r="G6" s="266"/>
-      <c r="H6" s="266"/>
-      <c r="I6" s="266"/>
-      <c r="J6" s="266"/>
+      <c r="G6" s="262"/>
+      <c r="H6" s="262"/>
+      <c r="I6" s="262"/>
+      <c r="J6" s="262"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="18"/>
@@ -26397,17 +26309,17 @@
       <c r="C7" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D7" s="265">
+      <c r="D7" s="261">
         <v>750</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="56"/>
-      <c r="G7" s="266"/>
-      <c r="H7" s="266"/>
-      <c r="I7" s="266"/>
-      <c r="J7" s="266"/>
+      <c r="G7" s="262"/>
+      <c r="H7" s="262"/>
+      <c r="I7" s="262"/>
+      <c r="J7" s="262"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="18"/>
@@ -26417,15 +26329,15 @@
       <c r="C8" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D8" s="265"/>
+      <c r="D8" s="261"/>
       <c r="E8" s="1">
         <v>34</v>
       </c>
       <c r="F8" s="56"/>
-      <c r="G8" s="266"/>
-      <c r="H8" s="266"/>
-      <c r="I8" s="266"/>
-      <c r="J8" s="266"/>
+      <c r="G8" s="262"/>
+      <c r="H8" s="262"/>
+      <c r="I8" s="262"/>
+      <c r="J8" s="262"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="18"/>
@@ -26435,51 +26347,51 @@
       <c r="C9" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D9" s="265"/>
+      <c r="D9" s="261"/>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="56"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="18"/>
       <c r="B10" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="C10" s="254" t="s">
+      <c r="C10" s="250" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="265"/>
+      <c r="D10" s="261"/>
       <c r="E10" s="1">
         <v>81</v>
       </c>
       <c r="F10" s="56"/>
-      <c r="G10" s="266"/>
-      <c r="H10" s="266"/>
-      <c r="I10" s="266"/>
-      <c r="J10" s="266"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="18"/>
       <c r="B11" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C11" s="254" t="s">
+      <c r="C11" s="250" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="265"/>
+      <c r="D11" s="261"/>
       <c r="E11" s="1">
         <v>8</v>
       </c>
       <c r="F11" s="60"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="34" t="s">
@@ -26488,72 +26400,72 @@
       <c r="B12" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="C12" s="254" t="s">
+      <c r="C12" s="250" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="265"/>
+      <c r="D12" s="261"/>
       <c r="E12" s="1">
         <v>78</v>
       </c>
       <c r="F12" s="63"/>
-      <c r="G12" s="266"/>
-      <c r="H12" s="266"/>
-      <c r="I12" s="266"/>
-      <c r="J12" s="266"/>
+      <c r="G12" s="262"/>
+      <c r="H12" s="262"/>
+      <c r="I12" s="262"/>
+      <c r="J12" s="262"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="18"/>
       <c r="B13" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="254" t="s">
+      <c r="C13" s="250" t="s">
         <v>161</v>
       </c>
-      <c r="D13" s="265"/>
+      <c r="D13" s="261"/>
       <c r="E13" s="1">
         <v>81</v>
       </c>
       <c r="F13" s="61"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="18"/>
       <c r="B14" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="C14" s="254" t="s">
+      <c r="C14" s="250" t="s">
         <v>161</v>
       </c>
-      <c r="D14" s="265"/>
+      <c r="D14" s="261"/>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="60"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
+      <c r="G14" s="262"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="262"/>
+      <c r="J14" s="262"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="18"/>
       <c r="B15" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C15" s="254" t="s">
+      <c r="C15" s="250" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="265"/>
+      <c r="D15" s="261"/>
       <c r="E15" s="1">
         <v>24</v>
       </c>
       <c r="F15" s="61"/>
-      <c r="G15" s="266"/>
-      <c r="H15" s="266"/>
-      <c r="I15" s="266"/>
-      <c r="J15" s="266"/>
+      <c r="G15" s="262"/>
+      <c r="H15" s="262"/>
+      <c r="I15" s="262"/>
+      <c r="J15" s="262"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="64" t="s">
@@ -26565,15 +26477,15 @@
       <c r="C16" s="59" t="s">
         <v>390</v>
       </c>
-      <c r="D16" s="265"/>
+      <c r="D16" s="261"/>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="57"/>
-      <c r="G16" s="266"/>
-      <c r="H16" s="266"/>
-      <c r="I16" s="266"/>
-      <c r="J16" s="266"/>
+      <c r="G16" s="262"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="262"/>
+      <c r="J16" s="262"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="18"/>
@@ -26583,12 +26495,12 @@
       <c r="C17" s="58" t="s">
         <v>392</v>
       </c>
-      <c r="D17" s="265"/>
+      <c r="D17" s="261"/>
       <c r="E17" s="1">
         <v>4</v>
       </c>
       <c r="F17" s="60"/>
-      <c r="G17" s="266"/>
+      <c r="G17" s="262"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="18"/>
@@ -26598,12 +26510,12 @@
       <c r="C18" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D18" s="265"/>
+      <c r="D18" s="261"/>
       <c r="E18" s="1">
         <v>4</v>
       </c>
       <c r="F18" s="60"/>
-      <c r="G18" s="266"/>
+      <c r="G18" s="262"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="44"/>
@@ -26613,18 +26525,18 @@
       <c r="C19" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D19" s="268"/>
+      <c r="D19" s="264"/>
       <c r="E19" s="27">
         <v>4</v>
       </c>
       <c r="F19" s="62"/>
-      <c r="G19" s="266"/>
+      <c r="G19" s="262"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="B20" s="266"/>
-      <c r="C20" s="266"/>
-      <c r="E20" s="266"/>
-      <c r="G20" s="266"/>
+      <c r="B20" s="262"/>
+      <c r="C20" s="262"/>
+      <c r="E20" s="262"/>
+      <c r="G20" s="262"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26674,10 +26586,10 @@
       <c r="B1" s="68" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="269" t="s">
+      <c r="C1" s="265" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="269" t="s">
+      <c r="D1" s="265" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="69"/>
@@ -26688,7 +26600,7 @@
       <c r="A2" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="250" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="21"/>
@@ -26712,7 +26624,7 @@
       <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="270" t="s">
+      <c r="E3" s="266" t="s">
         <v>370</v>
       </c>
       <c r="G3"/>
@@ -26722,14 +26634,14 @@
       <c r="A4" s="72" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="250" t="s">
         <v>226</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="9">
         <v>36</v>
       </c>
-      <c r="E4" s="270" t="s">
+      <c r="E4" s="266" t="s">
         <v>373</v>
       </c>
       <c r="G4"/>
@@ -26739,14 +26651,14 @@
       <c r="A5" s="72" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="254" t="s">
+      <c r="B5" s="250" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="9">
         <v>24</v>
       </c>
-      <c r="E5" s="270" t="s">
+      <c r="E5" s="266" t="s">
         <v>377</v>
       </c>
       <c r="G5"/>
@@ -26754,7 +26666,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="73"/>
-      <c r="B6" s="254" t="s">
+      <c r="B6" s="250" t="s">
         <v>324</v>
       </c>
       <c r="C6" s="21"/>
@@ -26767,7 +26679,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="73"/>
-      <c r="B7" s="254" t="s">
+      <c r="B7" s="250" t="s">
         <v>326</v>
       </c>
       <c r="C7" s="21"/>
@@ -26780,7 +26692,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="73"/>
-      <c r="B8" s="254" t="s">
+      <c r="B8" s="250" t="s">
         <v>396</v>
       </c>
       <c r="C8" s="21"/>
@@ -26849,7 +26761,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="73"/>
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="250" t="s">
         <v>401</v>
       </c>
       <c r="C13" s="21"/>
@@ -26864,7 +26776,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="73"/>
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="250" t="s">
         <v>403</v>
       </c>
       <c r="C14" s="21"/>
@@ -27020,7 +26932,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="73"/>
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="250" t="s">
         <v>411</v>
       </c>
       <c r="C26" s="66" t="s">
@@ -27035,7 +26947,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="73"/>
-      <c r="B27" s="254" t="s">
+      <c r="B27" s="250" t="s">
         <v>413</v>
       </c>
       <c r="C27" s="66" t="s">
@@ -27050,7 +26962,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="73"/>
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="250" t="s">
         <v>415</v>
       </c>
       <c r="C28" s="21"/>
@@ -27073,7 +26985,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="74"/>
-      <c r="F29" s="254"/>
+      <c r="F29" s="250"/>
       <c r="G29"/>
       <c r="H29"/>
     </row>
@@ -27082,14 +26994,14 @@
       <c r="B30" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="C30" s="254" t="s">
+      <c r="C30" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D30" s="9">
         <v>4</v>
       </c>
       <c r="E30" s="74"/>
-      <c r="F30" s="254"/>
+      <c r="F30" s="250"/>
       <c r="G30"/>
       <c r="H30"/>
     </row>
@@ -27098,15 +27010,15 @@
       <c r="B31" t="s">
         <v>418</v>
       </c>
-      <c r="C31" s="254" t="s">
+      <c r="C31" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D31" s="9">
         <v>2</v>
       </c>
       <c r="E31" s="74"/>
-      <c r="F31" s="254"/>
-      <c r="G31" s="254"/>
+      <c r="F31" s="250"/>
+      <c r="G31" s="250"/>
       <c r="H31"/>
     </row>
     <row r="32" spans="1:8">
@@ -27114,14 +27026,14 @@
       <c r="B32" t="s">
         <v>419</v>
       </c>
-      <c r="C32" s="254" t="s">
+      <c r="C32" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D32" s="9">
         <v>1</v>
       </c>
       <c r="E32" s="74"/>
-      <c r="F32" s="254"/>
+      <c r="F32" s="250"/>
       <c r="G32"/>
       <c r="H32"/>
     </row>
@@ -27130,14 +27042,14 @@
       <c r="B33" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="C33" s="254" t="s">
+      <c r="C33" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D33" s="9">
         <v>1</v>
       </c>
       <c r="E33" s="74"/>
-      <c r="F33" s="254"/>
+      <c r="F33" s="250"/>
       <c r="G33"/>
       <c r="H33"/>
     </row>
@@ -27146,14 +27058,14 @@
       <c r="B34" t="s">
         <v>421</v>
       </c>
-      <c r="C34" s="254" t="s">
+      <c r="C34" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D34" s="9">
         <v>1</v>
       </c>
       <c r="E34" s="74"/>
-      <c r="F34" s="254"/>
+      <c r="F34" s="250"/>
       <c r="G34"/>
       <c r="H34"/>
     </row>
@@ -27162,14 +27074,14 @@
       <c r="B35" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C35" s="254" t="s">
+      <c r="C35" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D35" s="9">
         <v>1</v>
       </c>
       <c r="E35" s="74"/>
-      <c r="F35" s="254"/>
+      <c r="F35" s="250"/>
       <c r="G35"/>
       <c r="H35"/>
     </row>
@@ -27178,14 +27090,14 @@
       <c r="B36" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C36" s="254" t="s">
+      <c r="C36" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D36" s="9">
         <v>1</v>
       </c>
       <c r="E36" s="74"/>
-      <c r="F36" s="254"/>
+      <c r="F36" s="250"/>
       <c r="G36"/>
       <c r="H36"/>
     </row>
@@ -27194,14 +27106,14 @@
       <c r="B37" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="C37" s="254" t="s">
+      <c r="C37" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D37" s="9">
         <v>2</v>
       </c>
       <c r="E37" s="74"/>
-      <c r="F37" s="254"/>
+      <c r="F37" s="250"/>
       <c r="G37"/>
       <c r="H37"/>
     </row>
@@ -27210,14 +27122,14 @@
       <c r="B38" s="24" t="s">
         <v>425</v>
       </c>
-      <c r="C38" s="254" t="s">
+      <c r="C38" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D38" s="9">
         <v>2</v>
       </c>
       <c r="E38" s="74"/>
-      <c r="F38" s="254"/>
+      <c r="F38" s="250"/>
       <c r="G38" s="1"/>
       <c r="H38"/>
     </row>
@@ -27226,14 +27138,14 @@
       <c r="B39" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="C39" s="254" t="s">
+      <c r="C39" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D39" s="9">
         <v>1</v>
       </c>
       <c r="E39" s="74"/>
-      <c r="F39" s="254"/>
+      <c r="F39" s="250"/>
       <c r="G39"/>
       <c r="H39"/>
     </row>
@@ -27242,14 +27154,14 @@
       <c r="B40" s="24" t="s">
         <v>427</v>
       </c>
-      <c r="C40" s="254" t="s">
+      <c r="C40" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D40" s="9">
         <v>1</v>
       </c>
       <c r="E40" s="74"/>
-      <c r="F40" s="254"/>
+      <c r="F40" s="250"/>
       <c r="G40"/>
       <c r="H40"/>
     </row>
@@ -27258,14 +27170,14 @@
       <c r="B41" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C41" s="254" t="s">
+      <c r="C41" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D41" s="9">
         <v>1</v>
       </c>
       <c r="E41" s="74"/>
-      <c r="F41" s="254"/>
+      <c r="F41" s="250"/>
       <c r="G41"/>
       <c r="H41"/>
     </row>
@@ -27274,14 +27186,14 @@
       <c r="B42" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C42" s="254" t="s">
+      <c r="C42" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D42" s="9">
         <v>1</v>
       </c>
       <c r="E42" s="74"/>
-      <c r="F42" s="254"/>
+      <c r="F42" s="250"/>
       <c r="G42"/>
       <c r="H42"/>
     </row>
@@ -27290,14 +27202,14 @@
       <c r="B43" s="24" t="s">
         <v>430</v>
       </c>
-      <c r="C43" s="254" t="s">
+      <c r="C43" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D43" s="9">
         <v>1</v>
       </c>
       <c r="E43" s="74"/>
-      <c r="F43" s="254"/>
+      <c r="F43" s="250"/>
       <c r="G43"/>
       <c r="H43"/>
     </row>
@@ -27306,19 +27218,19 @@
       <c r="B44" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="C44" s="271" t="s">
+      <c r="C44" s="267" t="s">
         <v>390</v>
       </c>
       <c r="D44" s="77">
         <v>1</v>
       </c>
       <c r="E44" s="78"/>
-      <c r="F44" s="254"/>
+      <c r="F44" s="250"/>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="F45" s="254"/>
+      <c r="F45" s="250"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27369,10 +27281,10 @@
       <c r="B1" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="260" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="260" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="33"/>
@@ -27381,7 +27293,7 @@
       <c r="A2" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="250" t="s">
         <v>432</v>
       </c>
       <c r="C2"/>
@@ -27396,14 +27308,14 @@
       <c r="A3" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="251" t="s">
+      <c r="B3" s="247" t="s">
         <v>336</v>
       </c>
-      <c r="C3" s="251"/>
+      <c r="C3" s="247"/>
       <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="272" t="s">
+      <c r="E3" s="268" t="s">
         <v>370</v>
       </c>
     </row>
@@ -27411,14 +27323,14 @@
       <c r="A4" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="247" t="s">
         <v>433</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="247"/>
       <c r="D4" s="9">
         <v>1</v>
       </c>
-      <c r="E4" s="272" t="s">
+      <c r="E4" s="268" t="s">
         <v>373</v>
       </c>
     </row>
@@ -27433,7 +27345,7 @@
       <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="268" t="s">
         <v>377</v>
       </c>
     </row>
@@ -27576,7 +27488,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="18"/>
-      <c r="B18" s="273" t="s">
+      <c r="B18" s="269" t="s">
         <v>443</v>
       </c>
       <c r="C18" s="51" t="s">
@@ -27600,10 +27512,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="18"/>
-      <c r="B20" s="274" t="s">
+      <c r="B20" s="270" t="s">
         <v>446</v>
       </c>
-      <c r="C20" s="274"/>
+      <c r="C20" s="270"/>
       <c r="D20" s="9">
         <v>1</v>
       </c>
@@ -27622,10 +27534,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="18"/>
-      <c r="B22" s="274" t="s">
+      <c r="B22" s="270" t="s">
         <v>448</v>
       </c>
-      <c r="C22" s="274"/>
+      <c r="C22" s="270"/>
       <c r="D22" s="9">
         <v>1</v>
       </c>
@@ -27679,7 +27591,7 @@
       <c r="A27" s="18"/>
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
-      <c r="D27" s="266"/>
+      <c r="D27" s="262"/>
       <c r="E27" s="39"/>
     </row>
     <row r="28" spans="1:5" ht="18.75">
@@ -27696,10 +27608,10 @@
       <c r="B29" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="248" t="s">
+      <c r="C29" s="244" t="s">
         <v>361</v>
       </c>
-      <c r="D29" s="275" t="s">
+      <c r="D29" s="271" t="s">
         <v>363</v>
       </c>
       <c r="E29" s="39"/>
@@ -27775,7 +27687,7 @@
       <c r="B36" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="C36" s="274"/>
+      <c r="C36" s="270"/>
       <c r="D36" s="30">
         <v>1</v>
       </c>
@@ -27860,10 +27772,10 @@
       <c r="B1" s="68" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="269" t="s">
+      <c r="C1" s="265" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="269" t="s">
+      <c r="D1" s="265" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="69"/>
@@ -27886,14 +27798,14 @@
       <c r="A3" s="72" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="254" t="s">
+      <c r="B3" s="250" t="s">
         <v>458</v>
       </c>
-      <c r="C3" s="254"/>
+      <c r="C3" s="250"/>
       <c r="D3" s="9">
         <v>12</v>
       </c>
-      <c r="E3" s="270" t="s">
+      <c r="E3" s="266" t="s">
         <v>370</v>
       </c>
     </row>
@@ -27901,14 +27813,14 @@
       <c r="A4" s="72" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="250" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="250"/>
       <c r="D4" s="9">
         <v>3</v>
       </c>
-      <c r="E4" s="270" t="s">
+      <c r="E4" s="266" t="s">
         <v>373</v>
       </c>
     </row>
@@ -27916,14 +27828,14 @@
       <c r="A5" s="72" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="254" t="s">
+      <c r="B5" s="250" t="s">
         <v>322</v>
       </c>
-      <c r="C5" s="254"/>
+      <c r="C5" s="250"/>
       <c r="D5" s="9">
         <v>6</v>
       </c>
-      <c r="E5" s="270" t="s">
+      <c r="E5" s="266" t="s">
         <v>377</v>
       </c>
     </row>
@@ -27932,10 +27844,10 @@
       <c r="B6" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="C6" s="254" t="s">
+      <c r="C6" s="250" t="s">
         <v>459</v>
       </c>
-      <c r="D6" s="260">
+      <c r="D6" s="256">
         <v>1</v>
       </c>
       <c r="E6" s="74"/>
@@ -27945,20 +27857,20 @@
       <c r="B7" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="C7" s="254" t="s">
+      <c r="C7" s="250" t="s">
         <v>461</v>
       </c>
-      <c r="D7" s="260">
+      <c r="D7" s="256">
         <v>28</v>
       </c>
       <c r="E7" s="74"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="73"/>
-      <c r="B8" s="254" t="s">
+      <c r="B8" s="250" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="254"/>
+      <c r="C8" s="250"/>
       <c r="D8" s="9">
         <v>1</v>
       </c>
@@ -27976,22 +27888,22 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="73"/>
-      <c r="B10" s="254" t="s">
+      <c r="B10" s="250" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="254"/>
-      <c r="D10" s="260">
+      <c r="C10" s="250"/>
+      <c r="D10" s="256">
         <v>6</v>
       </c>
       <c r="E10" s="74"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="73"/>
-      <c r="B11" s="254" t="s">
+      <c r="B11" s="250" t="s">
         <v>464</v>
       </c>
-      <c r="C11" s="254"/>
-      <c r="D11" s="260">
+      <c r="C11" s="250"/>
+      <c r="D11" s="256">
         <v>3</v>
       </c>
       <c r="E11" s="74"/>
@@ -28000,10 +27912,10 @@
       <c r="A12" s="72" t="s">
         <v>385</v>
       </c>
-      <c r="B12" s="249" t="s">
+      <c r="B12" s="245" t="s">
         <v>465</v>
       </c>
-      <c r="C12" s="254"/>
+      <c r="C12" s="250"/>
       <c r="D12" s="9">
         <v>1</v>
       </c>
@@ -28011,10 +27923,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="73"/>
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="250" t="s">
         <v>400</v>
       </c>
-      <c r="C13" s="254"/>
+      <c r="C13" s="250"/>
       <c r="D13" s="9">
         <v>42</v>
       </c>
@@ -28132,10 +28044,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="73"/>
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="250" t="s">
         <v>386</v>
       </c>
-      <c r="C25" s="254"/>
+      <c r="C25" s="250"/>
       <c r="D25" s="9">
         <v>6</v>
       </c>
@@ -28143,10 +28055,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="73"/>
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="250" t="s">
         <v>211</v>
       </c>
-      <c r="C26" s="254"/>
+      <c r="C26" s="250"/>
       <c r="D26" s="9">
         <v>21</v>
       </c>
@@ -28272,7 +28184,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="73"/>
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="250" t="s">
         <v>481</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -28437,10 +28349,10 @@
       <c r="B1" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="260" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="260" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="33"/>
@@ -28452,7 +28364,7 @@
       <c r="B2" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="254"/>
+      <c r="C2" s="250"/>
       <c r="D2" s="9">
         <v>14</v>
       </c>
@@ -28467,11 +28379,11 @@
       <c r="B3" t="s">
         <v>491</v>
       </c>
-      <c r="C3" s="254"/>
+      <c r="C3" s="250"/>
       <c r="D3" s="9">
         <v>13</v>
       </c>
-      <c r="E3" s="272" t="s">
+      <c r="E3" s="268" t="s">
         <v>370</v>
       </c>
     </row>
@@ -28479,14 +28391,14 @@
       <c r="A4" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="250" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="250"/>
       <c r="D4" s="9">
         <v>2</v>
       </c>
-      <c r="E4" s="272" t="s">
+      <c r="E4" s="268" t="s">
         <v>373</v>
       </c>
     </row>
@@ -28497,20 +28409,20 @@
       <c r="B5" t="s">
         <v>492</v>
       </c>
-      <c r="C5" s="254"/>
+      <c r="C5" s="250"/>
       <c r="D5" s="9">
         <v>2</v>
       </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="268" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="18"/>
-      <c r="B6" s="254" t="s">
+      <c r="B6" s="250" t="s">
         <v>493</v>
       </c>
-      <c r="C6" s="254"/>
+      <c r="C6" s="250"/>
       <c r="D6" s="9">
         <v>1</v>
       </c>
@@ -28518,10 +28430,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="18"/>
-      <c r="B7" s="254" t="s">
+      <c r="B7" s="250" t="s">
         <v>494</v>
       </c>
-      <c r="C7" s="254"/>
+      <c r="C7" s="250"/>
       <c r="D7" s="9">
         <v>4</v>
       </c>
@@ -28532,7 +28444,7 @@
       <c r="B8" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C8" s="254"/>
+      <c r="C8" s="250"/>
       <c r="D8" s="9">
         <v>6</v>
       </c>
@@ -28543,7 +28455,7 @@
       <c r="B9" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C9" s="254"/>
+      <c r="C9" s="250"/>
       <c r="D9" s="9">
         <v>6</v>
       </c>
@@ -28554,7 +28466,7 @@
       <c r="B10" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="276" t="s">
+      <c r="C10" s="272" t="s">
         <v>497</v>
       </c>
       <c r="D10" s="9">
@@ -28567,7 +28479,7 @@
       <c r="B11" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="C11" s="254"/>
+      <c r="C11" s="250"/>
       <c r="D11" s="9">
         <v>1</v>
       </c>
@@ -28575,10 +28487,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="18"/>
-      <c r="B12" s="254" t="s">
+      <c r="B12" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="254"/>
+      <c r="C12" s="250"/>
       <c r="D12" s="9">
         <v>1</v>
       </c>
@@ -28588,10 +28500,10 @@
       <c r="A13" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="250" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="254"/>
+      <c r="C13" s="250"/>
       <c r="D13" s="9">
         <v>1</v>
       </c>
@@ -28624,7 +28536,7 @@
       <c r="B16" t="s">
         <v>500</v>
       </c>
-      <c r="C16" s="254"/>
+      <c r="C16" s="250"/>
       <c r="D16" s="9">
         <v>4</v>
       </c>
@@ -28635,7 +28547,7 @@
       <c r="B17" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="254"/>
+      <c r="C17" s="250"/>
       <c r="D17" s="9">
         <v>19</v>
       </c>
@@ -28646,7 +28558,7 @@
       <c r="B18" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="C18" s="254"/>
+      <c r="C18" s="250"/>
       <c r="D18" s="9">
         <v>6</v>
       </c>
@@ -28657,7 +28569,7 @@
       <c r="B19" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C19" s="254"/>
+      <c r="C19" s="250"/>
       <c r="D19" s="9">
         <v>13</v>
       </c>
@@ -28665,10 +28577,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="18"/>
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="250" t="s">
         <v>502</v>
       </c>
-      <c r="C20" s="254"/>
+      <c r="C20" s="250"/>
       <c r="D20" s="9">
         <v>4</v>
       </c>
@@ -28676,10 +28588,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="18"/>
-      <c r="B21" s="254" t="s">
+      <c r="B21" s="250" t="s">
         <v>503</v>
       </c>
-      <c r="C21" s="254"/>
+      <c r="C21" s="250"/>
       <c r="D21" s="9">
         <v>6</v>
       </c>
@@ -28690,7 +28602,7 @@
       <c r="B22" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C22" s="254"/>
+      <c r="C22" s="250"/>
       <c r="D22" s="9">
         <v>4</v>
       </c>
@@ -28701,7 +28613,7 @@
       <c r="B23" t="s">
         <v>504</v>
       </c>
-      <c r="C23" s="254"/>
+      <c r="C23" s="250"/>
       <c r="D23" s="9">
         <v>6</v>
       </c>
@@ -28712,7 +28624,7 @@
       <c r="B24" s="21" t="s">
         <v>505</v>
       </c>
-      <c r="C24" s="254"/>
+      <c r="C24" s="250"/>
       <c r="D24" s="9">
         <v>4</v>
       </c>
@@ -28723,7 +28635,7 @@
       <c r="B25" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="254"/>
+      <c r="C25" s="250"/>
       <c r="D25" s="9">
         <v>4</v>
       </c>
@@ -28731,10 +28643,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="250" t="s">
         <v>506</v>
       </c>
-      <c r="C26" s="254"/>
+      <c r="C26" s="250"/>
       <c r="D26" s="9">
         <v>1</v>
       </c>
@@ -28742,10 +28654,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="18"/>
-      <c r="B27" s="254" t="s">
+      <c r="B27" s="250" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="254"/>
+      <c r="C27" s="250"/>
       <c r="D27" s="9">
         <v>16</v>
       </c>
@@ -28756,7 +28668,7 @@
       <c r="B28" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C28" s="254"/>
+      <c r="C28" s="250"/>
       <c r="D28" s="9">
         <v>52</v>
       </c>
@@ -28767,7 +28679,7 @@
       <c r="B29" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C29" s="254"/>
+      <c r="C29" s="250"/>
       <c r="D29" s="9">
         <v>77</v>
       </c>
@@ -28778,7 +28690,7 @@
       <c r="B30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="254"/>
+      <c r="C30" s="250"/>
       <c r="D30" s="9">
         <v>16</v>
       </c>
@@ -28786,10 +28698,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="18"/>
-      <c r="B31" s="254" t="s">
+      <c r="B31" s="250" t="s">
         <v>507</v>
       </c>
-      <c r="C31" s="254"/>
+      <c r="C31" s="250"/>
       <c r="D31" s="9">
         <v>44</v>
       </c>
@@ -28797,10 +28709,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="18"/>
-      <c r="B32" s="254" t="s">
+      <c r="B32" s="250" t="s">
         <v>508</v>
       </c>
-      <c r="C32" s="254"/>
+      <c r="C32" s="250"/>
       <c r="D32" s="9">
         <v>17</v>
       </c>
@@ -28821,10 +28733,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="18"/>
-      <c r="B34" s="254" t="s">
+      <c r="B34" s="250" t="s">
         <v>511</v>
       </c>
-      <c r="C34" s="254" t="s">
+      <c r="C34" s="250" t="s">
         <v>512</v>
       </c>
       <c r="D34" s="9">
@@ -28834,7 +28746,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="18"/>
-      <c r="B35" s="254" t="s">
+      <c r="B35" s="250" t="s">
         <v>513</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -28873,10 +28785,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="18"/>
-      <c r="B38" s="273" t="s">
+      <c r="B38" s="269" t="s">
         <v>516</v>
       </c>
-      <c r="C38" s="273" t="s">
+      <c r="C38" s="269" t="s">
         <v>357</v>
       </c>
       <c r="D38" s="40">
@@ -28899,7 +28811,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="18"/>
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="250" t="s">
         <v>518</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -29003,7 +28915,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="18"/>
-      <c r="B48" s="254" t="s">
+      <c r="B48" s="250" t="s">
         <v>526</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -29016,7 +28928,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="18"/>
-      <c r="B49" s="254" t="s">
+      <c r="B49" s="250" t="s">
         <v>527</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -29029,7 +28941,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="18"/>
-      <c r="B50" s="254" t="s">
+      <c r="B50" s="250" t="s">
         <v>528</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -29042,7 +28954,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="18"/>
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="250" t="s">
         <v>529</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -29276,7 +29188,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="18"/>
-      <c r="B69" s="254" t="s">
+      <c r="B69" s="250" t="s">
         <v>549</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -29305,7 +29217,7 @@
       <c r="B71" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C71" s="254" t="s">
+      <c r="C71" s="250" t="s">
         <v>510</v>
       </c>
       <c r="D71" s="9">
@@ -29318,7 +29230,7 @@
       <c r="B72" t="s">
         <v>552</v>
       </c>
-      <c r="C72" s="254" t="s">
+      <c r="C72" s="250" t="s">
         <v>510</v>
       </c>
       <c r="D72" s="9">
@@ -29397,10 +29309,10 @@
       <c r="B1" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="248" t="s">
+      <c r="C1" s="244" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="248" t="s">
+      <c r="D1" s="244" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="33"/>
@@ -29412,10 +29324,10 @@
       <c r="B2" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="244" t="s">
         <v>556</v>
       </c>
-      <c r="D2" s="277" t="s">
+      <c r="D2" s="273" t="s">
         <v>557</v>
       </c>
       <c r="E2" s="38" t="s">
@@ -29426,16 +29338,16 @@
       <c r="A3" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="254" t="s">
+      <c r="B3" s="250" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D3" s="254">
-        <v>1</v>
-      </c>
-      <c r="E3" s="272" t="s">
+      <c r="D3" s="250">
+        <v>1</v>
+      </c>
+      <c r="E3" s="268" t="s">
         <v>370</v>
       </c>
     </row>
@@ -29446,13 +29358,13 @@
       <c r="B4" t="s">
         <v>491</v>
       </c>
-      <c r="C4" s="254" t="s">
+      <c r="C4" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D4" s="254">
+      <c r="D4" s="250">
         <v>4</v>
       </c>
-      <c r="E4" s="272" t="s">
+      <c r="E4" s="268" t="s">
         <v>373</v>
       </c>
     </row>
@@ -29460,16 +29372,16 @@
       <c r="A5" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="254" t="s">
+      <c r="B5" s="250" t="s">
         <v>319</v>
       </c>
-      <c r="C5" s="254" t="s">
+      <c r="C5" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D5" s="254">
+      <c r="D5" s="250">
         <v>3</v>
       </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="268" t="s">
         <v>377</v>
       </c>
     </row>
@@ -29478,20 +29390,20 @@
       <c r="B6" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="C6" s="254" t="s">
+      <c r="C6" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D6" s="254">
+      <c r="D6" s="250">
         <v>1</v>
       </c>
       <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="18"/>
-      <c r="B7" s="254" t="s">
+      <c r="B7" s="250" t="s">
         <v>559</v>
       </c>
-      <c r="C7" s="254" t="s">
+      <c r="C7" s="250" t="s">
         <v>556</v>
       </c>
       <c r="D7" s="2">
@@ -29501,26 +29413,26 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="18"/>
-      <c r="B8" s="254" t="s">
+      <c r="B8" s="250" t="s">
         <v>560</v>
       </c>
-      <c r="C8" s="254" t="s">
+      <c r="C8" s="250" t="s">
         <v>561</v>
       </c>
-      <c r="D8" s="254">
+      <c r="D8" s="250">
         <v>1</v>
       </c>
       <c r="E8" s="39"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="18"/>
-      <c r="B9" s="258" t="s">
+      <c r="B9" s="254" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="254" t="s">
+      <c r="C9" s="250" t="s">
         <v>561</v>
       </c>
-      <c r="D9" s="254">
+      <c r="D9" s="250">
         <v>1</v>
       </c>
       <c r="E9" s="39"/>
@@ -29530,10 +29442,10 @@
       <c r="B10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="254" t="s">
+      <c r="C10" s="250" t="s">
         <v>561</v>
       </c>
-      <c r="D10" s="254">
+      <c r="D10" s="250">
         <v>1</v>
       </c>
       <c r="E10" s="39"/>
@@ -29543,10 +29455,10 @@
       <c r="B11" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="C11" s="254" t="s">
+      <c r="C11" s="250" t="s">
         <v>561</v>
       </c>
-      <c r="D11" s="254">
+      <c r="D11" s="250">
         <v>1</v>
       </c>
       <c r="E11" s="39"/>
@@ -29558,23 +29470,23 @@
       <c r="B12" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="254" t="s">
+      <c r="C12" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D12" s="254">
+      <c r="D12" s="250">
         <v>10</v>
       </c>
       <c r="E12" s="39"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="18"/>
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="250" t="s">
         <v>405</v>
       </c>
-      <c r="C13" s="254" t="s">
+      <c r="C13" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D13" s="254">
+      <c r="D13" s="250">
         <v>1</v>
       </c>
       <c r="E13" s="39"/>
@@ -29584,10 +29496,10 @@
       <c r="B14" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="C14" s="254" t="s">
+      <c r="C14" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D14" s="254">
+      <c r="D14" s="250">
         <v>2</v>
       </c>
       <c r="E14" s="39"/>
@@ -29597,10 +29509,10 @@
       <c r="B15" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C15" s="254" t="s">
+      <c r="C15" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D15" s="254">
+      <c r="D15" s="250">
         <v>7</v>
       </c>
       <c r="E15" s="39"/>
@@ -29610,20 +29522,20 @@
       <c r="B16" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="C16" s="254" t="s">
+      <c r="C16" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D16" s="254">
+      <c r="D16" s="250">
         <v>3</v>
       </c>
       <c r="E16" s="39"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="18"/>
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="250" t="s">
         <v>566</v>
       </c>
-      <c r="C17" s="254" t="s">
+      <c r="C17" s="250" t="s">
         <v>556</v>
       </c>
       <c r="D17" s="2">
@@ -29633,13 +29545,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="18"/>
-      <c r="B18" s="254" t="s">
+      <c r="B18" s="250" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="254" t="s">
+      <c r="C18" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D18" s="254">
+      <c r="D18" s="250">
         <v>1</v>
       </c>
       <c r="E18" s="39"/>
@@ -29649,10 +29561,10 @@
       <c r="B19" t="s">
         <v>567</v>
       </c>
-      <c r="C19" s="254" t="s">
+      <c r="C19" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D19" s="254">
+      <c r="D19" s="250">
         <v>2</v>
       </c>
       <c r="E19" s="39"/>
@@ -29662,20 +29574,20 @@
       <c r="B20" t="s">
         <v>568</v>
       </c>
-      <c r="C20" s="254" t="s">
+      <c r="C20" s="250" t="s">
         <v>556</v>
       </c>
-      <c r="D20" s="254">
+      <c r="D20" s="250">
         <v>2</v>
       </c>
       <c r="E20" s="39"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="18"/>
-      <c r="B21" s="254" t="s">
+      <c r="B21" s="250" t="s">
         <v>569</v>
       </c>
-      <c r="C21" s="254" t="s">
+      <c r="C21" s="250" t="s">
         <v>561</v>
       </c>
       <c r="D21" s="2">
@@ -29691,7 +29603,7 @@
       <c r="B22" t="s">
         <v>571</v>
       </c>
-      <c r="C22" s="254" t="s">
+      <c r="C22" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D22" s="2">
@@ -29704,7 +29616,7 @@
       <c r="B23" t="s">
         <v>572</v>
       </c>
-      <c r="C23" s="254" t="s">
+      <c r="C23" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D23" s="2">
@@ -29717,7 +29629,7 @@
       <c r="B24" t="s">
         <v>573</v>
       </c>
-      <c r="C24" s="254" t="s">
+      <c r="C24" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D24" s="2">
@@ -29730,10 +29642,10 @@
       <c r="B25" t="s">
         <v>574</v>
       </c>
-      <c r="C25" s="254" t="s">
+      <c r="C25" s="250" t="s">
         <v>390</v>
       </c>
-      <c r="D25" s="254">
+      <c r="D25" s="250">
         <v>1</v>
       </c>
       <c r="E25" s="39"/>
@@ -29743,7 +29655,7 @@
       <c r="B26" t="s">
         <v>575</v>
       </c>
-      <c r="C26" s="254" t="s">
+      <c r="C26" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D26" s="1">
@@ -29756,7 +29668,7 @@
       <c r="B27" t="s">
         <v>576</v>
       </c>
-      <c r="C27" s="254" t="s">
+      <c r="C27" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D27" s="1">
@@ -29769,20 +29681,20 @@
       <c r="B28" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C28" s="254" t="s">
+      <c r="C28" s="250" t="s">
         <v>390</v>
       </c>
-      <c r="D28" s="254">
+      <c r="D28" s="250">
         <v>2</v>
       </c>
       <c r="E28" s="39"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="18"/>
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="250" t="s">
         <v>578</v>
       </c>
-      <c r="C29" s="254" t="s">
+      <c r="C29" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D29" s="2">
@@ -29792,10 +29704,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="18"/>
-      <c r="B30" s="254" t="s">
+      <c r="B30" s="250" t="s">
         <v>579</v>
       </c>
-      <c r="C30" s="254" t="s">
+      <c r="C30" s="250" t="s">
         <v>540</v>
       </c>
       <c r="D30" s="2">
@@ -29808,10 +29720,10 @@
       <c r="B31" t="s">
         <v>580</v>
       </c>
-      <c r="C31" s="254" t="s">
+      <c r="C31" s="250" t="s">
         <v>390</v>
       </c>
-      <c r="D31" s="254">
+      <c r="D31" s="250">
         <v>1</v>
       </c>
       <c r="E31" s="39"/>
@@ -29821,10 +29733,10 @@
       <c r="B32" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C32" s="254" t="s">
+      <c r="C32" s="250" t="s">
         <v>582</v>
       </c>
-      <c r="D32" s="254">
+      <c r="D32" s="250">
         <v>2</v>
       </c>
       <c r="E32" s="39"/>
@@ -29834,10 +29746,10 @@
       <c r="B33" t="s">
         <v>583</v>
       </c>
-      <c r="C33" s="254" t="s">
+      <c r="C33" s="250" t="s">
         <v>584</v>
       </c>
-      <c r="D33" s="254">
+      <c r="D33" s="250">
         <v>2</v>
       </c>
       <c r="E33" s="39"/>
@@ -29847,10 +29759,10 @@
       <c r="B34" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C34" s="254" t="s">
+      <c r="C34" s="250" t="s">
         <v>586</v>
       </c>
-      <c r="D34" s="254">
+      <c r="D34" s="250">
         <v>2</v>
       </c>
       <c r="E34" s="39"/>
@@ -29860,36 +29772,36 @@
       <c r="B35" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C35" s="254" t="s">
+      <c r="C35" s="250" t="s">
         <v>582</v>
       </c>
-      <c r="D35" s="254">
+      <c r="D35" s="250">
         <v>2</v>
       </c>
       <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="18"/>
-      <c r="B36" s="254" t="s">
+      <c r="B36" s="250" t="s">
         <v>588</v>
       </c>
-      <c r="C36" s="254" t="s">
+      <c r="C36" s="250" t="s">
         <v>589</v>
       </c>
-      <c r="D36" s="254">
+      <c r="D36" s="250">
         <v>2</v>
       </c>
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="18"/>
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="250" t="s">
         <v>590</v>
       </c>
-      <c r="C37" s="254" t="s">
+      <c r="C37" s="250" t="s">
         <v>586</v>
       </c>
-      <c r="D37" s="254">
+      <c r="D37" s="250">
         <v>2</v>
       </c>
       <c r="E37" s="39"/>
@@ -29899,20 +29811,20 @@
       <c r="B38" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C38" s="254" t="s">
+      <c r="C38" s="250" t="s">
         <v>390</v>
       </c>
-      <c r="D38" s="254">
+      <c r="D38" s="250">
         <v>1</v>
       </c>
       <c r="E38" s="39"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="18"/>
-      <c r="B39" s="254" t="s">
+      <c r="B39" s="250" t="s">
         <v>592</v>
       </c>
-      <c r="C39" s="254" t="s">
+      <c r="C39" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D39" s="2">
@@ -29922,10 +29834,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="18"/>
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="250" t="s">
         <v>593</v>
       </c>
-      <c r="C40" s="254" t="s">
+      <c r="C40" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D40" s="2">
@@ -29935,10 +29847,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="18"/>
-      <c r="B41" s="254" t="s">
+      <c r="B41" s="250" t="s">
         <v>594</v>
       </c>
-      <c r="C41" s="254" t="s">
+      <c r="C41" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D41" s="2">
@@ -29948,10 +29860,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="18"/>
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="250" t="s">
         <v>595</v>
       </c>
-      <c r="C42" s="254" t="s">
+      <c r="C42" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D42" s="2">
@@ -29961,23 +29873,23 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="18"/>
-      <c r="B43" s="254" t="s">
+      <c r="B43" s="250" t="s">
         <v>596</v>
       </c>
-      <c r="C43" s="254" t="s">
+      <c r="C43" s="250" t="s">
         <v>390</v>
       </c>
-      <c r="D43" s="254">
+      <c r="D43" s="250">
         <v>1</v>
       </c>
       <c r="E43" s="39"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1">
       <c r="A44" s="44"/>
-      <c r="B44" s="254" t="s">
+      <c r="B44" s="250" t="s">
         <v>597</v>
       </c>
-      <c r="C44" s="254" t="s">
+      <c r="C44" s="250" t="s">
         <v>390</v>
       </c>
       <c r="D44" s="2">
@@ -29986,7 +29898,7 @@
       <c r="E44" s="46"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="C45" s="266"/>
+      <c r="C45" s="262"/>
     </row>
     <row r="46" spans="1:5" ht="30">
       <c r="B46" s="97" t="s">
@@ -30038,10 +29950,10 @@
       <c r="B1" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="260" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="260" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="33"/>
@@ -30053,8 +29965,8 @@
       <c r="B2" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="C2" s="254"/>
-      <c r="D2" s="254">
+      <c r="C2" s="250"/>
+      <c r="D2" s="250">
         <v>6</v>
       </c>
       <c r="E2" s="38" t="s">
@@ -30065,13 +29977,13 @@
       <c r="A3" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="253" t="s">
+      <c r="B3" s="249" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="254">
-        <v>1</v>
-      </c>
-      <c r="E3" s="272" t="s">
+      <c r="D3" s="250">
+        <v>1</v>
+      </c>
+      <c r="E3" s="268" t="s">
         <v>370</v>
       </c>
     </row>
@@ -30079,14 +29991,14 @@
       <c r="A4" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="250" t="s">
         <v>600</v>
       </c>
-      <c r="C4" s="254"/>
-      <c r="D4" s="254">
-        <v>1</v>
-      </c>
-      <c r="E4" s="272" t="s">
+      <c r="C4" s="250"/>
+      <c r="D4" s="250">
+        <v>1</v>
+      </c>
+      <c r="E4" s="268" t="s">
         <v>373</v>
       </c>
     </row>
@@ -30094,34 +30006,34 @@
       <c r="A5" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="253" t="s">
+      <c r="B5" s="249" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="254"/>
-      <c r="D5" s="254">
-        <v>1</v>
-      </c>
-      <c r="E5" s="272" t="s">
+      <c r="C5" s="250"/>
+      <c r="D5" s="250">
+        <v>1</v>
+      </c>
+      <c r="E5" s="268" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="18"/>
-      <c r="B6" s="253" t="s">
+      <c r="B6" s="249" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="254">
+      <c r="D6" s="250">
         <v>1</v>
       </c>
       <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="18"/>
-      <c r="B7" s="254" t="s">
+      <c r="B7" s="250" t="s">
         <v>601</v>
       </c>
-      <c r="C7" s="254"/>
-      <c r="D7" s="254">
+      <c r="C7" s="250"/>
+      <c r="D7" s="250">
         <v>1</v>
       </c>
       <c r="E7" s="39"/>
@@ -30131,8 +30043,8 @@
       <c r="B8" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="254"/>
-      <c r="D8" s="254">
+      <c r="C8" s="250"/>
+      <c r="D8" s="250">
         <v>4</v>
       </c>
       <c r="E8" s="39"/>
@@ -30142,7 +30054,7 @@
       <c r="B9" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="254">
+      <c r="D9" s="250">
         <v>12</v>
       </c>
       <c r="E9" s="39"/>
@@ -30152,7 +30064,7 @@
       <c r="B10" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="254">
+      <c r="D10" s="250">
         <v>4</v>
       </c>
       <c r="E10" s="39"/>
@@ -30162,7 +30074,7 @@
       <c r="B11" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="254">
+      <c r="D11" s="250">
         <v>4</v>
       </c>
       <c r="E11" s="39"/>
@@ -30174,7 +30086,7 @@
       <c r="B12" t="s">
         <v>384</v>
       </c>
-      <c r="D12" s="254">
+      <c r="D12" s="250">
         <v>2</v>
       </c>
       <c r="E12" s="39"/>
@@ -30184,7 +30096,7 @@
       <c r="B13" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D13" s="254">
+      <c r="D13" s="250">
         <v>2</v>
       </c>
       <c r="E13" s="39"/>
@@ -30194,7 +30106,7 @@
       <c r="B14" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="254">
+      <c r="D14" s="250">
         <v>6</v>
       </c>
       <c r="E14" s="39"/>
@@ -30204,17 +30116,17 @@
       <c r="B15" t="s">
         <v>602</v>
       </c>
-      <c r="D15" s="254">
+      <c r="D15" s="250">
         <v>1</v>
       </c>
       <c r="E15" s="39"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="18"/>
-      <c r="B16" s="249" t="s">
+      <c r="B16" s="245" t="s">
         <v>603</v>
       </c>
-      <c r="D16" s="254">
+      <c r="D16" s="250">
         <v>1</v>
       </c>
       <c r="E16" s="39"/>
@@ -30224,7 +30136,7 @@
       <c r="B17" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="D17" s="254">
+      <c r="D17" s="250">
         <v>1</v>
       </c>
       <c r="E17" s="39"/>
@@ -30235,7 +30147,7 @@
         <v>605</v>
       </c>
       <c r="C18" s="35"/>
-      <c r="D18" s="278">
+      <c r="D18" s="274">
         <v>1</v>
       </c>
       <c r="E18" s="46"/>
@@ -30286,10 +30198,10 @@
       <c r="B1" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="260" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="260" t="s">
         <v>363</v>
       </c>
       <c r="E1" s="33"/>
@@ -30324,7 +30236,7 @@
       <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="272" t="s">
+      <c r="E3" s="268" t="s">
         <v>370</v>
       </c>
     </row>
@@ -30341,7 +30253,7 @@
       <c r="D4" s="9">
         <v>1</v>
       </c>
-      <c r="E4" s="272" t="s">
+      <c r="E4" s="268" t="s">
         <v>373</v>
       </c>
     </row>
@@ -30352,25 +30264,25 @@
       <c r="B5" s="22" t="s">
         <v>610</v>
       </c>
-      <c r="C5" s="254" t="s">
+      <c r="C5" s="250" t="s">
         <v>611</v>
       </c>
-      <c r="D5" s="260">
+      <c r="D5" s="256">
         <v>2</v>
       </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="268" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="18"/>
-      <c r="B6" s="279" t="s">
+      <c r="B6" s="275" t="s">
         <v>610</v>
       </c>
-      <c r="C6" s="254" t="s">
+      <c r="C6" s="250" t="s">
         <v>612</v>
       </c>
-      <c r="D6" s="260">
+      <c r="D6" s="256">
         <v>5</v>
       </c>
       <c r="E6" s="39"/>
@@ -30380,10 +30292,10 @@
       <c r="B7" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="C7" s="254" t="s">
+      <c r="C7" s="250" t="s">
         <v>611</v>
       </c>
-      <c r="D7" s="260">
+      <c r="D7" s="256">
         <v>2</v>
       </c>
       <c r="E7" s="39"/>
@@ -30393,7 +30305,7 @@
       <c r="B8" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="C8" s="254" t="s">
+      <c r="C8" s="250" t="s">
         <v>612</v>
       </c>
       <c r="D8" s="9">
@@ -30403,10 +30315,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="18"/>
-      <c r="B9" s="280" t="s">
+      <c r="B9" s="276" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="254" t="s">
+      <c r="C9" s="250" t="s">
         <v>614</v>
       </c>
       <c r="D9" s="9">
@@ -30419,10 +30331,10 @@
       <c r="B10" s="22" t="s">
         <v>615</v>
       </c>
-      <c r="C10" s="254" t="s">
+      <c r="C10" s="250" t="s">
         <v>611</v>
       </c>
-      <c r="D10" s="260">
+      <c r="D10" s="256">
         <v>2</v>
       </c>
       <c r="E10" s="39"/>
@@ -30432,7 +30344,7 @@
       <c r="B11" s="22" t="s">
         <v>615</v>
       </c>
-      <c r="C11" s="254" t="s">
+      <c r="C11" s="250" t="s">
         <v>612</v>
       </c>
       <c r="D11" s="9">
@@ -30444,10 +30356,10 @@
       <c r="A12" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="B12" s="280" t="s">
+      <c r="B12" s="276" t="s">
         <v>616</v>
       </c>
-      <c r="C12" s="254" t="s">
+      <c r="C12" s="250" t="s">
         <v>617</v>
       </c>
       <c r="D12" s="9">
@@ -30460,10 +30372,10 @@
       <c r="B13" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="C13" s="254" t="s">
+      <c r="C13" s="250" t="s">
         <v>619</v>
       </c>
-      <c r="D13" s="260">
+      <c r="D13" s="256">
         <v>2</v>
       </c>
       <c r="E13" s="39"/>
@@ -30473,10 +30385,10 @@
       <c r="B14" s="22" t="s">
         <v>610</v>
       </c>
-      <c r="C14" s="254" t="s">
+      <c r="C14" s="250" t="s">
         <v>619</v>
       </c>
-      <c r="D14" s="260">
+      <c r="D14" s="256">
         <v>2</v>
       </c>
       <c r="E14" s="39"/>
@@ -30486,10 +30398,10 @@
       <c r="B15" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="C15" s="254" t="s">
+      <c r="C15" s="250" t="s">
         <v>611</v>
       </c>
-      <c r="D15" s="260">
+      <c r="D15" s="256">
         <v>2</v>
       </c>
       <c r="E15" s="39"/>
@@ -30499,36 +30411,36 @@
       <c r="B16" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="C16" s="254" t="s">
+      <c r="C16" s="250" t="s">
         <v>612</v>
       </c>
-      <c r="D16" s="260">
+      <c r="D16" s="256">
         <v>5</v>
       </c>
       <c r="E16" s="39"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="18"/>
-      <c r="B17" s="280" t="s">
+      <c r="B17" s="276" t="s">
         <v>620</v>
       </c>
-      <c r="C17" s="254" t="s">
+      <c r="C17" s="250" t="s">
         <v>621</v>
       </c>
-      <c r="D17" s="260">
+      <c r="D17" s="256">
         <v>5</v>
       </c>
       <c r="E17" s="39"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="18"/>
-      <c r="B18" s="280" t="s">
+      <c r="B18" s="276" t="s">
         <v>620</v>
       </c>
-      <c r="C18" s="254" t="s">
+      <c r="C18" s="250" t="s">
         <v>612</v>
       </c>
-      <c r="D18" s="260">
+      <c r="D18" s="256">
         <v>5</v>
       </c>
       <c r="E18" s="39"/>
@@ -30548,7 +30460,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="18"/>
-      <c r="B20" s="279" t="s">
+      <c r="B20" s="275" t="s">
         <v>610</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -30600,10 +30512,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="18"/>
-      <c r="B24" s="273" t="s">
+      <c r="B24" s="269" t="s">
         <v>627</v>
       </c>
-      <c r="C24" s="273" t="s">
+      <c r="C24" s="269" t="s">
         <v>444</v>
       </c>
       <c r="D24" s="40"/>
@@ -30611,20 +30523,20 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="18"/>
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="250" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="254" t="s">
+      <c r="C25" s="250" t="s">
         <v>628</v>
       </c>
-      <c r="D25" s="254">
+      <c r="D25" s="250">
         <v>1</v>
       </c>
       <c r="E25" s="39"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="18"/>
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="250" t="s">
         <v>629</v>
       </c>
       <c r="D26" s="9">
@@ -30688,10 +30600,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="18"/>
-      <c r="B32" s="253" t="s">
+      <c r="B32" s="249" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="254">
+      <c r="D32" s="250">
         <v>1</v>
       </c>
       <c r="E32" s="39"/>
@@ -30786,10 +30698,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="18"/>
-      <c r="B41" s="280" t="s">
+      <c r="B41" s="276" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="254" t="s">
+      <c r="C41" s="250" t="s">
         <v>630</v>
       </c>
       <c r="D41" s="9">
@@ -30799,10 +30711,10 @@
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="18"/>
-      <c r="B42" s="280" t="s">
+      <c r="B42" s="276" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="254" t="s">
+      <c r="C42" s="250" t="s">
         <v>630</v>
       </c>
       <c r="D42" s="9">
@@ -30815,7 +30727,7 @@
       <c r="B43" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="C43" s="254" t="s">
+      <c r="C43" s="250" t="s">
         <v>630</v>
       </c>
       <c r="D43" s="9">
@@ -30825,10 +30737,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="18"/>
-      <c r="B44" s="280" t="s">
+      <c r="B44" s="276" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="254" t="s">
+      <c r="C44" s="250" t="s">
         <v>632</v>
       </c>
       <c r="D44" s="9">
@@ -30841,23 +30753,23 @@
       <c r="B45" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="C45" s="254" t="s">
+      <c r="C45" s="250" t="s">
         <v>634</v>
       </c>
-      <c r="D45" s="254">
+      <c r="D45" s="250">
         <v>1</v>
       </c>
       <c r="E45" s="39"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="18"/>
-      <c r="B46" s="280" t="s">
+      <c r="B46" s="276" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="254" t="s">
+      <c r="C46" s="250" t="s">
         <v>635</v>
       </c>
-      <c r="D46" s="254">
+      <c r="D46" s="250">
         <v>1</v>
       </c>
       <c r="E46" s="39"/>
@@ -30867,7 +30779,7 @@
       <c r="B47" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C47" s="254" t="s">
+      <c r="C47" s="250" t="s">
         <v>636</v>
       </c>
       <c r="D47" s="9">
@@ -30880,7 +30792,7 @@
       <c r="B48" t="s">
         <v>637</v>
       </c>
-      <c r="C48" s="254" t="s">
+      <c r="C48" s="250" t="s">
         <v>638</v>
       </c>
       <c r="D48" s="9">
@@ -30893,7 +30805,7 @@
       <c r="B49" t="s">
         <v>639</v>
       </c>
-      <c r="C49" s="254" t="s">
+      <c r="C49" s="250" t="s">
         <v>640</v>
       </c>
       <c r="D49" s="9">
@@ -30903,10 +30815,10 @@
     </row>
     <row r="50" spans="1:5" ht="16.5" customHeight="1">
       <c r="A50" s="18"/>
-      <c r="B50" s="254" t="s">
+      <c r="B50" s="250" t="s">
         <v>641</v>
       </c>
-      <c r="C50" s="254" t="s">
+      <c r="C50" s="250" t="s">
         <v>642</v>
       </c>
       <c r="D50" s="9">
@@ -30919,7 +30831,7 @@
       <c r="B51" s="32" t="s">
         <v>643</v>
       </c>
-      <c r="C51" s="278" t="s">
+      <c r="C51" s="274" t="s">
         <v>638</v>
       </c>
       <c r="D51" s="45">

--- a/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5914" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C0DC06-E4DF-434B-981E-5F5987C62BDB}"/>
+  <xr:revisionPtr revIDLastSave="5915" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E28401-5A2B-4AD3-A891-59713B363E0A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMPLETE PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -1211,9 +1211,6 @@
     <t>Z Height Profile</t>
   </si>
   <si>
-    <t>2820 L-Bracket</t>
-  </si>
-  <si>
     <t>Corner Bracket</t>
   </si>
   <si>
@@ -3771,6 +3768,9 @@
   </si>
   <si>
     <t>add chamber fan tacho signal</t>
+  </si>
+  <si>
+    <t>2028 L-Bracket</t>
   </si>
 </sst>
 </file>
@@ -4577,7 +4577,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="327">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
@@ -5262,22 +5262,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="12" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5295,9 +5279,6 @@
     <cellStyle name="Normal 9" xfId="9" xr:uid="{40B67649-AC0A-4FC1-B41E-42AB5C2B58C9}"/>
   </cellStyles>
   <dxfs count="103">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5913,6 +5894,9 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -5951,16 +5935,16 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </right>
         <top style="medium">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
         <bottom style="medium">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -6115,83 +6099,6 @@
         </top>
         <bottom style="medium">
           <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -6864,6 +6771,83 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -8065,68 +8049,64 @@
 </namedSheetViews>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView2.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J151" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J151" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94" tableBorderDxfId="92" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J151" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J151">
     <sortCondition ref="A1:A151"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="96"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="95"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="93"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="92">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="90"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="88"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="86">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="91" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="89" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="85" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="84"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="83" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D74" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D74" totalsRowShown="0" headerRowDxfId="101" tableBorderDxfId="100" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D74" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D74">
     <sortCondition ref="B1:B74"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="99" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="98" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="97" totalsRowDxfId="96" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:G94" totalsRowCount="1" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:G94" totalsRowCount="1" headerRowDxfId="32">
   <autoFilter ref="A1:G93" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G91">
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Normal 7">
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="23" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>$J$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8139,7 +8119,7 @@
     <sortCondition ref="A1:A12"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="18"/>
     <tableColumn id="1" xr3:uid="{E1FF070C-6993-4332-802B-B4D29E1606E7}" name="Function"/>
     <tableColumn id="3" xr3:uid="{8FBB1689-4854-43C5-AC93-F6E571CF242D}" name="Description"/>
   </tableColumns>
@@ -8154,8 +8134,8 @@
     <sortCondition ref="A15:A31"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{A5B4F8F7-1DD2-464C-B2BB-DB18FF666977}" name="Gcode" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{A5B4F8F7-1DD2-464C-B2BB-DB18FF666977}" name="Gcode" dataDxfId="16"/>
     <tableColumn id="3" xr3:uid="{5B376876-1002-41A2-9B1B-97FBB74534E9}" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -8188,7 +8168,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
   <autoFilter ref="A4:L37" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8207,94 +8187,94 @@
     <sortCondition ref="A5:A37"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{197BC419-568C-45F9-A938-BCB10710A201}" name="Filament Name" dataDxfId="12" dataCellStyle="Normal 12"/>
-    <tableColumn id="2" xr3:uid="{AF3208FB-C432-479D-9CC1-34948B0D1C5F}" name="Build Sheet" dataDxfId="11" dataCellStyle="Normal 12"/>
-    <tableColumn id="4" xr3:uid="{FF9DC98D-9012-4B85-A61B-230EFCA62E94}" name="Cooling Fan Speed" dataDxfId="10" dataCellStyle="Normal 12"/>
-    <tableColumn id="5" xr3:uid="{6FC298B8-D32B-492D-BD10-401FC09A08D1}" name="Tg" dataDxfId="9" dataCellStyle="Normal 12"/>
-    <tableColumn id="6" xr3:uid="{8CBD91F1-4D45-4A1E-A8F8-EE3D4C691E6E}" name="Nozzle Temp" dataDxfId="8" dataCellStyle="Normal 12"/>
-    <tableColumn id="7" xr3:uid="{8281603E-57B6-4F65-AF6B-69F4FB88F5E0}" name="Bed Temp" dataDxfId="7" dataCellStyle="Normal 12"/>
-    <tableColumn id="8" xr3:uid="{DF87AE05-A3BC-421E-9BB7-23A2ABF4C361}" name="Chamber Temp" dataDxfId="6" dataCellStyle="Normal 12"/>
-    <tableColumn id="9" xr3:uid="{845BBCDF-F13A-47FB-8E5D-2AECC511780B}" name="Drying Temp" dataDxfId="5" dataCellStyle="Normal 12"/>
-    <tableColumn id="10" xr3:uid="{D362A04F-6A04-476D-AC24-1BCA0C4F59DB}" name="Drying Time" dataDxfId="4" dataCellStyle="Normal 12"/>
-    <tableColumn id="11" xr3:uid="{6994BD7F-8192-40FA-9548-36A5EE628106}" name="HDT" dataDxfId="3" dataCellStyle="Normal 12"/>
-    <tableColumn id="12" xr3:uid="{0856005B-5B46-415C-BB48-BE1984071133}" name="HDT-A" dataDxfId="2" dataCellStyle="Normal 12"/>
-    <tableColumn id="13" xr3:uid="{AC83266E-6805-4F79-BED7-5D3490D455AA}" name="Bending Modulus MPa" dataDxfId="1" dataCellStyle="Normal 12"/>
+    <tableColumn id="1" xr3:uid="{197BC419-568C-45F9-A938-BCB10710A201}" name="Filament Name" dataDxfId="11" dataCellStyle="Normal 12"/>
+    <tableColumn id="2" xr3:uid="{AF3208FB-C432-479D-9CC1-34948B0D1C5F}" name="Build Sheet" dataDxfId="10" dataCellStyle="Normal 12"/>
+    <tableColumn id="4" xr3:uid="{FF9DC98D-9012-4B85-A61B-230EFCA62E94}" name="Cooling Fan Speed" dataDxfId="9" dataCellStyle="Normal 12"/>
+    <tableColumn id="5" xr3:uid="{6FC298B8-D32B-492D-BD10-401FC09A08D1}" name="Tg" dataDxfId="8" dataCellStyle="Normal 12"/>
+    <tableColumn id="6" xr3:uid="{8CBD91F1-4D45-4A1E-A8F8-EE3D4C691E6E}" name="Nozzle Temp" dataDxfId="7" dataCellStyle="Normal 12"/>
+    <tableColumn id="7" xr3:uid="{8281603E-57B6-4F65-AF6B-69F4FB88F5E0}" name="Bed Temp" dataDxfId="6" dataCellStyle="Normal 12"/>
+    <tableColumn id="8" xr3:uid="{DF87AE05-A3BC-421E-9BB7-23A2ABF4C361}" name="Chamber Temp" dataDxfId="5" dataCellStyle="Normal 12"/>
+    <tableColumn id="9" xr3:uid="{845BBCDF-F13A-47FB-8E5D-2AECC511780B}" name="Drying Temp" dataDxfId="4" dataCellStyle="Normal 12"/>
+    <tableColumn id="10" xr3:uid="{D362A04F-6A04-476D-AC24-1BCA0C4F59DB}" name="Drying Time" dataDxfId="3" dataCellStyle="Normal 12"/>
+    <tableColumn id="11" xr3:uid="{6994BD7F-8192-40FA-9548-36A5EE628106}" name="HDT" dataDxfId="2" dataCellStyle="Normal 12"/>
+    <tableColumn id="12" xr3:uid="{0856005B-5B46-415C-BB48-BE1984071133}" name="HDT-A" dataDxfId="1" dataCellStyle="Normal 12"/>
+    <tableColumn id="13" xr3:uid="{AC83266E-6805-4F79-BED7-5D3490D455AA}" name="Bending Modulus MPa" dataDxfId="0" dataCellStyle="Normal 12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86" tableBorderDxfId="85" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="82" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="76" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D30" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D30" totalsRowShown="0" headerRowDxfId="68" tableBorderDxfId="67" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D30" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D30">
     <sortCondition ref="B1:B30"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="71" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B33:D44" totalsRowShown="0" headerRowDxfId="68" tableBorderDxfId="67" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B33:D44" totalsRowShown="0" headerRowDxfId="62" tableBorderDxfId="61" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B33:D44" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:D44">
     <sortCondition ref="B33:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="59" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D55" totalsRowShown="0" headerRowDxfId="62" tableBorderDxfId="61" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D55" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D55" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D55">
     <sortCondition ref="B1:B55"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8316,30 +8296,30 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D17" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D17" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D17" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D17">
     <sortCondition ref="B1:B17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="0" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D86" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D86" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D86" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D86">
     <sortCondition ref="B1:B86"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="34" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13497,46 +13477,46 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B1" t="s">
         <v>1177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1178</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1179</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B2" t="s">
         <v>1181</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="98" t="s">
         <v>1182</v>
-      </c>
-      <c r="C2" s="98" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="88" t="s">
         <v>1185</v>
-      </c>
-      <c r="C3" s="88" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B4" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C4" t="s">
         <v>361</v>
@@ -13544,98 +13524,89 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B5" t="s">
         <v>1188</v>
       </c>
-      <c r="B5" t="s">
-        <v>1189</v>
-      </c>
       <c r="C5" s="193" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B6" t="s">
         <v>1190</v>
       </c>
-      <c r="B6" t="s">
-        <v>1191</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B8" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="149" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="317" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B12" s="317" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C12" s="318"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="318"/>
-      <c r="B13" s="318"/>
-      <c r="C13" s="318"/>
+      <c r="B12" s="1" t="s">
+        <v>1181</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="317" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B14" s="318"/>
-      <c r="C14" s="318"/>
+      <c r="A14" s="1" t="s">
+        <v>1233</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="317" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B15" s="319" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C15" s="318"/>
+      <c r="A15" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1188</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13666,45 +13637,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>692</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>367</v>
       </c>
       <c r="E1" s="73" t="s">
+        <v>692</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C2" s="85">
         <v>98</v>
@@ -13722,7 +13693,7 @@
       </c>
       <c r="G2" s="77"/>
       <c r="I2" s="88" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="J2" s="88">
         <v>130</v>
@@ -13733,10 +13704,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C3" s="85">
         <v>10</v>
@@ -13756,7 +13727,7 @@
         <v>1.3888888888888888E-2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="J3">
         <v>130</v>
@@ -13770,10 +13741,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C4" s="85">
         <v>49</v>
@@ -13791,7 +13762,7 @@
       </c>
       <c r="G4" s="77"/>
       <c r="I4" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="J4" s="1">
         <v>155</v>
@@ -13805,10 +13776,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C5" s="85">
         <v>47</v>
@@ -13826,7 +13797,7 @@
       </c>
       <c r="G5" s="77"/>
       <c r="I5" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="J5" s="1">
         <v>150</v>
@@ -13837,10 +13808,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C6" s="85">
         <v>11</v>
@@ -13862,10 +13833,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C7" s="85">
         <v>200</v>
@@ -13887,10 +13858,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C8" s="85">
         <v>28</v>
@@ -13908,15 +13879,15 @@
       </c>
       <c r="G8" s="77"/>
       <c r="I8" s="45" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C9" s="85">
         <v>15</v>
@@ -13934,7 +13905,7 @@
       </c>
       <c r="G9" s="77"/>
       <c r="I9" s="87" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="J9" s="87">
         <v>3</v>
@@ -13945,10 +13916,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C10" s="85">
         <v>42</v>
@@ -13968,7 +13939,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J10">
         <v>0.25</v>
@@ -13979,10 +13950,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C11" s="85">
         <v>30</v>
@@ -14002,7 +13973,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="J11">
         <f>J9/J10</f>
@@ -14014,10 +13985,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C12" s="85"/>
       <c r="D12" s="22">
@@ -14033,7 +14004,7 @@
       </c>
       <c r="G12" s="77"/>
       <c r="I12" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J12">
         <f>J9/J10</f>
@@ -14045,10 +14016,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C13" s="85"/>
       <c r="D13" s="22">
@@ -14064,7 +14035,7 @@
       </c>
       <c r="G13" s="77"/>
       <c r="I13" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="J13">
         <v>0.6</v>
@@ -14075,10 +14046,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C14" s="85"/>
       <c r="D14" s="1">
@@ -14096,7 +14067,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J14" s="85">
         <f>J9/J13</f>
@@ -14108,10 +14079,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C15" s="85"/>
       <c r="D15" s="1">
@@ -14129,7 +14100,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J15" s="86">
         <v>0.2</v>
@@ -14140,10 +14111,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="85">
         <v>45</v>
@@ -14163,21 +14134,21 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="J16" s="148" t="s">
         <v>713</v>
       </c>
-      <c r="J16" s="148" t="s">
-        <v>714</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C17" s="85"/>
       <c r="D17" s="22">
@@ -14197,10 +14168,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C18" s="85"/>
       <c r="D18" s="1">
@@ -14218,10 +14189,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C19" s="85"/>
       <c r="D19" s="1">
@@ -14239,10 +14210,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C20" s="85"/>
       <c r="D20" s="1">
@@ -14260,10 +14231,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C21" s="85"/>
       <c r="D21" s="1">
@@ -14281,10 +14252,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C22" s="85"/>
       <c r="D22" s="1">
@@ -14302,10 +14273,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>716</v>
       </c>
       <c r="C23" s="85"/>
       <c r="D23" s="1">
@@ -14323,10 +14294,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C24" s="85"/>
       <c r="D24" s="1">
@@ -14344,10 +14315,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C25" s="85"/>
       <c r="D25" s="22">
@@ -14365,10 +14336,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C26" s="85"/>
       <c r="D26" s="1">
@@ -14386,10 +14357,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C27" s="85"/>
       <c r="D27" s="1">
@@ -14407,10 +14378,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C28" s="85"/>
       <c r="D28" s="22">
@@ -14428,10 +14399,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C29" s="85"/>
       <c r="D29" s="22">
@@ -14449,10 +14420,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C30" s="85"/>
       <c r="D30" s="22">
@@ -14470,10 +14441,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C31" s="85"/>
       <c r="D31" s="22">
@@ -14491,10 +14462,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C32" s="85"/>
       <c r="D32" s="22">
@@ -14512,10 +14483,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C33" s="85"/>
       <c r="D33" s="22">
@@ -14533,10 +14504,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C34" s="85"/>
       <c r="D34" s="22">
@@ -14554,10 +14525,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C35" s="85"/>
       <c r="D35" s="22">
@@ -14575,10 +14546,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C36" s="85"/>
       <c r="D36" s="22">
@@ -14596,10 +14567,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C37" s="85"/>
       <c r="D37" s="22">
@@ -14617,10 +14588,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C38" s="85"/>
       <c r="D38" s="76">
@@ -14638,10 +14609,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C39" s="85"/>
       <c r="D39" s="22">
@@ -14659,10 +14630,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C40" s="85"/>
       <c r="D40" s="22">
@@ -14680,10 +14651,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C41" s="85"/>
       <c r="D41" s="22">
@@ -14701,10 +14672,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C42" s="85"/>
       <c r="D42" s="22">
@@ -14722,10 +14693,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C43" s="85"/>
       <c r="D43" s="22">
@@ -14743,10 +14714,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C44" s="85"/>
       <c r="D44" s="22">
@@ -14764,10 +14735,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C45" s="85"/>
       <c r="D45" s="22">
@@ -14785,10 +14756,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C46" s="85"/>
       <c r="D46" s="22">
@@ -14806,10 +14777,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C47" s="85"/>
       <c r="D47" s="22">
@@ -14827,10 +14798,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C48" s="85"/>
       <c r="D48" s="22">
@@ -14848,10 +14819,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C49" s="85"/>
       <c r="D49" s="22">
@@ -14869,10 +14840,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C50" s="85"/>
       <c r="D50" s="22">
@@ -14890,10 +14861,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C51" s="85"/>
       <c r="D51" s="22">
@@ -14911,10 +14882,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="96" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C52" s="85"/>
       <c r="D52" s="22">
@@ -14932,10 +14903,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="96" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C53" s="85"/>
       <c r="D53" s="22">
@@ -14953,10 +14924,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C54" s="85"/>
       <c r="D54" s="22">
@@ -14974,10 +14945,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C55" s="85"/>
       <c r="D55" s="1">
@@ -14995,10 +14966,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C56" s="85"/>
       <c r="D56" s="1">
@@ -15016,10 +14987,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C57" s="85"/>
       <c r="D57" s="22">
@@ -15037,10 +15008,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C58" s="85"/>
       <c r="D58" s="22">
@@ -15058,10 +15029,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C59" s="85">
         <v>17</v>
@@ -15083,10 +15054,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C60" s="85"/>
       <c r="D60" s="1">
@@ -15104,10 +15075,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C61" s="85">
         <v>6</v>
@@ -15127,10 +15098,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C62" s="85">
         <v>9</v>
@@ -15150,10 +15121,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C63" s="85"/>
       <c r="D63" s="1">
@@ -15171,10 +15142,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C64" s="85"/>
       <c r="D64" s="26">
@@ -15192,10 +15163,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C65" s="85"/>
       <c r="D65" s="22">
@@ -15213,10 +15184,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B66" s="22" t="s">
         <v>720</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>721</v>
       </c>
       <c r="C66" s="85"/>
       <c r="D66" s="22">
@@ -15234,10 +15205,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B67" s="76" t="s">
         <v>722</v>
-      </c>
-      <c r="B67" s="76" t="s">
-        <v>723</v>
       </c>
       <c r="C67" s="85"/>
       <c r="D67" s="76">
@@ -15255,10 +15226,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B68" s="47" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C68" s="85"/>
       <c r="D68" s="47">
@@ -15278,10 +15249,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B69" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C69" s="85">
         <v>2</v>
@@ -15301,10 +15272,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B70" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C70" s="85">
         <v>9</v>
@@ -15324,10 +15295,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B71" s="47" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C71" s="85"/>
       <c r="D71" s="47">
@@ -15345,10 +15316,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B72" s="47" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C72" s="85"/>
       <c r="D72" s="47">
@@ -15366,10 +15337,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B73" s="47" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C73" s="85">
         <v>40</v>
@@ -15391,10 +15362,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C74" s="85">
         <v>40</v>
@@ -15416,10 +15387,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B75" s="47" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C75" s="85">
         <v>45</v>
@@ -15441,10 +15412,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B76" s="22" t="s">
         <v>725</v>
-      </c>
-      <c r="B76" s="22" t="s">
-        <v>726</v>
       </c>
       <c r="C76" s="85">
         <v>23</v>
@@ -15466,10 +15437,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C77" s="85">
         <v>47</v>
@@ -15489,10 +15460,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C78" s="85">
         <v>47</v>
@@ -15512,10 +15483,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C79" s="85">
         <v>47</v>
@@ -15535,10 +15506,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B80" s="22" t="s">
         <v>727</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>728</v>
       </c>
       <c r="C80" s="85"/>
       <c r="D80" s="47">
@@ -15556,10 +15527,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C81" s="85"/>
       <c r="D81" s="47">
@@ -15577,10 +15548,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C82" s="85"/>
       <c r="D82" s="47">
@@ -15598,10 +15569,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C83" s="85"/>
       <c r="D83" s="47">
@@ -15619,10 +15590,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C84" s="85"/>
       <c r="D84" s="47">
@@ -15640,10 +15611,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C85" s="85">
         <v>42</v>
@@ -15663,10 +15634,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C86" s="85">
         <v>42</v>
@@ -15686,10 +15657,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C87" s="85">
         <v>42</v>
@@ -15709,10 +15680,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C88" s="85"/>
       <c r="D88" s="47">
@@ -15730,10 +15701,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C89" s="85"/>
       <c r="D89" s="47">
@@ -15751,10 +15722,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C90" s="85"/>
       <c r="D90" s="47">
@@ -15772,10 +15743,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C91" s="85"/>
       <c r="D91" s="47">
@@ -15794,7 +15765,7 @@
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C92" s="85">
         <v>21</v>
@@ -15813,7 +15784,7 @@
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="22" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C93" s="85">
         <v>2</v>
@@ -15851,10 +15822,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="293" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C95">
         <v>46</v>
@@ -15865,10 +15836,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="96" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B96" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C96">
         <v>20</v>
@@ -15877,23 +15848,23 @@
         <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="96" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B97" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H97" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H98" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -15921,140 +15892,140 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1" t="s">
         <v>739</v>
-      </c>
-      <c r="B1" t="s">
-        <v>740</v>
       </c>
       <c r="C1" t="s">
         <v>365</v>
       </c>
       <c r="E1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
+        <v>744</v>
+      </c>
+      <c r="B3" t="s">
         <v>745</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="73" t="s">
         <v>746</v>
-      </c>
-      <c r="C3" s="73" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
+        <v>747</v>
+      </c>
+      <c r="B4" t="s">
         <v>748</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="4" t="s">
         <v>749</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
+        <v>750</v>
+      </c>
+      <c r="B5" t="s">
         <v>751</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>752</v>
-      </c>
-      <c r="C5" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="108" t="s">
+        <v>753</v>
+      </c>
+      <c r="B6" s="107" t="s">
         <v>754</v>
       </c>
-      <c r="B6" s="107" t="s">
+      <c r="C6" s="109" t="s">
         <v>755</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="E6" t="s">
         <v>756</v>
-      </c>
-      <c r="E6" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="B7" t="s">
         <v>758</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
+        <v>760</v>
+      </c>
+      <c r="B8" t="s">
         <v>761</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="90" t="s">
+        <v>763</v>
+      </c>
+      <c r="B9" t="s">
         <v>764</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
+        <v>766</v>
+      </c>
+      <c r="B10" t="s">
         <v>767</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>768</v>
-      </c>
-      <c r="C10" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>769</v>
+      </c>
+      <c r="B11" t="s">
         <v>770</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>771</v>
-      </c>
-      <c r="C11" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
+        <v>772</v>
+      </c>
+      <c r="B12" t="s">
         <v>773</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>774</v>
-      </c>
-      <c r="C12" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -16067,10 +16038,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B15" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C15" t="s">
         <v>365</v>
@@ -16078,137 +16049,137 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B16" t="s">
         <v>777</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>778</v>
-      </c>
-      <c r="C16" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
+        <v>779</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>780</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
+        <v>781</v>
+      </c>
+      <c r="C18" t="s">
         <v>782</v>
-      </c>
-      <c r="C18" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
+        <v>783</v>
+      </c>
+      <c r="C19" t="s">
         <v>784</v>
-      </c>
-      <c r="C19" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
+        <v>785</v>
+      </c>
+      <c r="C20" t="s">
         <v>786</v>
-      </c>
-      <c r="C20" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
+        <v>787</v>
+      </c>
+      <c r="C21" t="s">
         <v>788</v>
-      </c>
-      <c r="C21" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
+        <v>789</v>
+      </c>
+      <c r="C22" t="s">
         <v>790</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" s="95" t="s">
         <v>791</v>
-      </c>
-      <c r="E22" s="95" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="B23" t="s">
         <v>793</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>794</v>
-      </c>
-      <c r="C23" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
+        <v>795</v>
+      </c>
+      <c r="C24" t="s">
         <v>796</v>
-      </c>
-      <c r="C24" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
+        <v>797</v>
+      </c>
+      <c r="C25" t="s">
         <v>798</v>
-      </c>
-      <c r="C25" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
+        <v>799</v>
+      </c>
+      <c r="C26" t="s">
         <v>800</v>
-      </c>
-      <c r="C26" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B27" t="s">
         <v>802</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>803</v>
-      </c>
-      <c r="C27" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
+        <v>804</v>
+      </c>
+      <c r="B28" t="s">
         <v>805</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>806</v>
-      </c>
-      <c r="C28" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
+        <v>807</v>
+      </c>
+      <c r="C29" t="s">
         <v>808</v>
-      </c>
-      <c r="C29" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
+        <v>809</v>
+      </c>
+      <c r="C30" t="s">
         <v>810</v>
-      </c>
-      <c r="C30" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -16219,7 +16190,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="45" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B33" t="s">
         <v>365</v>
@@ -16227,55 +16198,55 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>812</v>
+      </c>
+      <c r="B34" t="s">
         <v>813</v>
-      </c>
-      <c r="B34" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B35" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B36" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B37" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
+        <v>817</v>
+      </c>
+      <c r="D39" t="s">
         <v>818</v>
-      </c>
-      <c r="D39" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
+        <v>819</v>
+      </c>
+      <c r="D40" t="s">
         <v>820</v>
-      </c>
-      <c r="D40" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B42" t="s">
         <v>365</v>
@@ -16283,82 +16254,82 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B43" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B44" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>824</v>
+      </c>
+      <c r="B45" t="s">
         <v>825</v>
-      </c>
-      <c r="B45" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B46" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B47" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B48" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B49" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B50" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B51" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B52" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -16397,12 +16368,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="159" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="160" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="156" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -16410,76 +16381,76 @@
       <c r="B3" s="161"/>
       <c r="C3" s="161"/>
       <c r="D3" s="154" t="s">
+        <v>835</v>
+      </c>
+      <c r="E3" s="154" t="s">
+        <v>835</v>
+      </c>
+      <c r="F3" s="154" t="s">
+        <v>835</v>
+      </c>
+      <c r="G3" s="154" t="s">
+        <v>835</v>
+      </c>
+      <c r="H3" s="154" t="s">
+        <v>835</v>
+      </c>
+      <c r="I3" s="154" t="s">
         <v>836</v>
-      </c>
-      <c r="E3" s="154" t="s">
-        <v>836</v>
-      </c>
-      <c r="F3" s="154" t="s">
-        <v>836</v>
-      </c>
-      <c r="G3" s="154" t="s">
-        <v>836</v>
-      </c>
-      <c r="H3" s="154" t="s">
-        <v>836</v>
-      </c>
-      <c r="I3" s="154" t="s">
-        <v>837</v>
       </c>
       <c r="J3" s="154"/>
       <c r="K3" s="154"/>
       <c r="L3" s="155" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="156" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="162" t="s">
+        <v>838</v>
+      </c>
+      <c r="B4" s="162" t="s">
         <v>839</v>
       </c>
-      <c r="B4" s="162" t="s">
+      <c r="C4" s="162" t="s">
         <v>840</v>
       </c>
-      <c r="C4" s="162" t="s">
+      <c r="D4" s="162" t="s">
         <v>841</v>
       </c>
-      <c r="D4" s="162" t="s">
+      <c r="E4" s="162" t="s">
         <v>842</v>
       </c>
-      <c r="E4" s="162" t="s">
+      <c r="F4" s="162" t="s">
         <v>843</v>
       </c>
-      <c r="F4" s="162" t="s">
+      <c r="G4" s="162" t="s">
         <v>844</v>
       </c>
-      <c r="G4" s="162" t="s">
+      <c r="H4" s="162" t="s">
         <v>845</v>
       </c>
-      <c r="H4" s="162" t="s">
+      <c r="I4" s="162" t="s">
         <v>846</v>
       </c>
-      <c r="I4" s="162" t="s">
+      <c r="J4" s="162" t="s">
         <v>847</v>
       </c>
-      <c r="J4" s="162" t="s">
+      <c r="K4" s="162" t="s">
         <v>848</v>
       </c>
-      <c r="K4" s="162" t="s">
+      <c r="L4" s="162" t="s">
         <v>849</v>
-      </c>
-      <c r="L4" s="162" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="163" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B5" s="294" t="s">
+        <v>850</v>
+      </c>
+      <c r="C5" s="295" t="s">
         <v>851</v>
-      </c>
-      <c r="C5" s="295" t="s">
-        <v>852</v>
       </c>
       <c r="D5" s="295">
         <v>105</v>
@@ -16511,13 +16482,13 @@
     </row>
     <row r="6" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="163" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B6" s="294" t="s">
+        <v>850</v>
+      </c>
+      <c r="C6" s="295" t="s">
         <v>851</v>
-      </c>
-      <c r="C6" s="295" t="s">
-        <v>852</v>
       </c>
       <c r="D6" s="295">
         <v>105</v>
@@ -16549,13 +16520,13 @@
     </row>
     <row r="7" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="163" t="s">
+        <v>853</v>
+      </c>
+      <c r="B7" s="294" t="s">
         <v>854</v>
       </c>
-      <c r="B7" s="294" t="s">
+      <c r="C7" s="295" t="s">
         <v>855</v>
-      </c>
-      <c r="C7" s="295" t="s">
-        <v>856</v>
       </c>
       <c r="D7" s="295">
         <v>90</v>
@@ -16587,10 +16558,10 @@
     </row>
     <row r="8" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="163" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B8" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C8" s="295">
         <v>0</v>
@@ -16608,10 +16579,10 @@
         <v>50</v>
       </c>
       <c r="H8" s="295" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="J8" s="295">
         <v>80</v>
@@ -16625,13 +16596,13 @@
     </row>
     <row r="9" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="164" t="s">
+        <v>858</v>
+      </c>
+      <c r="B9" s="294" t="s">
         <v>859</v>
       </c>
-      <c r="B9" s="294" t="s">
-        <v>860</v>
-      </c>
       <c r="C9" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D9" s="295">
         <v>105</v>
@@ -16663,13 +16634,13 @@
     </row>
     <row r="10" spans="1:12" s="156" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="164" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B10" s="294" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C10" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D10" s="295">
         <v>60</v>
@@ -16701,13 +16672,13 @@
     </row>
     <row r="11" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="164" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B11" s="294" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C11" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D11" s="295">
         <v>60</v>
@@ -16739,13 +16710,13 @@
     </row>
     <row r="12" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="164" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B12" s="294" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C12" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D12" s="295">
         <v>60</v>
@@ -16777,13 +16748,13 @@
     </row>
     <row r="13" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="164" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B13" s="294" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C13" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D13" s="295">
         <v>70</v>
@@ -16815,10 +16786,10 @@
     </row>
     <row r="14" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="164" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B14" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C14" s="295">
         <v>0</v>
@@ -16853,11 +16824,11 @@
     </row>
     <row r="15" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="163" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B15" s="294"/>
       <c r="C15" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D15" s="295">
         <v>137</v>
@@ -16889,11 +16860,11 @@
     </row>
     <row r="16" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="163" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B16" s="294"/>
       <c r="C16" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D16" s="295">
         <v>126</v>
@@ -16925,13 +16896,13 @@
     </row>
     <row r="17" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="164" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B17" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C17" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D17" s="295">
         <v>145</v>
@@ -16963,13 +16934,13 @@
     </row>
     <row r="18" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="164" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B18" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C18" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D18" s="295">
         <v>113</v>
@@ -17001,11 +16972,11 @@
     </row>
     <row r="19" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="164" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B19" s="294"/>
       <c r="C19" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D19" s="295">
         <v>158</v>
@@ -17037,11 +17008,11 @@
     </row>
     <row r="20" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="164" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B20" s="294"/>
       <c r="C20" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D20" s="295">
         <v>143</v>
@@ -17073,11 +17044,11 @@
     </row>
     <row r="21" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="164" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B21" s="294"/>
       <c r="C21" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D21" s="295">
         <v>140</v>
@@ -17109,13 +17080,13 @@
     </row>
     <row r="22" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="164" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B22" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C22" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D22" s="295">
         <v>113</v>
@@ -17147,13 +17118,13 @@
     </row>
     <row r="23" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="163" t="s">
+        <v>872</v>
+      </c>
+      <c r="B23" s="294" t="s">
         <v>873</v>
       </c>
-      <c r="B23" s="294" t="s">
-        <v>874</v>
-      </c>
       <c r="C23" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D23" s="295">
         <v>143</v>
@@ -17185,13 +17156,13 @@
     </row>
     <row r="24" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="163" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B24" s="294" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C24" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D24" s="295">
         <v>165</v>
@@ -17223,13 +17194,13 @@
     </row>
     <row r="25" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="164" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B25" s="294" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C25" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D25" s="295">
         <v>165</v>
@@ -17261,13 +17232,13 @@
     </row>
     <row r="26" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="164" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B26" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C26" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D26" s="295">
         <v>70</v>
@@ -17299,13 +17270,13 @@
     </row>
     <row r="27" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="163" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B27" s="294" t="s">
+        <v>854</v>
+      </c>
+      <c r="C27" s="295" t="s">
         <v>855</v>
-      </c>
-      <c r="C27" s="295" t="s">
-        <v>856</v>
       </c>
       <c r="D27" s="295">
         <v>80</v>
@@ -17337,13 +17308,13 @@
     </row>
     <row r="28" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="163" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B28" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C28" s="295" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D28" s="295">
         <v>85</v>
@@ -17375,13 +17346,13 @@
     </row>
     <row r="29" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="164" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B29" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C29" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D29" s="295">
         <v>90</v>
@@ -17413,10 +17384,10 @@
     </row>
     <row r="30" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="163" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B30" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C30" s="295">
         <v>0</v>
@@ -17451,10 +17422,10 @@
     </row>
     <row r="31" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="164" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B31" s="294" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C31" s="295">
         <v>0</v>
@@ -17489,10 +17460,10 @@
     </row>
     <row r="32" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="163" t="s">
+        <v>879</v>
+      </c>
+      <c r="B32" s="294" t="s">
         <v>880</v>
-      </c>
-      <c r="B32" s="294" t="s">
-        <v>881</v>
       </c>
       <c r="C32" s="295">
         <v>0</v>
@@ -17527,10 +17498,10 @@
     </row>
     <row r="33" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="163" t="s">
+        <v>881</v>
+      </c>
+      <c r="B33" s="294" t="s">
         <v>882</v>
-      </c>
-      <c r="B33" s="294" t="s">
-        <v>883</v>
       </c>
       <c r="C33" s="295">
         <v>0</v>
@@ -17565,11 +17536,11 @@
     </row>
     <row r="34" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="163" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B34" s="294"/>
       <c r="C34" s="295" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D34" s="295">
         <v>170</v>
@@ -17584,10 +17555,10 @@
         <v>100</v>
       </c>
       <c r="H34" s="295" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I34" s="296" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="J34" s="295">
         <v>158</v>
@@ -17601,11 +17572,11 @@
     </row>
     <row r="35" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="163" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B35" s="294"/>
       <c r="C35" s="295" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D35" s="295">
         <v>80</v>
@@ -17637,10 +17608,10 @@
     </row>
     <row r="36" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="164" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B36" s="294" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C36" s="295">
         <v>0</v>
@@ -17675,7 +17646,7 @@
     </row>
     <row r="37" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="164" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B37" s="294"/>
       <c r="C37" s="295">
@@ -17711,7 +17682,7 @@
     </row>
     <row r="38" spans="1:12" s="156" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="151" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B38" s="313"/>
       <c r="C38" s="313"/>
@@ -17725,7 +17696,7 @@
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="169" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B39" s="315"/>
       <c r="C39" s="315"/>
@@ -17741,7 +17712,7 @@
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="171" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B40" s="165"/>
       <c r="C40" s="165"/>
@@ -17757,13 +17728,13 @@
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="173" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="L41" s="174"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="175" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B42" s="166"/>
       <c r="C42" s="166"/>
@@ -17779,7 +17750,7 @@
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="171" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B43" s="165"/>
       <c r="C43" s="165"/>
@@ -17795,7 +17766,7 @@
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="175" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B44" s="166"/>
       <c r="C44" s="166"/>
@@ -17811,7 +17782,7 @@
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="171" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B45" s="165"/>
       <c r="C45" s="165"/>
@@ -17827,7 +17798,7 @@
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="175" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B46" s="298"/>
       <c r="C46" s="298"/>
@@ -17843,7 +17814,7 @@
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="171" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B47" s="165"/>
       <c r="C47" s="165"/>
@@ -17859,7 +17830,7 @@
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="173" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E48" s="158"/>
       <c r="F48" s="158"/>
@@ -17872,7 +17843,7 @@
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="175" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B49" s="166"/>
       <c r="C49" s="166"/>
@@ -17888,7 +17859,7 @@
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="171" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B50" s="165"/>
       <c r="C50" s="165"/>
@@ -17904,7 +17875,7 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="173" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E51" s="158"/>
       <c r="F51" s="158"/>
@@ -17917,7 +17888,7 @@
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="177" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B52" s="178"/>
       <c r="C52" s="178"/>
@@ -24481,7 +24452,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="92" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -24489,32 +24460,32 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="93" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="94" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="92" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="92" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="92" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="92" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -24522,17 +24493,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="93" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="94" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="92" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -24540,37 +24511,37 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="93" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="92" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="92" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="92" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="92" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="92" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="92" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -24578,22 +24549,22 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="92" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="92" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="92" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -24622,112 +24593,112 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="306" t="s">
+        <v>923</v>
+      </c>
+      <c r="B1" s="307" t="s">
         <v>924</v>
       </c>
-      <c r="B1" s="307" t="s">
+      <c r="C1" s="307" t="s">
         <v>925</v>
       </c>
-      <c r="C1" s="307" t="s">
+      <c r="D1" s="307" t="s">
         <v>926</v>
       </c>
-      <c r="D1" s="307" t="s">
+      <c r="E1" s="307" t="s">
         <v>927</v>
       </c>
-      <c r="E1" s="307" t="s">
+      <c r="F1" s="307" t="s">
         <v>928</v>
       </c>
-      <c r="F1" s="307" t="s">
+      <c r="G1" s="308" t="s">
         <v>929</v>
       </c>
-      <c r="G1" s="308" t="s">
+      <c r="H1" s="140" t="s">
         <v>930</v>
-      </c>
-      <c r="H1" s="140" t="s">
-        <v>931</v>
       </c>
       <c r="I1" s="309"/>
       <c r="J1" s="309" t="s">
+        <v>931</v>
+      </c>
+      <c r="K1" s="309" t="s">
         <v>932</v>
-      </c>
-      <c r="K1" s="309" t="s">
-        <v>933</v>
       </c>
       <c r="L1" s="309"/>
       <c r="M1" s="309"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="306" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2" s="307">
+        <v>1</v>
+      </c>
+      <c r="C2" s="307">
+        <v>1</v>
+      </c>
+      <c r="D2" s="307">
+        <v>1</v>
+      </c>
+      <c r="E2" s="307">
+        <v>1</v>
+      </c>
+      <c r="F2" s="307">
+        <v>1</v>
+      </c>
+      <c r="G2" s="308" t="s">
         <v>934</v>
-      </c>
-      <c r="B2" s="307">
-        <v>1</v>
-      </c>
-      <c r="C2" s="307">
-        <v>1</v>
-      </c>
-      <c r="D2" s="307">
-        <v>1</v>
-      </c>
-      <c r="E2" s="307">
-        <v>1</v>
-      </c>
-      <c r="F2" s="307">
-        <v>1</v>
-      </c>
-      <c r="G2" s="308" t="s">
-        <v>935</v>
       </c>
       <c r="H2" s="140">
         <v>2</v>
       </c>
       <c r="I2" s="309"/>
       <c r="J2" s="309" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K2" s="309" t="s">
+        <v>935</v>
+      </c>
+      <c r="L2" s="309" t="s">
         <v>936</v>
-      </c>
-      <c r="L2" s="309" t="s">
-        <v>937</v>
       </c>
       <c r="M2" s="309"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="306" t="s">
+        <v>937</v>
+      </c>
+      <c r="B3" s="307" t="s">
         <v>938</v>
       </c>
-      <c r="B3" s="307" t="s">
+      <c r="C3" s="307" t="s">
         <v>939</v>
       </c>
-      <c r="C3" s="307" t="s">
+      <c r="D3" s="146" t="s">
+        <v>938</v>
+      </c>
+      <c r="E3" s="146" t="s">
+        <v>938</v>
+      </c>
+      <c r="F3" s="307" t="s">
         <v>940</v>
-      </c>
-      <c r="D3" s="146" t="s">
-        <v>939</v>
-      </c>
-      <c r="E3" s="146" t="s">
-        <v>939</v>
-      </c>
-      <c r="F3" s="307" t="s">
-        <v>941</v>
       </c>
       <c r="G3" s="308"/>
       <c r="H3" s="140" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="I3" s="309"/>
       <c r="J3" s="309"/>
       <c r="K3" s="309" t="s">
+        <v>941</v>
+      </c>
+      <c r="L3" s="309" t="s">
         <v>942</v>
-      </c>
-      <c r="L3" s="309" t="s">
-        <v>943</v>
       </c>
       <c r="M3" s="309"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="306" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B4" s="307">
         <v>450</v>
@@ -24736,7 +24707,7 @@
         <v>450</v>
       </c>
       <c r="D4" s="307" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E4" s="307">
         <v>285</v>
@@ -24748,35 +24719,35 @@
         <v>300</v>
       </c>
       <c r="H4" s="140" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I4" s="309"/>
       <c r="J4" s="310" t="s">
+        <v>946</v>
+      </c>
+      <c r="K4" s="309" t="s">
+        <v>706</v>
+      </c>
+      <c r="L4" s="309" t="s">
         <v>947</v>
-      </c>
-      <c r="K4" s="309" t="s">
-        <v>707</v>
-      </c>
-      <c r="L4" s="309" t="s">
-        <v>948</v>
       </c>
       <c r="M4" s="309"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="306" t="s">
+        <v>948</v>
+      </c>
+      <c r="B5" s="307" t="s">
         <v>949</v>
       </c>
-      <c r="B5" s="307" t="s">
+      <c r="C5" s="307" t="s">
         <v>950</v>
-      </c>
-      <c r="C5" s="307" t="s">
-        <v>951</v>
       </c>
       <c r="D5" s="307">
         <v>150</v>
       </c>
       <c r="E5" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F5" s="307">
         <v>157</v>
@@ -24785,23 +24756,23 @@
         <v>120</v>
       </c>
       <c r="H5" s="140" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="I5" s="309"/>
       <c r="J5" s="310" t="s">
+        <v>952</v>
+      </c>
+      <c r="K5" s="309" t="s">
         <v>953</v>
       </c>
-      <c r="K5" s="309" t="s">
+      <c r="L5" s="309" t="s">
         <v>954</v>
-      </c>
-      <c r="L5" s="309" t="s">
-        <v>955</v>
       </c>
       <c r="M5" s="309"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="306" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B6" s="307">
         <v>80</v>
@@ -24810,641 +24781,641 @@
         <v>100</v>
       </c>
       <c r="D6" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E6" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F6" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G6" s="308">
         <v>60</v>
       </c>
       <c r="H6" s="140" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="I6" s="309"/>
       <c r="J6" s="310" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="K6" s="309" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L6" s="309"/>
       <c r="M6" s="309"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="306" t="s">
+        <v>958</v>
+      </c>
+      <c r="B7" s="307" t="s">
         <v>959</v>
       </c>
-      <c r="B7" s="307" t="s">
+      <c r="C7" s="307" t="s">
         <v>960</v>
       </c>
-      <c r="C7" s="307" t="s">
+      <c r="D7" s="307" t="s">
         <v>961</v>
       </c>
-      <c r="D7" s="307" t="s">
+      <c r="E7" s="307" t="s">
         <v>962</v>
       </c>
-      <c r="E7" s="307" t="s">
+      <c r="F7" s="307" t="s">
         <v>963</v>
       </c>
-      <c r="F7" s="307" t="s">
+      <c r="G7" s="308" t="s">
         <v>964</v>
       </c>
-      <c r="G7" s="308" t="s">
+      <c r="H7" s="140" t="s">
         <v>965</v>
-      </c>
-      <c r="H7" s="140" t="s">
-        <v>966</v>
       </c>
       <c r="I7" s="309"/>
       <c r="J7" s="310" t="s">
+        <v>966</v>
+      </c>
+      <c r="K7" s="309" t="s">
         <v>967</v>
       </c>
-      <c r="K7" s="309" t="s">
+      <c r="L7" s="309" t="s">
         <v>968</v>
-      </c>
-      <c r="L7" s="309" t="s">
-        <v>969</v>
       </c>
       <c r="M7" s="309"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="306" t="s">
+        <v>969</v>
+      </c>
+      <c r="B8" s="307" t="s">
         <v>970</v>
       </c>
-      <c r="B8" s="307" t="s">
+      <c r="C8" s="307" t="s">
+        <v>970</v>
+      </c>
+      <c r="D8" s="307" t="s">
+        <v>857</v>
+      </c>
+      <c r="E8" s="307" t="s">
+        <v>970</v>
+      </c>
+      <c r="F8" s="307" t="s">
+        <v>970</v>
+      </c>
+      <c r="G8" s="308" t="s">
         <v>971</v>
       </c>
-      <c r="C8" s="307" t="s">
-        <v>971</v>
-      </c>
-      <c r="D8" s="307" t="s">
-        <v>858</v>
-      </c>
-      <c r="E8" s="307" t="s">
-        <v>971</v>
-      </c>
-      <c r="F8" s="307" t="s">
-        <v>971</v>
-      </c>
-      <c r="G8" s="308" t="s">
+      <c r="H8" s="140" t="s">
         <v>972</v>
-      </c>
-      <c r="H8" s="140" t="s">
-        <v>973</v>
       </c>
       <c r="I8" s="309"/>
       <c r="J8" s="309"/>
       <c r="K8" s="309" t="s">
+        <v>973</v>
+      </c>
+      <c r="L8" s="309" t="s">
         <v>974</v>
-      </c>
-      <c r="L8" s="309" t="s">
-        <v>975</v>
       </c>
       <c r="M8" s="309"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="306" t="s">
+        <v>975</v>
+      </c>
+      <c r="B9" s="307" t="s">
         <v>976</v>
       </c>
-      <c r="B9" s="307" t="s">
+      <c r="C9" s="307" t="s">
+        <v>976</v>
+      </c>
+      <c r="D9" s="307" t="s">
         <v>977</v>
       </c>
-      <c r="C9" s="307" t="s">
-        <v>977</v>
-      </c>
-      <c r="D9" s="307" t="s">
+      <c r="E9" s="307" t="s">
         <v>978</v>
       </c>
-      <c r="E9" s="307" t="s">
+      <c r="F9" s="307" t="s">
         <v>979</v>
-      </c>
-      <c r="F9" s="307" t="s">
-        <v>980</v>
       </c>
       <c r="G9" s="308"/>
       <c r="H9" s="140" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="I9" s="309"/>
       <c r="J9" s="309"/>
       <c r="K9" s="309" t="s">
+        <v>981</v>
+      </c>
+      <c r="L9" s="309" t="s">
         <v>982</v>
-      </c>
-      <c r="L9" s="309" t="s">
-        <v>983</v>
       </c>
       <c r="M9" s="309"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="306" t="s">
+        <v>983</v>
+      </c>
+      <c r="B10" s="311" t="s">
         <v>984</v>
       </c>
-      <c r="B10" s="311" t="s">
+      <c r="C10" s="311" t="s">
         <v>985</v>
       </c>
-      <c r="C10" s="311" t="s">
+      <c r="D10" s="311" t="s">
         <v>986</v>
       </c>
-      <c r="D10" s="311" t="s">
+      <c r="E10" s="311" t="s">
         <v>987</v>
       </c>
-      <c r="E10" s="311" t="s">
+      <c r="F10" s="307" t="s">
         <v>988</v>
       </c>
-      <c r="F10" s="307" t="s">
+      <c r="G10" s="141" t="s">
         <v>989</v>
       </c>
-      <c r="G10" s="141" t="s">
+      <c r="H10" s="140" t="s">
         <v>990</v>
-      </c>
-      <c r="H10" s="140" t="s">
-        <v>991</v>
       </c>
       <c r="I10" s="309"/>
       <c r="J10" s="309"/>
       <c r="K10" s="309" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="L10" s="309"/>
       <c r="M10" s="309"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="306" t="s">
+        <v>992</v>
+      </c>
+      <c r="B11" s="307" t="s">
         <v>993</v>
       </c>
-      <c r="B11" s="307" t="s">
+      <c r="C11" s="307" t="s">
+        <v>993</v>
+      </c>
+      <c r="D11" s="307" t="s">
         <v>994</v>
       </c>
-      <c r="C11" s="307" t="s">
-        <v>994</v>
-      </c>
-      <c r="D11" s="307" t="s">
+      <c r="E11" s="307" t="s">
         <v>995</v>
       </c>
-      <c r="E11" s="307" t="s">
+      <c r="F11" s="307" t="s">
         <v>996</v>
       </c>
-      <c r="F11" s="307" t="s">
-        <v>997</v>
-      </c>
       <c r="G11" s="308" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H11" s="140" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="I11" s="309"/>
       <c r="J11" s="310" t="s">
+        <v>997</v>
+      </c>
+      <c r="K11" s="309" t="s">
+        <v>991</v>
+      </c>
+      <c r="L11" s="309" t="s">
         <v>998</v>
-      </c>
-      <c r="K11" s="309" t="s">
-        <v>992</v>
-      </c>
-      <c r="L11" s="309" t="s">
-        <v>999</v>
       </c>
       <c r="M11" s="309"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="312" t="s">
+        <v>999</v>
+      </c>
+      <c r="B12" s="311" t="s">
         <v>1000</v>
       </c>
-      <c r="B12" s="311" t="s">
+      <c r="C12" s="311" t="s">
         <v>1001</v>
       </c>
-      <c r="C12" s="311" t="s">
+      <c r="D12" s="147" t="s">
         <v>1002</v>
       </c>
-      <c r="D12" s="147" t="s">
+      <c r="E12" s="311" t="s">
         <v>1003</v>
       </c>
-      <c r="E12" s="311" t="s">
+      <c r="F12" s="147" t="s">
         <v>1004</v>
-      </c>
-      <c r="F12" s="147" t="s">
-        <v>1005</v>
       </c>
       <c r="G12" s="308"/>
       <c r="H12" s="140" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="I12" s="309"/>
       <c r="J12" s="310" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K12" s="309" t="s">
         <v>1007</v>
       </c>
-      <c r="K12" s="309" t="s">
+      <c r="L12" s="309" t="s">
         <v>1008</v>
-      </c>
-      <c r="L12" s="309" t="s">
-        <v>1009</v>
       </c>
       <c r="M12" s="309"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="306" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B13" s="307" t="s">
         <v>1010</v>
       </c>
-      <c r="B13" s="307" t="s">
-        <v>1011</v>
-      </c>
       <c r="C13" s="307" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D13" s="307">
         <v>120</v>
       </c>
       <c r="E13" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F13" s="307" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G13" s="308" t="s">
         <v>1012</v>
       </c>
-      <c r="G13" s="308" t="s">
-        <v>1013</v>
-      </c>
       <c r="H13" s="140" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I13" s="309"/>
       <c r="J13" s="310" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K13" s="309" t="s">
         <v>1014</v>
       </c>
-      <c r="K13" s="309" t="s">
+      <c r="L13" s="309" t="s">
         <v>1015</v>
-      </c>
-      <c r="L13" s="309" t="s">
-        <v>1016</v>
       </c>
       <c r="M13" s="309"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="306" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B14" s="307" t="s">
         <v>1017</v>
       </c>
-      <c r="B14" s="307" t="s">
+      <c r="C14" s="307" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D14" s="307" t="s">
         <v>1018</v>
       </c>
-      <c r="C14" s="307" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D14" s="307" t="s">
+      <c r="E14" s="307" t="s">
         <v>1019</v>
       </c>
-      <c r="E14" s="307" t="s">
+      <c r="F14" s="307" t="s">
         <v>1020</v>
       </c>
-      <c r="F14" s="307" t="s">
+      <c r="G14" s="308" t="s">
         <v>1021</v>
       </c>
-      <c r="G14" s="308" t="s">
+      <c r="H14" s="140" t="s">
         <v>1022</v>
-      </c>
-      <c r="H14" s="140" t="s">
-        <v>1023</v>
       </c>
       <c r="I14" s="309"/>
       <c r="J14" s="309"/>
       <c r="K14" s="309" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L14" s="309" t="s">
         <v>1024</v>
-      </c>
-      <c r="L14" s="309" t="s">
-        <v>1025</v>
       </c>
       <c r="M14" s="309"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="139" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B15" s="307" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C15" s="307" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D15" s="307"/>
       <c r="E15" s="307"/>
       <c r="F15" s="307"/>
       <c r="G15" s="308"/>
       <c r="H15" s="140" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="I15" s="309"/>
       <c r="J15" s="310" t="s">
+        <v>1026</v>
+      </c>
+      <c r="K15" s="309" t="s">
         <v>1027</v>
       </c>
-      <c r="K15" s="309" t="s">
+      <c r="L15" s="309" t="s">
         <v>1028</v>
-      </c>
-      <c r="L15" s="309" t="s">
-        <v>1029</v>
       </c>
       <c r="M15" s="309"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="306" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B16" s="307" t="s">
         <v>1030</v>
       </c>
-      <c r="B16" s="307" t="s">
+      <c r="C16" s="307" t="s">
         <v>1031</v>
       </c>
-      <c r="C16" s="307" t="s">
+      <c r="D16" s="307" t="s">
         <v>1032</v>
       </c>
-      <c r="D16" s="307" t="s">
+      <c r="E16" s="307" t="s">
         <v>1033</v>
       </c>
-      <c r="E16" s="307" t="s">
-        <v>1034</v>
-      </c>
       <c r="F16" s="307" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G16" s="308"/>
       <c r="H16" s="140" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="I16" s="309"/>
       <c r="J16" s="310" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K16" s="309" t="s">
         <v>1036</v>
       </c>
-      <c r="K16" s="309" t="s">
+      <c r="L16" s="309" t="s">
         <v>1037</v>
-      </c>
-      <c r="L16" s="309" t="s">
-        <v>1038</v>
       </c>
       <c r="M16" s="309"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="306" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B17" s="307" t="s">
         <v>1039</v>
       </c>
-      <c r="B17" s="307" t="s">
+      <c r="C17" s="307" t="s">
         <v>1040</v>
       </c>
-      <c r="C17" s="307" t="s">
+      <c r="D17" s="307" t="s">
         <v>1041</v>
       </c>
-      <c r="D17" s="307" t="s">
-        <v>1042</v>
-      </c>
       <c r="E17" s="307" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F17" s="307" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G17" s="308"/>
       <c r="H17" s="140" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="I17" s="309"/>
       <c r="J17" s="309"/>
       <c r="K17" s="309" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="L17" s="309"/>
       <c r="M17" s="309"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="306" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B18" s="307" t="s">
         <v>1044</v>
       </c>
-      <c r="B18" s="307" t="s">
+      <c r="C18" s="307" t="s">
         <v>1045</v>
       </c>
-      <c r="C18" s="307" t="s">
+      <c r="D18" s="307" t="s">
         <v>1046</v>
       </c>
-      <c r="D18" s="307" t="s">
+      <c r="E18" s="307" t="s">
         <v>1047</v>
       </c>
-      <c r="E18" s="307" t="s">
+      <c r="F18" s="307" t="s">
         <v>1048</v>
-      </c>
-      <c r="F18" s="307" t="s">
-        <v>1049</v>
       </c>
       <c r="G18" s="308"/>
       <c r="H18" s="140" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="I18" s="309"/>
       <c r="J18" s="309"/>
       <c r="K18" s="309" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L18" s="309" t="s">
         <v>1051</v>
-      </c>
-      <c r="L18" s="309" t="s">
-        <v>1052</v>
       </c>
       <c r="M18" s="309"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="306" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B19" s="307" t="s">
         <v>1053</v>
       </c>
-      <c r="B19" s="307" t="s">
+      <c r="C19" s="307" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D19" s="307" t="s">
         <v>1054</v>
       </c>
-      <c r="C19" s="307" t="s">
+      <c r="E19" s="307" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F19" s="307" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G19" s="308" t="s">
         <v>1054</v>
       </c>
-      <c r="D19" s="307" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E19" s="307" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F19" s="307" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G19" s="308" t="s">
-        <v>1055</v>
-      </c>
       <c r="H19" s="308" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I19" s="309"/>
       <c r="J19" s="309"/>
       <c r="K19" s="309" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L19" s="309" t="s">
         <v>1058</v>
-      </c>
-      <c r="L19" s="309" t="s">
-        <v>1059</v>
       </c>
       <c r="M19" s="309"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B20" s="140" t="s">
         <v>1060</v>
       </c>
-      <c r="B20" s="140" t="s">
+      <c r="C20" s="140" t="s">
         <v>1061</v>
-      </c>
-      <c r="C20" s="140" t="s">
-        <v>1062</v>
       </c>
       <c r="D20" s="307"/>
       <c r="E20" s="307"/>
       <c r="F20" s="307"/>
       <c r="G20" s="308" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H20" s="140" t="s">
         <v>1063</v>
-      </c>
-      <c r="H20" s="140" t="s">
-        <v>1064</v>
       </c>
       <c r="I20" s="309"/>
       <c r="J20" s="309"/>
       <c r="K20" s="309" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L20" s="309" t="s">
         <v>1065</v>
-      </c>
-      <c r="L20" s="309" t="s">
-        <v>1066</v>
       </c>
       <c r="M20" s="309"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="306" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B21" s="307" t="s">
         <v>1067</v>
       </c>
-      <c r="B21" s="307" t="s">
+      <c r="C21" s="307" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D21" s="307" t="s">
         <v>1068</v>
       </c>
-      <c r="C21" s="307" t="s">
+      <c r="E21" s="307" t="s">
         <v>1068</v>
-      </c>
-      <c r="D21" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E21" s="307" t="s">
-        <v>1069</v>
       </c>
       <c r="F21" s="307"/>
       <c r="G21" s="142" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H21" s="140" t="s">
         <v>1070</v>
-      </c>
-      <c r="H21" s="140" t="s">
-        <v>1071</v>
       </c>
       <c r="I21" s="309"/>
       <c r="J21" s="310" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K21" s="309" t="s">
         <v>1072</v>
-      </c>
-      <c r="K21" s="309" t="s">
-        <v>1073</v>
       </c>
       <c r="L21" s="309"/>
       <c r="M21" s="309"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="306" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B22" s="307" t="s">
         <v>1074</v>
       </c>
-      <c r="B22" s="307" t="s">
+      <c r="C22" s="307" t="s">
         <v>1075</v>
       </c>
-      <c r="C22" s="307" t="s">
+      <c r="D22" s="307" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E22" s="307" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F22" s="307" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G22" s="308" t="s">
         <v>1076</v>
       </c>
-      <c r="D22" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E22" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F22" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G22" s="308" t="s">
+      <c r="H22" s="140" t="s">
         <v>1077</v>
-      </c>
-      <c r="H22" s="140" t="s">
-        <v>1078</v>
       </c>
       <c r="I22" s="309"/>
       <c r="J22" s="309"/>
       <c r="K22" s="309" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L22" s="309" t="s">
         <v>1079</v>
-      </c>
-      <c r="L22" s="309" t="s">
-        <v>1080</v>
       </c>
       <c r="M22" s="309"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="306" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B23" s="307" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C23" s="307" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D23" s="307" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E23" s="307" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F23" s="307" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G23" s="308" t="s">
         <v>1081</v>
       </c>
-      <c r="B23" s="307" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C23" s="307" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D23" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E23" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F23" s="307" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G23" s="308" t="s">
-        <v>1082</v>
-      </c>
       <c r="H23" s="140" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="I23" s="309"/>
       <c r="J23" s="309"/>
       <c r="K23" s="309" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L23" s="309" t="s">
         <v>1083</v>
-      </c>
-      <c r="L23" s="309" t="s">
-        <v>1084</v>
       </c>
       <c r="M23" s="309"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="306" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B24" s="307" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C24" s="307" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D24" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E24" s="307" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F24" s="307"/>
       <c r="G24" s="308"/>
       <c r="H24" s="140" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="I24" s="309"/>
       <c r="J24" s="309"/>
       <c r="K24" s="309" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L24" s="309" t="s">
         <v>1086</v>
-      </c>
-      <c r="L24" s="309" t="s">
-        <v>1087</v>
       </c>
       <c r="M24" s="309"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="306" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B25" s="307">
         <v>0.05</v>
@@ -25453,10 +25424,10 @@
         <v>0.05</v>
       </c>
       <c r="D25" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E25" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F25" s="307"/>
       <c r="G25" s="308">
@@ -25468,292 +25439,292 @@
       <c r="I25" s="309"/>
       <c r="J25" s="309"/>
       <c r="K25" s="309" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="L25" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M25" s="309"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="306" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B26" s="307" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C26" s="307" t="s">
         <v>1090</v>
       </c>
-      <c r="B26" s="307" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C26" s="307" t="s">
+      <c r="D26" s="307" t="s">
+        <v>940</v>
+      </c>
+      <c r="E26" s="307" t="s">
         <v>1091</v>
-      </c>
-      <c r="D26" s="307" t="s">
-        <v>941</v>
-      </c>
-      <c r="E26" s="307" t="s">
-        <v>1092</v>
       </c>
       <c r="F26" s="307"/>
       <c r="G26" s="308" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H26" s="140" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="I26" s="309"/>
       <c r="J26" s="309"/>
       <c r="K26" s="309" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="L26" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M26" s="309"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="306" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B27" s="307" t="s">
         <v>1095</v>
       </c>
-      <c r="B27" s="307" t="s">
+      <c r="C27" s="307" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D27" s="307" t="s">
+        <v>940</v>
+      </c>
+      <c r="E27" s="307" t="s">
         <v>1096</v>
-      </c>
-      <c r="C27" s="307" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D27" s="307" t="s">
-        <v>941</v>
-      </c>
-      <c r="E27" s="307" t="s">
-        <v>1097</v>
       </c>
       <c r="F27" s="307"/>
       <c r="G27" s="308"/>
       <c r="H27" s="307" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="I27" s="309"/>
       <c r="J27" s="309"/>
       <c r="K27" s="309" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="L27" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M27" s="309"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="306" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B28" s="307" t="s">
         <v>1099</v>
       </c>
-      <c r="B28" s="307" t="s">
+      <c r="C28" s="307" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D28" s="307" t="s">
+        <v>940</v>
+      </c>
+      <c r="E28" s="307" t="s">
         <v>1100</v>
-      </c>
-      <c r="C28" s="307" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D28" s="307" t="s">
-        <v>941</v>
-      </c>
-      <c r="E28" s="307" t="s">
-        <v>1101</v>
       </c>
       <c r="F28" s="307"/>
       <c r="G28" s="307" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H28" s="140" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I28" s="309"/>
       <c r="J28" s="309" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="K28" s="309" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="L28" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M28" s="309"/>
     </row>
     <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="306" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B29" s="307" t="s">
         <v>1104</v>
       </c>
-      <c r="B29" s="307" t="s">
+      <c r="C29" s="307" t="s">
         <v>1105</v>
       </c>
-      <c r="C29" s="307" t="s">
+      <c r="D29" s="307" t="s">
         <v>1106</v>
       </c>
-      <c r="D29" s="307" t="s">
-        <v>1107</v>
-      </c>
       <c r="E29" s="307" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F29" s="307"/>
       <c r="G29" s="308" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H29" s="140" t="s">
         <v>1108</v>
-      </c>
-      <c r="H29" s="140" t="s">
-        <v>1109</v>
       </c>
       <c r="I29" s="309"/>
       <c r="J29" s="310" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K29" s="309" t="s">
         <v>1110</v>
-      </c>
-      <c r="K29" s="309" t="s">
-        <v>1111</v>
       </c>
       <c r="L29" s="309"/>
       <c r="M29" s="309"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="306" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B30" s="307" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C30" s="307" t="s">
         <v>1112</v>
       </c>
-      <c r="C30" s="307" t="s">
-        <v>1113</v>
-      </c>
       <c r="D30" s="307" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E30" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F30" s="307"/>
       <c r="G30" s="308" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H30" s="140" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="I30" s="309"/>
       <c r="J30" s="310" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K30" s="309" t="s">
         <v>1115</v>
       </c>
-      <c r="K30" s="309" t="s">
+      <c r="L30" s="309" t="s">
         <v>1116</v>
-      </c>
-      <c r="L30" s="309" t="s">
-        <v>1117</v>
       </c>
       <c r="M30" s="309"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="306" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B31" s="307" t="s">
         <v>1118</v>
       </c>
-      <c r="B31" s="307" t="s">
-        <v>1119</v>
-      </c>
       <c r="C31" s="307" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D31" s="307" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E31" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F31" s="307"/>
       <c r="G31" s="308" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H31" s="307" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I31" s="309"/>
       <c r="J31" s="310" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K31" s="309" t="s">
         <v>1121</v>
       </c>
-      <c r="K31" s="309" t="s">
+      <c r="L31" s="309" t="s">
         <v>1122</v>
-      </c>
-      <c r="L31" s="309" t="s">
-        <v>1123</v>
       </c>
       <c r="M31" s="309"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="306" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B32" s="307" t="s">
         <v>1124</v>
       </c>
-      <c r="B32" s="307" t="s">
-        <v>1125</v>
-      </c>
       <c r="C32" s="307" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D32" s="307" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E32" s="307" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F32" s="307"/>
       <c r="G32" s="308" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H32" s="140" t="s">
         <v>1126</v>
-      </c>
-      <c r="H32" s="140" t="s">
-        <v>1127</v>
       </c>
       <c r="I32" s="309"/>
       <c r="J32" s="309"/>
       <c r="K32" s="309" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L32" s="309" t="s">
         <v>1128</v>
-      </c>
-      <c r="L32" s="309" t="s">
-        <v>1129</v>
       </c>
       <c r="M32" s="309"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="306" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B33" s="307" t="s">
         <v>1130</v>
       </c>
-      <c r="B33" s="307" t="s">
+      <c r="C33" s="307" t="s">
         <v>1131</v>
       </c>
-      <c r="C33" s="307" t="s">
+      <c r="D33" s="307" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E33" s="307" t="s">
         <v>1132</v>
-      </c>
-      <c r="D33" s="307" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E33" s="307" t="s">
-        <v>1133</v>
       </c>
       <c r="F33" s="307"/>
       <c r="G33" s="308" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H33" s="140" t="s">
         <v>1134</v>
-      </c>
-      <c r="H33" s="140" t="s">
-        <v>1135</v>
       </c>
       <c r="I33" s="309"/>
       <c r="J33" s="310" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K33" s="309" t="s">
         <v>1136</v>
       </c>
-      <c r="K33" s="309" t="s">
-        <v>1137</v>
-      </c>
       <c r="L33" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M33" s="309"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="306" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B34" s="307" t="s">
         <v>1138</v>
       </c>
-      <c r="B34" s="307" t="s">
+      <c r="C34" s="307" t="s">
         <v>1139</v>
-      </c>
-      <c r="C34" s="307" t="s">
-        <v>1140</v>
       </c>
       <c r="D34" s="307">
         <v>1000</v>
@@ -25773,16 +25744,16 @@
       <c r="I34" s="309"/>
       <c r="J34" s="309"/>
       <c r="K34" s="309" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L34" s="309" t="s">
         <v>1141</v>
-      </c>
-      <c r="L34" s="309" t="s">
-        <v>1142</v>
       </c>
       <c r="M34" s="309"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="306" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B35" s="307">
         <v>1.75</v>
@@ -25807,10 +25778,10 @@
       </c>
       <c r="I35" s="309"/>
       <c r="J35" s="309" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K35" s="309" t="s">
         <v>1144</v>
-      </c>
-      <c r="K35" s="309" t="s">
-        <v>1145</v>
       </c>
       <c r="L35" s="309"/>
       <c r="M35" s="309"/>
@@ -25826,10 +25797,10 @@
       <c r="I36" s="309"/>
       <c r="J36" s="309"/>
       <c r="K36" s="309" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="L36" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M36" s="309"/>
     </row>
@@ -25844,10 +25815,10 @@
       <c r="I37" s="309"/>
       <c r="J37" s="309"/>
       <c r="K37" s="309" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L37" s="309" t="s">
         <v>1147</v>
-      </c>
-      <c r="L37" s="309" t="s">
-        <v>1148</v>
       </c>
       <c r="M37" s="309"/>
     </row>
@@ -25862,7 +25833,7 @@
       <c r="I38" s="309"/>
       <c r="J38" s="309"/>
       <c r="K38" s="309" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L38" s="309"/>
       <c r="M38" s="309"/>
@@ -25878,10 +25849,10 @@
       <c r="I39" s="309"/>
       <c r="J39" s="309"/>
       <c r="K39" s="309" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L39" s="309" t="s">
         <v>1150</v>
-      </c>
-      <c r="L39" s="309" t="s">
-        <v>1151</v>
       </c>
       <c r="M39" s="309"/>
     </row>
@@ -25896,10 +25867,10 @@
       <c r="I40" s="309"/>
       <c r="J40" s="309"/>
       <c r="K40" s="309" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="L40" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M40" s="309"/>
     </row>
@@ -25914,10 +25885,10 @@
       <c r="I41" s="309"/>
       <c r="J41" s="309"/>
       <c r="K41" s="309" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L41" s="309" t="s">
         <v>1153</v>
-      </c>
-      <c r="L41" s="309" t="s">
-        <v>1154</v>
       </c>
       <c r="M41" s="309"/>
     </row>
@@ -25932,10 +25903,10 @@
       <c r="I42" s="309"/>
       <c r="J42" s="309"/>
       <c r="K42" s="309" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L42" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M42" s="309"/>
     </row>
@@ -25950,10 +25921,10 @@
       <c r="I43" s="309"/>
       <c r="J43" s="309"/>
       <c r="K43" s="309" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="L43" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M43" s="309"/>
     </row>
@@ -25968,7 +25939,7 @@
       <c r="I44" s="309"/>
       <c r="J44" s="309"/>
       <c r="K44" s="309" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="L44" s="309"/>
       <c r="M44" s="309"/>
@@ -25984,10 +25955,10 @@
       <c r="I45" s="309"/>
       <c r="J45" s="309"/>
       <c r="K45" s="309" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L45" s="309" t="s">
         <v>1158</v>
-      </c>
-      <c r="L45" s="309" t="s">
-        <v>1159</v>
       </c>
       <c r="M45" s="309"/>
     </row>
@@ -26002,10 +25973,10 @@
       <c r="I46" s="309"/>
       <c r="J46" s="309"/>
       <c r="K46" s="309" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L46" s="309" t="s">
         <v>1160</v>
-      </c>
-      <c r="L46" s="309" t="s">
-        <v>1161</v>
       </c>
       <c r="M46" s="309"/>
     </row>
@@ -26020,10 +25991,10 @@
       <c r="I47" s="309"/>
       <c r="J47" s="309"/>
       <c r="K47" s="309" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L47" s="309" t="s">
         <v>1162</v>
-      </c>
-      <c r="L47" s="309" t="s">
-        <v>1163</v>
       </c>
       <c r="M47" s="309"/>
     </row>
@@ -26038,47 +26009,47 @@
       <c r="I48" s="309"/>
       <c r="J48" s="309"/>
       <c r="K48" s="309" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L48" s="309" t="s">
         <v>1164</v>
-      </c>
-      <c r="L48" s="309" t="s">
-        <v>1165</v>
       </c>
       <c r="M48" s="309"/>
     </row>
     <row r="49" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J49" s="309"/>
       <c r="K49" s="309" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="L49" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M49" s="309"/>
     </row>
     <row r="50" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J50" s="309"/>
       <c r="K50" s="309" t="s">
+        <v>1166</v>
+      </c>
+      <c r="L50" s="309" t="s">
         <v>1167</v>
-      </c>
-      <c r="L50" s="309" t="s">
-        <v>1168</v>
       </c>
       <c r="M50" s="309"/>
     </row>
     <row r="51" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J51" s="309"/>
       <c r="K51" s="309" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L51" s="309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M51" s="309"/>
     </row>
     <row r="52" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J52" s="309"/>
       <c r="K52" s="309" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="L52" s="309"/>
       <c r="M52" s="309"/>
@@ -26086,30 +26057,30 @@
     <row r="53" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J53" s="309"/>
       <c r="K53" s="309" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L53" s="309" t="s">
         <v>1171</v>
-      </c>
-      <c r="L53" s="309" t="s">
-        <v>1172</v>
       </c>
       <c r="M53" s="309"/>
     </row>
     <row r="54" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J54" s="309"/>
       <c r="K54" s="309" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L54" s="309" t="s">
         <v>1173</v>
-      </c>
-      <c r="L54" s="309" t="s">
-        <v>1174</v>
       </c>
       <c r="M54" s="309"/>
     </row>
     <row r="55" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J55" s="309"/>
       <c r="K55" s="309" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L55" s="309" t="s">
         <v>1175</v>
-      </c>
-      <c r="L55" s="309" t="s">
-        <v>1176</v>
       </c>
       <c r="M55" s="309"/>
     </row>
@@ -26136,7 +26107,7 @@
         <v>364</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>365</v>
@@ -26145,12 +26116,12 @@
         <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="100" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -26159,81 +26130,81 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>1204</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" s="89" t="s">
         <v>1205</v>
-      </c>
-      <c r="E6" s="89" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C7" t="s">
         <v>1207</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>1213</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C15" t="s">
         <v>1215</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -26241,7 +26212,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -26249,71 +26220,71 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="97" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E19" s="89" t="s">
         <v>1219</v>
-      </c>
-      <c r="E19" s="89" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="101" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>1222</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="89" t="s">
         <v>1224</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="E23" s="89" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="101" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B30" t="s">
         <v>1227</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>1228</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>1229</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="74" t="s">
         <v>1230</v>
-      </c>
-      <c r="E30" s="74" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="99" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
         <v>1232</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1233</v>
       </c>
     </row>
   </sheetData>
@@ -26500,10 +26471,10 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="D8" s="278"/>
       <c r="E8" s="1">
@@ -26518,10 +26489,10 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
       <c r="B9" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="D9" s="278"/>
       <c r="E9" s="1">
@@ -26536,7 +26507,7 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C10" s="245" t="s">
         <v>161</v>
@@ -26571,10 +26542,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>388</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>389</v>
       </c>
       <c r="C12" s="245" t="s">
         <v>161</v>
@@ -26645,13 +26616,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="150" t="s">
+        <v>389</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="54" t="s">
         <v>391</v>
-      </c>
-      <c r="C16" s="54" t="s">
-        <v>392</v>
       </c>
       <c r="D16" s="278"/>
       <c r="E16" s="1">
@@ -26666,10 +26637,10 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C17" s="53" t="s">
         <v>393</v>
-      </c>
-      <c r="C17" s="53" t="s">
-        <v>394</v>
       </c>
       <c r="D17" s="278"/>
       <c r="E17" s="1">
@@ -26681,10 +26652,10 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D18" s="278"/>
       <c r="E18" s="1">
@@ -26696,10 +26667,10 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
       <c r="B19" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D19" s="281"/>
       <c r="E19" s="25">
@@ -26764,7 +26735,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="282" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="63"/>
     </row>
@@ -26840,7 +26811,7 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="67"/>
       <c r="B7" s="245" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="8">
@@ -26851,7 +26822,7 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="67"/>
       <c r="B8" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="8">
@@ -26862,7 +26833,7 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="67"/>
       <c r="B9" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C9"/>
       <c r="D9" s="8">
@@ -26873,7 +26844,7 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="67"/>
       <c r="B10" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="8">
@@ -26884,7 +26855,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="67"/>
       <c r="B11" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="8">
@@ -26894,30 +26865,30 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="66" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B12" s="245" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="8">
         <v>8</v>
       </c>
       <c r="E12" s="69" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="67"/>
       <c r="B13" s="245" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="8">
         <v>12</v>
       </c>
       <c r="E13" s="69" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -26934,7 +26905,7 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="67"/>
       <c r="B15" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="8">
@@ -26945,7 +26916,7 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="67"/>
       <c r="B16" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="8">
@@ -26956,7 +26927,7 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="67"/>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="8">
@@ -26967,7 +26938,7 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="67"/>
       <c r="B18" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="8">
@@ -26978,7 +26949,7 @@
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="67"/>
       <c r="B19" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="8">
@@ -26989,7 +26960,7 @@
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="67"/>
       <c r="B20" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="8">
@@ -27000,7 +26971,7 @@
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="67"/>
       <c r="B21" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="8">
@@ -27022,7 +26993,7 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="67"/>
       <c r="B23" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="8">
@@ -27033,7 +27004,7 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="67"/>
       <c r="B24" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="8">
@@ -27044,7 +27015,7 @@
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="67"/>
       <c r="B25" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="8">
@@ -27055,10 +27026,10 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="67"/>
       <c r="B26" s="245" t="s">
+        <v>413</v>
+      </c>
+      <c r="C26" s="60" t="s">
         <v>414</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>415</v>
       </c>
       <c r="D26" s="8">
         <v>2</v>
@@ -27068,10 +27039,10 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="67"/>
       <c r="B27" s="245" t="s">
+        <v>415</v>
+      </c>
+      <c r="C27" s="60" t="s">
         <v>416</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>417</v>
       </c>
       <c r="D27" s="8">
         <v>1</v>
@@ -27081,7 +27052,7 @@
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="67"/>
       <c r="B28" s="245" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="8">
@@ -27092,10 +27063,10 @@
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="67"/>
       <c r="B29" s="22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D29" s="8">
         <v>1</v>
@@ -27106,10 +27077,10 @@
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="22" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C30" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D30" s="8">
         <v>4</v>
@@ -27120,10 +27091,10 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="67"/>
       <c r="B31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C31" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D31" s="8">
         <v>2</v>
@@ -27134,10 +27105,10 @@
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="67"/>
       <c r="B32" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C32" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D32" s="8">
         <v>1</v>
@@ -27148,10 +27119,10 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="67"/>
       <c r="B33" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C33" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D33" s="8">
         <v>1</v>
@@ -27162,10 +27133,10 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="67"/>
       <c r="B34" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C34" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D34" s="8">
         <v>1</v>
@@ -27176,10 +27147,10 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="67"/>
       <c r="B35" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C35" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D35" s="8">
         <v>1</v>
@@ -27190,10 +27161,10 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="67"/>
       <c r="B36" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C36" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D36" s="8">
         <v>1</v>
@@ -27204,10 +27175,10 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="67"/>
       <c r="B37" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C37" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D37" s="8">
         <v>2</v>
@@ -27218,10 +27189,10 @@
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="67"/>
       <c r="B38" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C38" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D38" s="8">
         <v>2</v>
@@ -27232,10 +27203,10 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="67"/>
       <c r="B39" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C39" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D39" s="8">
         <v>1</v>
@@ -27246,10 +27217,10 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="67"/>
       <c r="B40" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C40" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
@@ -27260,10 +27231,10 @@
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="67"/>
       <c r="B41" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C41" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D41" s="8">
         <v>1</v>
@@ -27274,10 +27245,10 @@
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="67"/>
       <c r="B42" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C42" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D42" s="8">
         <v>1</v>
@@ -27288,10 +27259,10 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="67"/>
       <c r="B43" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C43" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D43" s="8">
         <v>1</v>
@@ -27302,10 +27273,10 @@
     <row r="44" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="70"/>
       <c r="B44" s="22" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C44" s="284" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D44" s="71">
         <v>1</v>
@@ -27367,7 +27338,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="277" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="31"/>
     </row>
@@ -27376,7 +27347,7 @@
         <v>368</v>
       </c>
       <c r="B2" s="245" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C2"/>
       <c r="D2" s="247">
@@ -27406,7 +27377,7 @@
         <v>375</v>
       </c>
       <c r="B4" s="264" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C4" s="264"/>
       <c r="D4" s="247">
@@ -27432,7 +27403,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C6"/>
       <c r="D6" s="247">
@@ -27443,7 +27414,7 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C7" s="286"/>
       <c r="D7" s="247">
@@ -27497,7 +27468,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B12" t="s">
         <v>183</v>
@@ -27522,7 +27493,7 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C14"/>
       <c r="D14" s="247">
@@ -27533,7 +27504,7 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C15"/>
       <c r="D15" s="247">
@@ -27544,7 +27515,7 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C16"/>
       <c r="D16" s="247">
@@ -27555,7 +27526,7 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C17"/>
       <c r="D17" s="247">
@@ -27577,7 +27548,7 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="102" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C19" s="102"/>
       <c r="D19" s="247">
@@ -27588,7 +27559,7 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="245" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C20"/>
       <c r="D20" s="247">
@@ -27599,7 +27570,7 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="286" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C21" s="286"/>
       <c r="D21" s="247">
@@ -27610,7 +27581,7 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="286" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C22" s="286"/>
       <c r="D22" s="247">
@@ -27621,7 +27592,7 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="286" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C23" s="286"/>
       <c r="D23" s="247">
@@ -27632,7 +27603,7 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="286" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C24" s="286"/>
       <c r="D24" s="247">
@@ -27643,7 +27614,7 @@
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="22" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="247">
@@ -27654,7 +27625,7 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C26" s="48"/>
       <c r="D26" s="247">
@@ -27665,7 +27636,7 @@
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="247">
@@ -27676,7 +27647,7 @@
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="48" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C28" s="286"/>
       <c r="D28" s="247">
@@ -27687,7 +27658,7 @@
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C29" s="47"/>
       <c r="D29" s="247">
@@ -27698,7 +27669,7 @@
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="48" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C30" s="48"/>
       <c r="D30" s="247">
@@ -27716,7 +27687,7 @@
     <row r="32" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="27"/>
@@ -27731,14 +27702,14 @@
         <v>365</v>
       </c>
       <c r="D33" s="287" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E33" s="37"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="8">
@@ -27749,18 +27720,18 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C35" s="261"/>
       <c r="D35" s="183" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E35" s="37"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="28">
@@ -27771,7 +27742,7 @@
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C37" s="102"/>
       <c r="D37" s="28">
@@ -27782,7 +27753,7 @@
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C38" s="286"/>
       <c r="D38" s="28">
@@ -27793,7 +27764,7 @@
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C39" s="47"/>
       <c r="D39" s="8">
@@ -27815,7 +27786,7 @@
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="257"/>
       <c r="B41" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C41"/>
       <c r="D41" s="28">
@@ -27826,7 +27797,7 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="257"/>
       <c r="B42" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C42"/>
       <c r="D42" s="28">
@@ -27848,7 +27819,7 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="288"/>
       <c r="B44" s="181" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C44" s="182"/>
       <c r="D44" s="29">
@@ -27909,7 +27880,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="277" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="31"/>
       <c r="F1" s="245"/>
@@ -27919,13 +27890,13 @@
         <v>368</v>
       </c>
       <c r="B2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="184" t="s">
         <v>467</v>
-      </c>
-      <c r="D2" s="184" t="s">
-        <v>468</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>371</v>
@@ -27940,7 +27911,7 @@
         <v>223</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D3" s="8">
         <v>12</v>
@@ -27955,10 +27926,10 @@
         <v>375</v>
       </c>
       <c r="B4" s="245" t="s">
+        <v>469</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>470</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>471</v>
       </c>
       <c r="D4" s="8">
         <v>12</v>
@@ -27976,7 +27947,7 @@
         <v>321</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D5" s="8">
         <v>3</v>
@@ -27990,7 +27961,7 @@
         <v>324</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D6" s="8">
         <v>6</v>
@@ -28004,7 +27975,7 @@
         <v>311</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D7" s="247">
         <v>1</v>
@@ -28015,10 +27986,10 @@
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="C8" s="245" t="s">
         <v>474</v>
-      </c>
-      <c r="C8" s="245" t="s">
-        <v>475</v>
       </c>
       <c r="D8" s="247">
         <v>36</v>
@@ -28029,7 +28000,7 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
       <c r="B9" s="245" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C9" s="245"/>
       <c r="D9" s="8">
@@ -28041,7 +28012,7 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="22" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D10" s="8">
         <v>3</v>
@@ -28052,7 +28023,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="245" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C11" s="245"/>
       <c r="D11" s="247">
@@ -28063,7 +28034,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B12" s="245" t="s">
         <v>244</v>
@@ -28078,10 +28049,10 @@
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="D13" s="8">
         <v>5</v>
@@ -28092,7 +28063,7 @@
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="262" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C14" s="245"/>
       <c r="D14" s="8">
@@ -28115,7 +28086,7 @@
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="245" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C16" s="245"/>
       <c r="D16" s="8">
@@ -28127,7 +28098,7 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="245" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D17" s="8">
         <v>35</v>
@@ -28182,7 +28153,7 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D22" s="8">
         <v>3</v>
@@ -28193,7 +28164,7 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D23" s="8">
         <v>3</v>
@@ -28204,7 +28175,7 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D24" s="8">
         <v>3</v>
@@ -28238,7 +28209,7 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D27" s="8">
         <v>3</v>
@@ -28249,7 +28220,7 @@
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D28" s="8">
         <v>17</v>
@@ -28260,7 +28231,7 @@
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="245" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C29" s="245"/>
       <c r="D29" s="8">
@@ -28284,7 +28255,7 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D31" s="8">
         <v>3</v>
@@ -28295,7 +28266,7 @@
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D32" s="8">
         <v>3</v>
@@ -28306,7 +28277,7 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D33" s="8">
         <v>3</v>
@@ -28317,7 +28288,7 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D34" s="8">
         <v>3</v>
@@ -28328,7 +28299,7 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D35" s="8">
         <v>1</v>
@@ -28339,10 +28310,10 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="D36" s="8">
         <v>1</v>
@@ -28353,10 +28324,10 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" t="s">
+        <v>491</v>
+      </c>
+      <c r="C37" t="s">
         <v>492</v>
-      </c>
-      <c r="C37" t="s">
-        <v>493</v>
       </c>
       <c r="D37" s="8">
         <v>1</v>
@@ -28367,10 +28338,10 @@
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D38" s="8">
         <v>1</v>
@@ -28381,10 +28352,10 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D39" s="8">
         <v>1</v>
@@ -28395,10 +28366,10 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="245" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
@@ -28409,10 +28380,10 @@
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C41" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D41" s="8">
         <v>1</v>
@@ -28423,10 +28394,10 @@
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C42" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D42" s="8">
         <v>1</v>
@@ -28437,10 +28408,10 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="245" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D43" s="8">
         <v>2</v>
@@ -28451,10 +28422,10 @@
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="245" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D44" s="8">
         <v>1</v>
@@ -28465,10 +28436,10 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="245" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D45" s="8">
         <v>1</v>
@@ -28479,10 +28450,10 @@
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="245" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D46" s="8">
         <v>1</v>
@@ -28493,10 +28464,10 @@
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="245" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D47" s="8">
         <v>1</v>
@@ -28507,10 +28478,10 @@
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D48" s="8">
         <v>1</v>
@@ -28521,10 +28492,10 @@
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D49" s="8">
         <v>1</v>
@@ -28535,10 +28506,10 @@
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D50" s="8">
         <v>1</v>
@@ -28549,10 +28520,10 @@
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="37"/>
@@ -28561,10 +28532,10 @@
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D52" s="8">
         <v>3</v>
@@ -28575,10 +28546,10 @@
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D53" s="8">
         <v>1</v>
@@ -28589,10 +28560,10 @@
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D54" s="8">
         <v>1</v>
@@ -28603,10 +28574,10 @@
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="42"/>
       <c r="B55" s="33" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D55" s="43">
         <v>1</v>
@@ -28699,7 +28670,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="277" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="31"/>
     </row>
@@ -28708,13 +28679,13 @@
         <v>368</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="C2" s="261" t="s">
         <v>583</v>
       </c>
-      <c r="C2" s="261" t="s">
+      <c r="D2" s="291" t="s">
         <v>584</v>
-      </c>
-      <c r="D2" s="291" t="s">
-        <v>585</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>371</v>
@@ -28728,7 +28699,7 @@
         <v>162</v>
       </c>
       <c r="C3" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D3" s="245">
         <v>1</v>
@@ -28742,10 +28713,10 @@
         <v>375</v>
       </c>
       <c r="B4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C4" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D4" s="245">
         <v>4</v>
@@ -28762,7 +28733,7 @@
         <v>321</v>
       </c>
       <c r="C5" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D5" s="245">
         <v>3</v>
@@ -28772,10 +28743,10 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C6" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D6" s="245">
         <v>1</v>
@@ -28785,10 +28756,10 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="245" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -28798,10 +28769,10 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="245" t="s">
+        <v>587</v>
+      </c>
+      <c r="C8" s="245" t="s">
         <v>588</v>
-      </c>
-      <c r="C8" s="245" t="s">
-        <v>589</v>
       </c>
       <c r="D8" s="245">
         <v>1</v>
@@ -28814,7 +28785,7 @@
         <v>61</v>
       </c>
       <c r="C9" s="245" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D9" s="245">
         <v>1</v>
@@ -28827,7 +28798,7 @@
         <v>52</v>
       </c>
       <c r="C10" s="245" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D10" s="245">
         <v>1</v>
@@ -28837,10 +28808,10 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="19" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C11" s="245" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D11" s="245">
         <v>1</v>
@@ -28849,13 +28820,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C12" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D12" s="245">
         <v>5</v>
@@ -28868,7 +28839,7 @@
         <v>173</v>
       </c>
       <c r="C13" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D13" s="245">
         <v>10</v>
@@ -28881,7 +28852,7 @@
         <v>177</v>
       </c>
       <c r="C14" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D14" s="245">
         <v>5</v>
@@ -28891,10 +28862,10 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="245" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C15" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D15" s="245">
         <v>5</v>
@@ -28904,10 +28875,10 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C16" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D16" s="245">
         <v>2</v>
@@ -28917,10 +28888,10 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C17" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D17" s="245">
         <v>7</v>
@@ -28930,10 +28901,10 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C18" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D18" s="245">
         <v>3</v>
@@ -28943,10 +28914,10 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="245" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C19" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -28959,7 +28930,7 @@
         <v>232</v>
       </c>
       <c r="C20" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D20" s="245">
         <v>1</v>
@@ -28969,10 +28940,10 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C21" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D21" s="245">
         <v>2</v>
@@ -28982,10 +28953,10 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C22" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D22" s="245">
         <v>4</v>
@@ -28995,10 +28966,10 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C23" s="245" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D23" s="245">
         <v>2</v>
@@ -29008,10 +28979,10 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="245" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C24" s="245" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -29021,10 +28992,10 @@
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C25" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -29034,10 +29005,10 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
@@ -29047,10 +29018,10 @@
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C27" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -29060,10 +29031,10 @@
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D28" s="245">
         <v>1</v>
@@ -29073,10 +29044,10 @@
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="20"/>
       <c r="B29" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C29" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -29086,10 +29057,10 @@
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C30" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -29099,10 +29070,10 @@
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C31" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D31" s="245">
         <v>2</v>
@@ -29112,10 +29083,10 @@
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="245" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C32" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D32" s="2">
         <v>4</v>
@@ -29125,10 +29096,10 @@
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="245" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C33" s="245" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -29138,10 +29109,10 @@
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C34" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D34" s="245">
         <v>1</v>
@@ -29151,10 +29122,10 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C35" s="245" t="s">
         <v>608</v>
-      </c>
-      <c r="C35" s="245" t="s">
-        <v>609</v>
       </c>
       <c r="D35" s="245">
         <v>2</v>
@@ -29164,10 +29135,10 @@
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" t="s">
+        <v>609</v>
+      </c>
+      <c r="C36" s="245" t="s">
         <v>610</v>
-      </c>
-      <c r="C36" s="245" t="s">
-        <v>611</v>
       </c>
       <c r="D36" s="245">
         <v>2</v>
@@ -29177,10 +29148,10 @@
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C37" s="245" t="s">
         <v>612</v>
-      </c>
-      <c r="C37" s="245" t="s">
-        <v>613</v>
       </c>
       <c r="D37" s="245">
         <v>2</v>
@@ -29190,10 +29161,10 @@
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C38" s="245" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D38" s="245">
         <v>2</v>
@@ -29203,10 +29174,10 @@
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="245" t="s">
+        <v>614</v>
+      </c>
+      <c r="C39" s="245" t="s">
         <v>615</v>
-      </c>
-      <c r="C39" s="245" t="s">
-        <v>616</v>
       </c>
       <c r="D39" s="245">
         <v>2</v>
@@ -29216,10 +29187,10 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="245" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C40" s="245" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D40" s="245">
         <v>2</v>
@@ -29229,10 +29200,10 @@
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C41" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D41" s="245">
         <v>1</v>
@@ -29242,10 +29213,10 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="245" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C42" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -29255,10 +29226,10 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="245" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C43" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D43" s="2">
         <v>1</v>
@@ -29268,10 +29239,10 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="245" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C44" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -29281,10 +29252,10 @@
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="245" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C45" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -29294,10 +29265,10 @@
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="245" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C46" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D46" s="245">
         <v>1</v>
@@ -29307,10 +29278,10 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="42"/>
       <c r="B47" s="290" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C47" s="290" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D47" s="33">
         <v>1</v>
@@ -29344,7 +29315,7 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
@@ -29366,7 +29337,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="277" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="31"/>
     </row>
@@ -29374,11 +29345,11 @@
       <c r="A2" s="35" t="s">
         <v>368</v>
       </c>
-      <c r="B2" s="322" t="s">
-        <v>684</v>
-      </c>
-      <c r="C2" s="321"/>
-      <c r="D2" s="321">
+      <c r="B2" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245">
         <v>6</v>
       </c>
       <c r="E2" s="36" t="s">
@@ -29389,11 +29360,10 @@
       <c r="A3" s="32" t="s">
         <v>372</v>
       </c>
-      <c r="B3" s="323" t="s">
+      <c r="B3" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="321">
+      <c r="D3" s="245">
         <v>1</v>
       </c>
       <c r="E3" s="285" t="s">
@@ -29404,11 +29374,11 @@
       <c r="A4" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>685</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321">
+      <c r="B4" s="245" t="s">
+        <v>684</v>
+      </c>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245">
         <v>1</v>
       </c>
       <c r="E4" s="285" t="s">
@@ -29419,134 +29389,125 @@
       <c r="A5" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="B5" s="323" t="s">
+      <c r="B5" s="266" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="321"/>
-      <c r="D5" s="321">
+      <c r="C5" s="245"/>
+      <c r="D5" s="245">
         <v>1</v>
       </c>
       <c r="E5" s="285"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
-      <c r="B6" s="323" t="s">
+      <c r="B6" s="266" t="s">
         <v>273</v>
       </c>
-      <c r="C6" s="320"/>
-      <c r="D6" s="321">
+      <c r="D6" s="245">
         <v>1</v>
       </c>
       <c r="E6" s="37"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
-      <c r="B7" s="321" t="s">
-        <v>686</v>
-      </c>
-      <c r="C7" s="321"/>
-      <c r="D7" s="321">
+      <c r="B7" s="245" t="s">
+        <v>685</v>
+      </c>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245">
         <v>5</v>
       </c>
       <c r="E7" s="37"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
-      <c r="B8" s="324" t="s">
+      <c r="B8" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="321"/>
-      <c r="D8" s="321">
+      <c r="C8" s="245"/>
+      <c r="D8" s="245">
         <v>4</v>
       </c>
       <c r="E8" s="37"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
-      <c r="B9" s="324" t="s">
+      <c r="B9" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="320"/>
-      <c r="D9" s="321">
+      <c r="D9" s="245">
         <v>12</v>
       </c>
       <c r="E9" s="37"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
-      <c r="B10" s="324" t="s">
+      <c r="B10" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="320"/>
-      <c r="D10" s="321">
+      <c r="D10" s="245">
         <v>4</v>
       </c>
       <c r="E10" s="37"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
-      <c r="B11" s="324" t="s">
+      <c r="B11" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="320"/>
-      <c r="D11" s="321">
+      <c r="D11" s="245">
         <v>4</v>
       </c>
       <c r="E11" s="37"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>388</v>
-      </c>
-      <c r="B12" s="324" t="s">
         <v>387</v>
       </c>
-      <c r="C12" s="320"/>
-      <c r="D12" s="321">
+      <c r="B12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="245">
         <v>3</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
-      <c r="B13" s="320" t="s">
+      <c r="B13" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="320"/>
-      <c r="D13" s="321">
+      <c r="D13" s="245">
         <v>7</v>
       </c>
       <c r="E13" s="37"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
-      <c r="B14" s="324" t="s">
-        <v>687</v>
-      </c>
-      <c r="C14" s="320"/>
-      <c r="D14" s="321">
+      <c r="B14" t="s">
+        <v>686</v>
+      </c>
+      <c r="D14" s="245">
         <v>1</v>
       </c>
       <c r="E14" s="37"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
-      <c r="B15" s="325" t="s">
-        <v>688</v>
-      </c>
-      <c r="C15" s="320"/>
-      <c r="D15" s="321">
+      <c r="B15" s="262" t="s">
+        <v>687</v>
+      </c>
+      <c r="D15" s="245">
         <v>1</v>
       </c>
       <c r="E15" s="37"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
-      <c r="B16" s="326" t="s">
-        <v>689</v>
-      </c>
-      <c r="C16" s="320"/>
-      <c r="D16" s="321">
+      <c r="B16" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="D16" s="245">
         <v>1</v>
       </c>
       <c r="E16" s="37"/>
@@ -29554,34 +29515,13 @@
     <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="42"/>
       <c r="B17" s="33" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="290">
         <v>1</v>
       </c>
       <c r="E17" s="44"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="320"/>
-      <c r="B18" s="320"/>
-      <c r="C18" s="320"/>
-      <c r="D18" s="320"/>
-      <c r="E18" s="320"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="320"/>
-      <c r="B19" s="320"/>
-      <c r="C19" s="320"/>
-      <c r="D19" s="320"/>
-      <c r="E19" s="320"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="320"/>
-      <c r="B20" s="320"/>
-      <c r="C20" s="320"/>
-      <c r="D20" s="320"/>
-      <c r="E20" s="320"/>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
@@ -29632,7 +29572,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="277" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="31"/>
     </row>
@@ -29644,7 +29584,7 @@
         <v>141</v>
       </c>
       <c r="C2" s="261" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D2" s="191">
         <v>1</v>
@@ -29661,7 +29601,7 @@
         <v>115</v>
       </c>
       <c r="C3" s="261" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D3" s="191">
         <v>1</v>
@@ -29690,7 +29630,7 @@
         <v>378</v>
       </c>
       <c r="B5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C5" s="245"/>
       <c r="D5" s="8">
@@ -29712,7 +29652,7 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C7" s="245"/>
       <c r="D7" s="8">
@@ -29723,7 +29663,7 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="245" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C8" s="245"/>
       <c r="D8" s="8">
@@ -29734,7 +29674,7 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
       <c r="B9" s="245" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C9" s="245"/>
       <c r="D9" s="8">
@@ -29745,7 +29685,7 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C10" s="245"/>
       <c r="D10" s="8">
@@ -29756,7 +29696,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C11" s="245"/>
       <c r="D11" s="8">
@@ -29770,7 +29710,7 @@
         <v>314</v>
       </c>
       <c r="C12" s="289" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D12" s="8">
         <v>2</v>
@@ -29779,7 +29719,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>111</v>
@@ -29815,7 +29755,7 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="8">
@@ -29826,7 +29766,7 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="8">
@@ -29837,7 +29777,7 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C18" s="245"/>
       <c r="D18" s="8">
@@ -29881,7 +29821,7 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C22" s="245"/>
       <c r="D22" s="8">
@@ -29892,7 +29832,7 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="245" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C23" s="245"/>
       <c r="D23" s="8">
@@ -29903,7 +29843,7 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="245" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C24" s="245"/>
       <c r="D24" s="8">
@@ -29925,7 +29865,7 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C26" s="245"/>
       <c r="D26" s="8">
@@ -29969,7 +29909,7 @@
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="245" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C30" s="245"/>
       <c r="D30" s="8">
@@ -29991,7 +29931,7 @@
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C32" s="245"/>
       <c r="D32" s="8">
@@ -30002,7 +29942,7 @@
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C33" s="245"/>
       <c r="D33" s="8">
@@ -30024,7 +29964,7 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="245" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C35" s="245"/>
       <c r="D35" s="8">
@@ -30035,7 +29975,7 @@
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="42"/>
       <c r="B36" s="290" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C36" s="290"/>
       <c r="D36" s="43">
@@ -30046,10 +29986,10 @@
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="34"/>
       <c r="B37" s="190" t="s">
+        <v>528</v>
+      </c>
+      <c r="C37" s="190" t="s">
         <v>529</v>
-      </c>
-      <c r="C37" s="190" t="s">
-        <v>530</v>
       </c>
       <c r="D37" s="192">
         <v>1</v>
@@ -30059,10 +29999,10 @@
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="245" t="s">
+        <v>530</v>
+      </c>
+      <c r="C38" s="245" t="s">
         <v>531</v>
-      </c>
-      <c r="C38" s="245" t="s">
-        <v>532</v>
       </c>
       <c r="D38" s="8">
         <v>1</v>
@@ -30072,10 +30012,10 @@
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C39" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D39" s="8">
         <v>1</v>
@@ -30085,10 +30025,10 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
@@ -30098,10 +30038,10 @@
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D41" s="8">
         <v>1</v>
@@ -30111,7 +30051,7 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="254" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C42" s="254" t="s">
         <v>361</v>
@@ -30124,7 +30064,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="254" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C43" s="254" t="s">
         <v>361</v>
@@ -30137,10 +30077,10 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D44" s="8">
         <v>4</v>
@@ -30150,10 +30090,10 @@
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="245" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D45" s="8">
         <v>2</v>
@@ -30163,10 +30103,10 @@
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D46" s="8">
         <v>1</v>
@@ -30176,10 +30116,10 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D47" s="8">
         <v>1</v>
@@ -30189,10 +30129,10 @@
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D48" s="8">
         <v>2</v>
@@ -30202,10 +30142,10 @@
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D49" s="8">
         <v>1</v>
@@ -30215,10 +30155,10 @@
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D50" s="8">
         <v>1</v>
@@ -30228,10 +30168,10 @@
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D51" s="8">
         <v>1</v>
@@ -30241,10 +30181,10 @@
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D52" s="8">
         <v>1</v>
@@ -30254,10 +30194,10 @@
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="245" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D53" s="8">
         <v>1</v>
@@ -30267,10 +30207,10 @@
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="245" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D54" s="8">
         <v>1</v>
@@ -30280,10 +30220,10 @@
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="245" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D55" s="8">
         <v>1</v>
@@ -30293,10 +30233,10 @@
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="245" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D56" s="8">
         <v>1</v>
@@ -30306,10 +30246,10 @@
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D57" s="8">
         <v>1</v>
@@ -30319,10 +30259,10 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D58" s="8">
         <v>1</v>
@@ -30332,10 +30272,10 @@
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
       <c r="B59" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="D59" s="8">
         <v>1</v>
@@ -30345,10 +30285,10 @@
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D60" s="8">
         <v>1</v>
@@ -30358,10 +30298,10 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D61" s="8">
         <v>1</v>
@@ -30371,10 +30311,10 @@
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D62" s="8">
         <v>1</v>
@@ -30384,10 +30324,10 @@
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D63" s="8">
         <v>1</v>
@@ -30397,10 +30337,10 @@
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D64" s="8">
         <v>1</v>
@@ -30410,10 +30350,10 @@
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="D65" s="8">
         <v>1</v>
@@ -30423,10 +30363,10 @@
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D66" s="8">
         <v>2</v>
@@ -30436,10 +30376,10 @@
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D67" s="8">
         <v>1</v>
@@ -30449,10 +30389,10 @@
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D68" s="8">
         <v>1</v>
@@ -30462,10 +30402,10 @@
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D69" s="8">
         <v>1</v>
@@ -30475,10 +30415,10 @@
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D70" s="8">
         <v>1</v>
@@ -30488,10 +30428,10 @@
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D71" s="8">
         <v>1</v>
@@ -30501,10 +30441,10 @@
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="17"/>
       <c r="B72" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D72" s="8">
         <v>1</v>
@@ -30514,10 +30454,10 @@
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="17"/>
       <c r="B73" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D73" s="8">
         <v>1</v>
@@ -30527,10 +30467,10 @@
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="245" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D74" s="8">
         <v>6</v>
@@ -30540,10 +30480,10 @@
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="17"/>
       <c r="B75" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D75" s="8">
         <v>1</v>
@@ -30553,10 +30493,10 @@
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="17"/>
       <c r="B76" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C76" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D76" s="8">
         <v>1</v>
@@ -30566,10 +30506,10 @@
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="17"/>
       <c r="B77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C77" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D77" s="8">
         <v>1</v>
@@ -30579,10 +30519,10 @@
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="17"/>
       <c r="B78" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C78" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D78" s="8">
         <v>1</v>
@@ -30592,10 +30532,10 @@
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="17"/>
       <c r="B79" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C79" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D79" s="8">
         <v>1</v>
@@ -30605,10 +30545,10 @@
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="17"/>
       <c r="B80" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C80" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D80" s="8">
         <v>1</v>
@@ -30618,10 +30558,10 @@
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="17"/>
       <c r="B81" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C81" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D81" s="8">
         <v>1</v>
@@ -30631,10 +30571,10 @@
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="17"/>
       <c r="B82" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C82" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D82" s="8">
         <v>1</v>
@@ -30644,10 +30584,10 @@
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="17"/>
       <c r="B83" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C83" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D83" s="8">
         <v>1</v>
@@ -30657,10 +30597,10 @@
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="17"/>
       <c r="B84" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C84" s="245" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D84" s="8">
         <v>1</v>
@@ -30670,10 +30610,10 @@
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="17"/>
       <c r="B85" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D85" s="8">
         <v>2</v>
@@ -30683,10 +30623,10 @@
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="42"/>
       <c r="B86" s="33" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D86" s="43">
         <v>1</v>
@@ -30750,7 +30690,7 @@
         <v>365</v>
       </c>
       <c r="D1" s="277" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E1" s="31"/>
     </row>
@@ -30759,10 +30699,10 @@
         <v>368</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="C2" s="245" t="s">
         <v>625</v>
-      </c>
-      <c r="C2" s="245" t="s">
-        <v>626</v>
       </c>
       <c r="D2" s="247">
         <v>1</v>
@@ -30776,10 +30716,10 @@
         <v>372</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C3" s="245" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D3" s="247">
         <v>1</v>
@@ -30793,10 +30733,10 @@
         <v>375</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C4" s="245" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D4" s="247">
         <v>1</v>
@@ -30810,10 +30750,10 @@
         <v>378</v>
       </c>
       <c r="B5" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="C5" s="245" t="s">
         <v>629</v>
-      </c>
-      <c r="C5" s="245" t="s">
-        <v>630</v>
       </c>
       <c r="D5" s="247">
         <v>2</v>
@@ -30823,10 +30763,10 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="292" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C6" s="245" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D6" s="247">
         <v>5</v>
@@ -30836,10 +30776,10 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="20" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D7" s="247">
         <v>2</v>
@@ -30849,10 +30789,10 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="292" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C8" s="245" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D8" s="247">
         <v>2</v>
@@ -30862,10 +30802,10 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
       <c r="B9" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C9" s="245" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D9" s="247">
         <v>2</v>
@@ -30875,10 +30815,10 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C10" s="245" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D10" s="247">
         <v>2</v>
@@ -30891,7 +30831,7 @@
         <v>155</v>
       </c>
       <c r="C11" s="245" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D11" s="247">
         <v>2</v>
@@ -30900,13 +30840,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>153</v>
       </c>
       <c r="C12" s="245" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D12" s="247">
         <v>1</v>
@@ -30919,7 +30859,7 @@
         <v>150</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D13" s="247">
         <v>1</v>
@@ -30929,10 +30869,10 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="32"/>
       <c r="B14" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C14" s="245" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D14" s="247">
         <v>1</v>
@@ -30942,10 +30882,10 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C15" s="245" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D15" s="247">
         <v>1</v>
@@ -30955,10 +30895,10 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="20" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C16" s="245" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D16" s="247">
         <v>2</v>
@@ -30968,10 +30908,10 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="20" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C17" s="245" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D17" s="247">
         <v>2</v>
@@ -30981,10 +30921,10 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="C18" s="245" t="s">
         <v>641</v>
-      </c>
-      <c r="C18" s="245" t="s">
-        <v>642</v>
       </c>
       <c r="D18" s="247">
         <v>3</v>
@@ -30994,10 +30934,10 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C19" s="245" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D19" s="247">
         <v>3</v>
@@ -31007,10 +30947,10 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C20" s="245" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D20" s="247">
         <v>3</v>
@@ -31020,10 +30960,10 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="257" t="s">
+        <v>644</v>
+      </c>
+      <c r="C21" s="245" t="s">
         <v>645</v>
-      </c>
-      <c r="C21" s="245" t="s">
-        <v>646</v>
       </c>
       <c r="D21" s="247">
         <v>5</v>
@@ -31033,10 +30973,10 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C22" s="245" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D22" s="247">
         <v>2</v>
@@ -31046,10 +30986,10 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C23" s="245" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D23" s="247">
         <v>2</v>
@@ -31059,10 +30999,10 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C24" s="245" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D24" s="247">
         <v>5</v>
@@ -31072,10 +31012,10 @@
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C25" s="245" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D25" s="247">
         <v>2</v>
@@ -31085,10 +31025,10 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="245" t="s">
+        <v>647</v>
+      </c>
+      <c r="C26" s="245" t="s">
         <v>648</v>
-      </c>
-      <c r="C26" s="245" t="s">
-        <v>649</v>
       </c>
       <c r="D26" s="247">
         <v>5</v>
@@ -31098,10 +31038,10 @@
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="245" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C27" s="245" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D27" s="247">
         <v>5</v>
@@ -31114,7 +31054,7 @@
         <v>38</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D28" s="247">
         <v>1</v>
@@ -31124,10 +31064,10 @@
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="251" t="s">
+        <v>650</v>
+      </c>
+      <c r="C29" s="251" t="s">
         <v>651</v>
-      </c>
-      <c r="C29" s="251" t="s">
-        <v>652</v>
       </c>
       <c r="D29" s="256"/>
       <c r="E29" s="37"/>
@@ -31135,10 +31075,10 @@
     <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="251" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C30" s="254" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D30" s="256"/>
       <c r="E30" s="37"/>
@@ -31149,7 +31089,7 @@
         <v>147</v>
       </c>
       <c r="C31" s="245" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D31" s="245">
         <v>1</v>
@@ -31159,7 +31099,7 @@
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
       <c r="B32" s="245" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C32" s="245"/>
       <c r="D32" s="247">
@@ -31170,10 +31110,10 @@
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="39" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D33" s="247">
         <v>1</v>
@@ -31183,10 +31123,10 @@
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="245" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D34" s="247">
         <v>1</v>
@@ -31196,7 +31136,7 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="19" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C35" s="245"/>
       <c r="D35" s="247">
@@ -31232,7 +31172,7 @@
         <v>122</v>
       </c>
       <c r="C38" s="249" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D38" s="41">
         <v>1</v>
@@ -31245,7 +31185,7 @@
         <v>125</v>
       </c>
       <c r="C39" s="249" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D39" s="41">
         <v>1</v>
@@ -31277,10 +31217,10 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="250" t="s">
+        <v>659</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>660</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>661</v>
       </c>
       <c r="D42" s="245">
         <v>1</v>
@@ -31323,7 +31263,7 @@
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C46"/>
       <c r="D46" s="247">
@@ -31334,7 +31274,7 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C47"/>
       <c r="D47" s="247">
@@ -31367,7 +31307,7 @@
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50">
@@ -31378,7 +31318,7 @@
     <row r="51" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51">
@@ -31403,7 +31343,7 @@
         <v>43</v>
       </c>
       <c r="C53" s="245" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D53" s="247">
         <v>2</v>
@@ -31416,7 +31356,7 @@
         <v>46</v>
       </c>
       <c r="C54" s="245" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D54" s="247">
         <v>1</v>
@@ -31429,7 +31369,7 @@
         <v>48</v>
       </c>
       <c r="C55" s="245" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D55" s="247">
         <v>1</v>
@@ -31442,7 +31382,7 @@
         <v>35</v>
       </c>
       <c r="C56" s="245" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D56" s="247">
         <v>1</v>
@@ -31452,10 +31392,10 @@
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="20" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D57" s="247">
         <v>1</v>
@@ -31465,10 +31405,10 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="102" t="s">
+        <v>666</v>
+      </c>
+      <c r="C58" s="245" t="s">
         <v>667</v>
-      </c>
-      <c r="C58" s="245" t="s">
-        <v>668</v>
       </c>
       <c r="D58" s="245">
         <v>1</v>
@@ -31481,7 +31421,7 @@
         <v>136</v>
       </c>
       <c r="C59" s="245" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D59" s="245">
         <v>1</v>
@@ -31491,10 +31431,10 @@
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="20" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D60" s="247">
         <v>1</v>
@@ -31504,10 +31444,10 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="C61" s="19" t="s">
         <v>671</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>672</v>
       </c>
       <c r="D61" s="247">
         <v>1</v>
@@ -31520,7 +31460,7 @@
         <v>118</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D62" s="247">
         <v>3</v>
@@ -31530,10 +31470,10 @@
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="245" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C63" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D63" s="247">
         <v>1</v>
@@ -31543,10 +31483,10 @@
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="245" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C64" s="245" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D64" s="247">
         <v>1</v>
@@ -31556,10 +31496,10 @@
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D65" s="247">
         <v>1</v>
@@ -31569,10 +31509,10 @@
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D66" s="247">
         <v>1</v>
@@ -31582,10 +31522,10 @@
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D67" s="247">
         <v>1</v>
@@ -31595,10 +31535,10 @@
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D68" s="247">
         <v>1</v>
@@ -31608,10 +31548,10 @@
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D69" s="247">
         <v>1</v>
@@ -31621,10 +31561,10 @@
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D70" s="247">
         <v>2</v>
@@ -31634,10 +31574,10 @@
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="245" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D71" s="247">
         <v>1</v>
@@ -31647,10 +31587,10 @@
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="257"/>
       <c r="B72" s="245" t="s">
+        <v>679</v>
+      </c>
+      <c r="C72" s="245" t="s">
         <v>680</v>
-      </c>
-      <c r="C72" s="245" t="s">
-        <v>681</v>
       </c>
       <c r="D72" s="8">
         <v>2</v>
@@ -31660,10 +31600,10 @@
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="257"/>
       <c r="B73" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D73" s="247">
         <v>1</v>
@@ -31673,10 +31613,10 @@
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="42"/>
       <c r="B74" s="30" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C74" s="246" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D74" s="43">
         <v>1</v>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 Build Guide Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5915" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E28401-5A2B-4AD3-A891-59713B363E0A}"/>
+  <xr:revisionPtr revIDLastSave="5925" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D91DBFC-8419-499D-8186-5CADE794F0F5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMPLETE PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -5935,6 +5935,83 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
           <color indexed="64"/>
         </left>
         <right style="medium">
@@ -6431,130 +6508,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6774,24 +6727,107 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6810,42 +6846,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="medium">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -8049,40 +8049,44 @@
 </namedSheetViews>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J151" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94" tableBorderDxfId="92" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J151" totalsRowShown="0" headerRowDxfId="94" dataDxfId="92" headerRowBorderDxfId="93" tableBorderDxfId="91" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J151" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J151">
     <sortCondition ref="A1:A151"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="90"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="88"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="87"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="86">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="87"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="86"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="85">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="85" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="84"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="83" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="84" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="83"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Qty" dataDxfId="82" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D74" totalsRowShown="0" headerRowDxfId="101" tableBorderDxfId="100" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D74" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D74" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D74">
     <sortCondition ref="B1:B74"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="99" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="98" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="97" totalsRowDxfId="96" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="34" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8205,121 +8209,121 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="101" dataDxfId="100" tableBorderDxfId="99" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="76" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="96" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D30" totalsRowShown="0" headerRowDxfId="68" tableBorderDxfId="67" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D30" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D30" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D30">
     <sortCondition ref="B1:B30"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="71" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B33:D44" totalsRowShown="0" headerRowDxfId="62" tableBorderDxfId="61" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B33:D44" totalsRowShown="0" headerRowDxfId="68" tableBorderDxfId="67" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B33:D44" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:D44">
     <sortCondition ref="B33:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="59" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="65" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D55" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D55" totalsRowShown="0" headerRowDxfId="62" tableBorderDxfId="61" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D55" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D55">
     <sortCondition ref="B1:B55"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D47" totalsRowShown="0" headerRowDxfId="50" tableBorderDxfId="49" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D47" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D47" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D47">
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="48" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D17" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D17" totalsRowShown="0" headerRowDxfId="50" tableBorderDxfId="49" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D17" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D17">
     <sortCondition ref="B1:B17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="48" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D86" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D86" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D86" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D86">
     <sortCondition ref="B1:B86"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="34" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8533,12 +8537,12 @@
     <col min="1" max="1" width="11.5703125" style="102" customWidth="1"/>
     <col min="2" max="2" width="36.7109375" style="102" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="102" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="102" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="102" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="105" customWidth="1"/>
     <col min="6" max="6" width="10" style="102" customWidth="1"/>
     <col min="7" max="7" width="36.28515625" customWidth="1"/>
     <col min="8" max="8" width="16.140625" style="102" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7" style="102" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="102" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" style="106" customWidth="1"/>
     <col min="11" max="16384" width="8.7109375" style="102"/>
   </cols>
@@ -10685,14 +10689,14 @@
         <v>194</v>
       </c>
       <c r="D70" s="198">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" s="199">
         <v>2</v>
       </c>
       <c r="F70" s="199">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G70" s="110" t="s">
         <v>169</v>
@@ -11821,7 +11825,7 @@
         <v>239</v>
       </c>
       <c r="I104" s="123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J104" s="200"/>
     </row>
@@ -11851,7 +11855,9 @@
       <c r="H105" s="265" t="s">
         <v>239</v>
       </c>
-      <c r="I105" s="123"/>
+      <c r="I105" s="123">
+        <v>3</v>
+      </c>
       <c r="J105" s="200"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -11973,7 +11979,9 @@
       <c r="H109" s="265" t="s">
         <v>251</v>
       </c>
-      <c r="I109" s="123"/>
+      <c r="I109" s="123">
+        <v>50</v>
+      </c>
       <c r="J109" s="200"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -13266,7 +13274,7 @@
       <c r="E152" s="118"/>
       <c r="F152" s="119">
         <f>SUBTOTAL(109,Table1321[*Cost Price $USD])</f>
-        <v>2369.5799999999995</v>
+        <v>2371.5799999999995</v>
       </c>
       <c r="G152" s="120" t="s">
         <v>363</v>
